--- a/Noyau RH FPE/1. DOCUMENTATION RH-PAIE/4. Autres/Impact des situations administratives sur l'avancement d'échelon.xlsx
+++ b/Noyau RH FPE/1. DOCUMENTATION RH-PAIE/4. Autres/Impact des situations administratives sur l'avancement d'échelon.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pfougere-adc\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\balidfs1\ONP\ONP\CISIRH\03-BARRI\REFERENTIELS\NOYAU\1-20260710_26.00.00\8-Informations complémentaires\Divers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E35B692-C7B0-41DD-8391-C79F01A75F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAC6B59-32AA-4AEF-B43B-301B5478B95E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="604" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="604" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3977" uniqueCount="935">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3968" uniqueCount="934">
   <si>
     <t>AVANCEMENT ECHELON</t>
   </si>
@@ -2907,12 +2907,6 @@
     <t>Congé sans salaire d'office pour raison de santé après avis de la commission médicale</t>
   </si>
   <si>
-    <t>2025-84</t>
-  </si>
-  <si>
-    <t>2025-57</t>
-  </si>
-  <si>
     <t>ACI1A</t>
   </si>
   <si>
@@ -2961,7 +2955,10 @@
     <t>Congé sans salaire pour suivre un cycle préparatoire à un concours ou période probatoire ou scolarité</t>
   </si>
   <si>
-    <t>2025-105</t>
+    <t>26.00.00</t>
+  </si>
+  <si>
+    <t>2025-91</t>
   </si>
 </sst>
 </file>
@@ -3246,7 +3243,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="3" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3355,9 +3352,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3409,12 +3403,6 @@
     <xf numFmtId="14" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3442,20 +3430,17 @@
     <xf numFmtId="11" fontId="2" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="10" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="3" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="10" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="3" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="11" fontId="3" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="3" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3465,15 +3450,6 @@
     </xf>
     <xf numFmtId="11" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="3" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="3" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="3" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3851,62 +3827,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q407"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="4" customWidth="1"/>
-    <col min="2" max="3" width="11.42578125" style="11"/>
-    <col min="4" max="4" width="48.28515625" style="11" customWidth="1"/>
-    <col min="5" max="9" width="11.42578125" style="11" hidden="1" customWidth="1"/>
-    <col min="10" max="12" width="11.42578125" style="11" customWidth="1"/>
-    <col min="13" max="13" width="16.28515625" style="11" customWidth="1"/>
-    <col min="14" max="14" width="12.42578125" style="11" customWidth="1"/>
-    <col min="15" max="15" width="20.85546875" style="18" customWidth="1"/>
-    <col min="16" max="16" width="30.140625" style="11" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="11.42578125" style="4"/>
-    <col min="18" max="16384" width="11.42578125" style="11"/>
+    <col min="1" max="1" width="9.7265625" style="4" customWidth="1"/>
+    <col min="2" max="3" width="11.453125" style="11"/>
+    <col min="4" max="4" width="48.26953125" style="11" customWidth="1"/>
+    <col min="5" max="9" width="11.453125" style="11" hidden="1" customWidth="1"/>
+    <col min="10" max="12" width="11.453125" style="11" customWidth="1"/>
+    <col min="13" max="13" width="16.26953125" style="11" customWidth="1"/>
+    <col min="14" max="14" width="12.453125" style="11" customWidth="1"/>
+    <col min="15" max="15" width="20.81640625" style="18" customWidth="1"/>
+    <col min="16" max="16" width="30.1796875" style="11" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="11.453125" style="4"/>
+    <col min="18" max="16384" width="11.453125" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
+    <row r="1" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-    </row>
-    <row r="2" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="66" t="s">
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+    </row>
+    <row r="2" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="A2" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="66" t="s">
+      <c r="C2" s="63" t="s">
         <v>572</v>
       </c>
-      <c r="D2" s="66" t="s">
+      <c r="D2" s="63" t="s">
         <v>573</v>
       </c>
-      <c r="E2" s="81" t="s">
+      <c r="E2" s="74" t="s">
         <v>574</v>
       </c>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="66" t="s">
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="63" t="s">
         <v>575</v>
       </c>
-      <c r="K2" s="66" t="s">
+      <c r="K2" s="63" t="s">
         <v>576</v>
       </c>
-      <c r="L2" s="66" t="s">
+      <c r="L2" s="63" t="s">
         <v>769</v>
       </c>
       <c r="M2" s="1" t="s">
@@ -3925,7 +3901,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>30</v>
       </c>
@@ -3935,51 +3911,51 @@
       <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="82" t="s">
+      <c r="D3" s="75" t="s">
         <v>540</v>
       </c>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="82"/>
-      <c r="O3" s="82"/>
-      <c r="P3" s="82"/>
-      <c r="Q3" s="44"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="67" t="s">
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="75"/>
+      <c r="L3" s="75"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="43"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="64" t="s">
         <v>539</v>
       </c>
-      <c r="D4" s="83" t="s">
+      <c r="D4" s="76" t="s">
         <v>540</v>
       </c>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="44"/>
-    </row>
-    <row r="5" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="76"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="43"/>
+    </row>
+    <row r="5" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="33" t="s">
         <v>30</v>
       </c>
@@ -4024,9 +4000,9 @@
         <v>682</v>
       </c>
       <c r="P5" s="12"/>
-      <c r="Q5" s="44"/>
-    </row>
-    <row r="6" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q5" s="43"/>
+    </row>
+    <row r="6" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="33" t="s">
         <v>30</v>
       </c>
@@ -4063,9 +4039,9 @@
         <v>682</v>
       </c>
       <c r="P6" s="12"/>
-      <c r="Q6" s="44"/>
-    </row>
-    <row r="7" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q6" s="43"/>
+    </row>
+    <row r="7" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="33" t="s">
         <v>770</v>
       </c>
@@ -4102,9 +4078,9 @@
         <v>682</v>
       </c>
       <c r="P7" s="12"/>
-      <c r="Q7" s="44"/>
-    </row>
-    <row r="8" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q7" s="43"/>
+    </row>
+    <row r="8" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="33" t="s">
         <v>722</v>
       </c>
@@ -4141,50 +4117,50 @@
         <v>682</v>
       </c>
       <c r="P8" s="12"/>
-      <c r="Q8" s="44"/>
-    </row>
-    <row r="9" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q8" s="43"/>
+    </row>
+    <row r="9" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="33" t="s">
         <v>887</v>
       </c>
       <c r="B9" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="61" t="s">
+      <c r="C9" s="58" t="s">
         <v>868</v>
       </c>
-      <c r="D9" s="62" t="s">
+      <c r="D9" s="59" t="s">
         <v>869</v>
       </c>
-      <c r="E9" s="61" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="61" t="s">
+      <c r="E9" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="63">
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="60">
         <v>31048</v>
       </c>
-      <c r="K9" s="63"/>
-      <c r="L9" s="63" t="s">
-        <v>591</v>
-      </c>
-      <c r="M9" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="N9" s="64" t="s">
+      <c r="K9" s="60"/>
+      <c r="L9" s="60" t="s">
+        <v>591</v>
+      </c>
+      <c r="M9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="N9" s="61" t="s">
         <v>8</v>
       </c>
       <c r="O9" s="37" t="s">
         <v>682</v>
       </c>
       <c r="P9" s="13"/>
-      <c r="Q9" s="44"/>
-    </row>
-    <row r="10" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q9" s="43"/>
+    </row>
+    <row r="10" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="33" t="s">
         <v>30</v>
       </c>
@@ -4223,9 +4199,9 @@
         <v>591</v>
       </c>
       <c r="P10" s="12"/>
-      <c r="Q10" s="44"/>
-    </row>
-    <row r="11" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q10" s="43"/>
+    </row>
+    <row r="11" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="33" t="s">
         <v>30</v>
       </c>
@@ -4264,9 +4240,9 @@
         <v>591</v>
       </c>
       <c r="P11" s="12"/>
-      <c r="Q11" s="44"/>
-    </row>
-    <row r="12" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q11" s="43"/>
+    </row>
+    <row r="12" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="33" t="s">
         <v>30</v>
       </c>
@@ -4305,9 +4281,9 @@
         <v>682</v>
       </c>
       <c r="P12" s="12"/>
-      <c r="Q12" s="44"/>
-    </row>
-    <row r="13" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q12" s="43"/>
+    </row>
+    <row r="13" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="33" t="s">
         <v>30</v>
       </c>
@@ -4346,9 +4322,9 @@
         <v>682</v>
       </c>
       <c r="P13" s="12"/>
-      <c r="Q13" s="44"/>
-    </row>
-    <row r="14" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q13" s="43"/>
+    </row>
+    <row r="14" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="33" t="s">
         <v>30</v>
       </c>
@@ -4387,52 +4363,50 @@
         <v>682</v>
       </c>
       <c r="P14" s="12"/>
-      <c r="Q14" s="44"/>
-    </row>
-    <row r="15" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="46" t="s">
+      <c r="Q14" s="43"/>
+    </row>
+    <row r="15" spans="1:17" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="33" t="s">
         <v>913</v>
       </c>
-      <c r="B15" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="38" t="s">
+      <c r="B15" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="32" t="s">
         <v>792</v>
       </c>
-      <c r="D15" s="72" t="s">
+      <c r="D15" s="7" t="s">
         <v>793</v>
       </c>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38" t="s">
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J15" s="57">
+      <c r="J15" s="35">
         <v>43460</v>
       </c>
-      <c r="K15" s="57">
+      <c r="K15" s="35">
         <v>45140</v>
       </c>
-      <c r="L15" s="57" t="s">
-        <v>591</v>
-      </c>
-      <c r="M15" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="N15" s="58" t="s">
-        <v>8</v>
-      </c>
-      <c r="O15" s="59" t="s">
+      <c r="L15" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="M15" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="N15" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="37" t="s">
         <v>682</v>
       </c>
-      <c r="P15" s="65"/>
-      <c r="Q15" s="39" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="P15" s="62"/>
+      <c r="Q15" s="38"/>
+    </row>
+    <row r="16" spans="1:17" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A16" s="33" t="s">
         <v>829</v>
       </c>
@@ -4471,9 +4445,9 @@
         <v>591</v>
       </c>
       <c r="P16" s="12"/>
-      <c r="Q16" s="44"/>
-    </row>
-    <row r="17" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Q16" s="43"/>
+    </row>
+    <row r="17" spans="1:17" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A17" s="33" t="s">
         <v>829</v>
       </c>
@@ -4512,9 +4486,9 @@
         <v>682</v>
       </c>
       <c r="P17" s="12"/>
-      <c r="Q17" s="44"/>
-    </row>
-    <row r="18" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Q17" s="43"/>
+    </row>
+    <row r="18" spans="1:17" ht="25" x14ac:dyDescent="0.35">
       <c r="A18" s="33" t="s">
         <v>829</v>
       </c>
@@ -4555,9 +4529,9 @@
         <v>682</v>
       </c>
       <c r="P18" s="12"/>
-      <c r="Q18" s="44"/>
-    </row>
-    <row r="19" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q18" s="43"/>
+    </row>
+    <row r="19" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="33" t="s">
         <v>829</v>
       </c>
@@ -4598,9 +4572,9 @@
         <v>591</v>
       </c>
       <c r="P19" s="12"/>
-      <c r="Q19" s="44"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q19" s="43"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="33" t="s">
         <v>861</v>
       </c>
@@ -4645,9 +4619,9 @@
         <v>682</v>
       </c>
       <c r="P20" s="12"/>
-      <c r="Q20" s="44"/>
-    </row>
-    <row r="21" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q20" s="43"/>
+    </row>
+    <row r="21" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="33" t="s">
         <v>861</v>
       </c>
@@ -4694,9 +4668,9 @@
       <c r="P21" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q21" s="44"/>
-    </row>
-    <row r="22" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Q21" s="43"/>
+    </row>
+    <row r="22" spans="1:17" ht="25" x14ac:dyDescent="0.35">
       <c r="A22" s="33" t="s">
         <v>890</v>
       </c>
@@ -4735,9 +4709,9 @@
         <v>591</v>
       </c>
       <c r="P22" s="12"/>
-      <c r="Q22" s="44"/>
-    </row>
-    <row r="23" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Q22" s="43"/>
+    </row>
+    <row r="23" spans="1:17" ht="25" x14ac:dyDescent="0.35">
       <c r="A23" s="33" t="s">
         <v>890</v>
       </c>
@@ -4776,9 +4750,9 @@
         <v>591</v>
       </c>
       <c r="P23" s="12"/>
-      <c r="Q23" s="44"/>
-    </row>
-    <row r="24" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Q23" s="43"/>
+    </row>
+    <row r="24" spans="1:17" ht="25" x14ac:dyDescent="0.35">
       <c r="A24" s="33" t="s">
         <v>890</v>
       </c>
@@ -4817,9 +4791,9 @@
         <v>682</v>
       </c>
       <c r="P24" s="12"/>
-      <c r="Q24" s="44"/>
-    </row>
-    <row r="25" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Q24" s="43"/>
+    </row>
+    <row r="25" spans="1:17" ht="25" x14ac:dyDescent="0.35">
       <c r="A25" s="33" t="s">
         <v>890</v>
       </c>
@@ -4858,9 +4832,9 @@
         <v>682</v>
       </c>
       <c r="P25" s="12"/>
-      <c r="Q25" s="44"/>
-    </row>
-    <row r="26" spans="1:17" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q25" s="43"/>
+    </row>
+    <row r="26" spans="1:17" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="33" t="s">
         <v>890</v>
       </c>
@@ -4899,9 +4873,9 @@
         <v>682</v>
       </c>
       <c r="P26" s="12"/>
-      <c r="Q26" s="44"/>
-    </row>
-    <row r="27" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Q26" s="43"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="33" t="s">
         <v>890</v>
       </c>
@@ -4938,9 +4912,9 @@
         <v>591</v>
       </c>
       <c r="P27" s="12"/>
-      <c r="Q27" s="44"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q27" s="43"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="33" t="s">
         <v>890</v>
       </c>
@@ -4983,7 +4957,7 @@
       <c r="P28" s="12"/>
       <c r="Q28" s="19"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="33" t="s">
         <v>890</v>
       </c>
@@ -5026,7 +5000,7 @@
       <c r="P29" s="12"/>
       <c r="Q29" s="19"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="33" t="s">
         <v>890</v>
       </c>
@@ -5069,7 +5043,7 @@
       <c r="P30" s="12"/>
       <c r="Q30" s="19"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" s="33" t="s">
         <v>890</v>
       </c>
@@ -5080,7 +5054,7 @@
         <v>912</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="E31" s="32" t="s">
         <v>6</v>
@@ -5110,212 +5084,202 @@
       <c r="P31" s="12"/>
       <c r="Q31" s="19"/>
     </row>
-    <row r="32" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="46" t="s">
+    <row r="32" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="33" t="s">
         <v>913</v>
       </c>
-      <c r="B32" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="C32" s="38" t="s">
+      <c r="B32" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>916</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>917</v>
+      </c>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="J32" s="35">
+        <v>45141</v>
+      </c>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="M32" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="N32" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="O32" s="37" t="s">
+        <v>682</v>
+      </c>
+      <c r="P32" s="62"/>
+      <c r="Q32" s="38"/>
+    </row>
+    <row r="33" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="33" t="s">
+        <v>913</v>
+      </c>
+      <c r="B33" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="32" t="s">
         <v>918</v>
       </c>
-      <c r="D32" s="72" t="s">
+      <c r="D33" s="7" t="s">
+        <v>922</v>
+      </c>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="J33" s="35">
+        <v>45141</v>
+      </c>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="M33" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="N33" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="O33" s="37" t="s">
+        <v>682</v>
+      </c>
+      <c r="P33" s="62"/>
+      <c r="Q33" s="38"/>
+    </row>
+    <row r="34" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="33" t="s">
+        <v>913</v>
+      </c>
+      <c r="B34" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="32" t="s">
         <v>919</v>
       </c>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="38" t="s">
+      <c r="D34" s="7" t="s">
+        <v>923</v>
+      </c>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J32" s="57">
+      <c r="J34" s="35">
         <v>45141</v>
       </c>
-      <c r="K32" s="57"/>
-      <c r="L32" s="57" t="s">
-        <v>591</v>
-      </c>
-      <c r="M32" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="N32" s="58" t="s">
-        <v>8</v>
-      </c>
-      <c r="O32" s="59" t="s">
+      <c r="K34" s="35"/>
+      <c r="L34" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="M34" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="N34" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="O34" s="37" t="s">
         <v>682</v>
       </c>
-      <c r="P32" s="65"/>
-      <c r="Q32" s="39" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="46" t="s">
+      <c r="P34" s="62"/>
+      <c r="Q34" s="38"/>
+    </row>
+    <row r="35" spans="1:17" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="33" t="s">
         <v>913</v>
       </c>
-      <c r="B33" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="38" t="s">
+      <c r="B35" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" s="32" t="s">
         <v>920</v>
       </c>
-      <c r="D33" s="72" t="s">
+      <c r="D35" s="7" t="s">
         <v>924</v>
       </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38" t="s">
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J33" s="57">
+      <c r="J35" s="35">
         <v>45141</v>
       </c>
-      <c r="K33" s="57"/>
-      <c r="L33" s="57" t="s">
-        <v>591</v>
-      </c>
-      <c r="M33" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="N33" s="58" t="s">
-        <v>8</v>
-      </c>
-      <c r="O33" s="59" t="s">
+      <c r="K35" s="35"/>
+      <c r="L35" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="M35" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="N35" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="O35" s="37" t="s">
         <v>682</v>
       </c>
-      <c r="P33" s="65"/>
-      <c r="Q33" s="39" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="46" t="s">
+      <c r="P35" s="62"/>
+      <c r="Q35" s="38"/>
+    </row>
+    <row r="36" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="33" t="s">
         <v>913</v>
       </c>
-      <c r="B34" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="38" t="s">
+      <c r="B36" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="32" t="s">
         <v>921</v>
       </c>
-      <c r="D34" s="72" t="s">
-        <v>925</v>
-      </c>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="38" t="s">
+      <c r="D36" s="7" t="s">
+        <v>928</v>
+      </c>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J34" s="57">
+      <c r="J36" s="35">
         <v>45141</v>
       </c>
-      <c r="K34" s="57"/>
-      <c r="L34" s="57" t="s">
-        <v>591</v>
-      </c>
-      <c r="M34" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="N34" s="58" t="s">
-        <v>8</v>
-      </c>
-      <c r="O34" s="59" t="s">
+      <c r="K36" s="35"/>
+      <c r="L36" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="M36" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="N36" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="O36" s="37" t="s">
         <v>682</v>
       </c>
-      <c r="P34" s="65"/>
-      <c r="Q34" s="39" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A35" s="46" t="s">
-        <v>913</v>
-      </c>
-      <c r="B35" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="C35" s="38" t="s">
-        <v>922</v>
-      </c>
-      <c r="D35" s="72" t="s">
-        <v>926</v>
-      </c>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
-      <c r="I35" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="J35" s="57">
-        <v>45141</v>
-      </c>
-      <c r="K35" s="57"/>
-      <c r="L35" s="57" t="s">
-        <v>591</v>
-      </c>
-      <c r="M35" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="N35" s="58" t="s">
-        <v>8</v>
-      </c>
-      <c r="O35" s="59" t="s">
-        <v>682</v>
-      </c>
-      <c r="P35" s="65"/>
-      <c r="Q35" s="39" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="46" t="s">
-        <v>913</v>
-      </c>
-      <c r="B36" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="C36" s="38" t="s">
-        <v>923</v>
-      </c>
-      <c r="D36" s="72" t="s">
-        <v>930</v>
-      </c>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="J36" s="57">
-        <v>45141</v>
-      </c>
-      <c r="K36" s="57"/>
-      <c r="L36" s="57" t="s">
-        <v>591</v>
-      </c>
-      <c r="M36" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="N36" s="58" t="s">
-        <v>8</v>
-      </c>
-      <c r="O36" s="59" t="s">
-        <v>682</v>
-      </c>
-      <c r="P36" s="65"/>
-      <c r="Q36" s="39" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P36" s="62"/>
+      <c r="Q36" s="38"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>30</v>
       </c>
@@ -5325,51 +5289,51 @@
       <c r="C37" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D37" s="77" t="s">
+      <c r="D37" s="67" t="s">
         <v>541</v>
       </c>
-      <c r="E37" s="78"/>
-      <c r="F37" s="78"/>
-      <c r="G37" s="78"/>
-      <c r="H37" s="78"/>
-      <c r="I37" s="78"/>
-      <c r="J37" s="78"/>
-      <c r="K37" s="78"/>
-      <c r="L37" s="78"/>
-      <c r="M37" s="78"/>
-      <c r="N37" s="78"/>
-      <c r="O37" s="78"/>
-      <c r="P37" s="79"/>
-      <c r="Q37" s="44"/>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B38" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C38" s="67" t="s">
+      <c r="E37" s="68"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="68"/>
+      <c r="H37" s="68"/>
+      <c r="I37" s="68"/>
+      <c r="J37" s="68"/>
+      <c r="K37" s="68"/>
+      <c r="L37" s="68"/>
+      <c r="M37" s="68"/>
+      <c r="N37" s="68"/>
+      <c r="O37" s="68"/>
+      <c r="P37" s="69"/>
+      <c r="Q37" s="43"/>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A38" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="74" t="s">
+      <c r="D38" s="70" t="s">
         <v>541</v>
       </c>
-      <c r="E38" s="75"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
-      <c r="J38" s="75"/>
-      <c r="K38" s="75"/>
-      <c r="L38" s="75"/>
-      <c r="M38" s="75"/>
-      <c r="N38" s="75"/>
-      <c r="O38" s="75"/>
-      <c r="P38" s="76"/>
-      <c r="Q38" s="44"/>
-    </row>
-    <row r="39" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="71"/>
+      <c r="M38" s="71"/>
+      <c r="N38" s="71"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="72"/>
+      <c r="Q38" s="43"/>
+    </row>
+    <row r="39" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="33" t="s">
         <v>30</v>
       </c>
@@ -5406,9 +5370,9 @@
         <v>682</v>
       </c>
       <c r="P39" s="12"/>
-      <c r="Q39" s="44"/>
-    </row>
-    <row r="40" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q39" s="43"/>
+    </row>
+    <row r="40" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="33" t="s">
         <v>30</v>
       </c>
@@ -5445,9 +5409,9 @@
         <v>682</v>
       </c>
       <c r="P40" s="12"/>
-      <c r="Q40" s="44"/>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q40" s="43"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>30</v>
       </c>
@@ -5457,51 +5421,51 @@
       <c r="C41" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="77" t="s">
+      <c r="D41" s="67" t="s">
         <v>542</v>
       </c>
-      <c r="E41" s="78"/>
-      <c r="F41" s="78"/>
-      <c r="G41" s="78"/>
-      <c r="H41" s="78"/>
-      <c r="I41" s="78"/>
-      <c r="J41" s="78"/>
-      <c r="K41" s="78"/>
-      <c r="L41" s="78"/>
-      <c r="M41" s="78"/>
-      <c r="N41" s="78"/>
-      <c r="O41" s="78"/>
-      <c r="P41" s="79"/>
-      <c r="Q41" s="44"/>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B42" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="67" t="s">
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
+      <c r="H41" s="68"/>
+      <c r="I41" s="68"/>
+      <c r="J41" s="68"/>
+      <c r="K41" s="68"/>
+      <c r="L41" s="68"/>
+      <c r="M41" s="68"/>
+      <c r="N41" s="68"/>
+      <c r="O41" s="68"/>
+      <c r="P41" s="69"/>
+      <c r="Q41" s="43"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A42" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B42" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="74" t="s">
+      <c r="D42" s="70" t="s">
         <v>543</v>
       </c>
-      <c r="E42" s="75"/>
-      <c r="F42" s="75"/>
-      <c r="G42" s="75"/>
-      <c r="H42" s="75"/>
-      <c r="I42" s="75"/>
-      <c r="J42" s="75"/>
-      <c r="K42" s="75"/>
-      <c r="L42" s="75"/>
-      <c r="M42" s="75"/>
-      <c r="N42" s="75"/>
-      <c r="O42" s="75"/>
-      <c r="P42" s="76"/>
-      <c r="Q42" s="44"/>
-    </row>
-    <row r="43" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="71"/>
+      <c r="L42" s="71"/>
+      <c r="M42" s="71"/>
+      <c r="N42" s="71"/>
+      <c r="O42" s="71"/>
+      <c r="P42" s="72"/>
+      <c r="Q42" s="43"/>
+    </row>
+    <row r="43" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="33" t="s">
         <v>30</v>
       </c>
@@ -5544,9 +5508,9 @@
         <v>682</v>
       </c>
       <c r="P43" s="12"/>
-      <c r="Q43" s="44"/>
-    </row>
-    <row r="44" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q43" s="43"/>
+    </row>
+    <row r="44" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="33" t="s">
         <v>30</v>
       </c>
@@ -5585,9 +5549,9 @@
         <v>682</v>
       </c>
       <c r="P44" s="12"/>
-      <c r="Q44" s="44"/>
-    </row>
-    <row r="45" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q44" s="43"/>
+    </row>
+    <row r="45" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="33" t="s">
         <v>30</v>
       </c>
@@ -5628,9 +5592,9 @@
         <v>682</v>
       </c>
       <c r="P45" s="12"/>
-      <c r="Q45" s="44"/>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q45" s="43"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>30</v>
       </c>
@@ -5640,51 +5604,51 @@
       <c r="C46" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D46" s="77" t="s">
+      <c r="D46" s="67" t="s">
         <v>545</v>
       </c>
-      <c r="E46" s="78"/>
-      <c r="F46" s="78"/>
-      <c r="G46" s="78"/>
-      <c r="H46" s="78"/>
-      <c r="I46" s="78"/>
-      <c r="J46" s="78"/>
-      <c r="K46" s="78"/>
-      <c r="L46" s="78"/>
-      <c r="M46" s="78"/>
-      <c r="N46" s="78"/>
-      <c r="O46" s="78"/>
-      <c r="P46" s="79"/>
-      <c r="Q46" s="44"/>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B47" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C47" s="67" t="s">
+      <c r="E46" s="68"/>
+      <c r="F46" s="68"/>
+      <c r="G46" s="68"/>
+      <c r="H46" s="68"/>
+      <c r="I46" s="68"/>
+      <c r="J46" s="68"/>
+      <c r="K46" s="68"/>
+      <c r="L46" s="68"/>
+      <c r="M46" s="68"/>
+      <c r="N46" s="68"/>
+      <c r="O46" s="68"/>
+      <c r="P46" s="69"/>
+      <c r="Q46" s="43"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A47" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C47" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="74" t="s">
+      <c r="D47" s="70" t="s">
         <v>544</v>
       </c>
-      <c r="E47" s="75"/>
-      <c r="F47" s="75"/>
-      <c r="G47" s="75"/>
-      <c r="H47" s="75"/>
-      <c r="I47" s="75"/>
-      <c r="J47" s="75"/>
-      <c r="K47" s="75"/>
-      <c r="L47" s="75"/>
-      <c r="M47" s="75"/>
-      <c r="N47" s="75"/>
-      <c r="O47" s="75"/>
-      <c r="P47" s="76"/>
-      <c r="Q47" s="44"/>
-    </row>
-    <row r="48" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E47" s="71"/>
+      <c r="F47" s="71"/>
+      <c r="G47" s="71"/>
+      <c r="H47" s="71"/>
+      <c r="I47" s="71"/>
+      <c r="J47" s="71"/>
+      <c r="K47" s="71"/>
+      <c r="L47" s="71"/>
+      <c r="M47" s="71"/>
+      <c r="N47" s="71"/>
+      <c r="O47" s="71"/>
+      <c r="P47" s="72"/>
+      <c r="Q47" s="43"/>
+    </row>
+    <row r="48" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="33" t="s">
         <v>30</v>
       </c>
@@ -5725,9 +5689,9 @@
         <v>682</v>
       </c>
       <c r="P48" s="12"/>
-      <c r="Q48" s="44"/>
-    </row>
-    <row r="49" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q48" s="43"/>
+    </row>
+    <row r="49" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="33" t="s">
         <v>30</v>
       </c>
@@ -5766,9 +5730,9 @@
         <v>682</v>
       </c>
       <c r="P49" s="12"/>
-      <c r="Q49" s="44"/>
-    </row>
-    <row r="50" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q49" s="43"/>
+    </row>
+    <row r="50" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="33" t="s">
         <v>30</v>
       </c>
@@ -5805,9 +5769,9 @@
         <v>682</v>
       </c>
       <c r="P50" s="12"/>
-      <c r="Q50" s="44"/>
-    </row>
-    <row r="51" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q50" s="43"/>
+    </row>
+    <row r="51" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="33" t="s">
         <v>30</v>
       </c>
@@ -5844,9 +5808,9 @@
         <v>682</v>
       </c>
       <c r="P51" s="12"/>
-      <c r="Q51" s="44"/>
-    </row>
-    <row r="52" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q51" s="43"/>
+    </row>
+    <row r="52" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="33" t="s">
         <v>30</v>
       </c>
@@ -5883,9 +5847,9 @@
         <v>682</v>
       </c>
       <c r="P52" s="12"/>
-      <c r="Q52" s="44"/>
-    </row>
-    <row r="53" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q52" s="43"/>
+    </row>
+    <row r="53" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="33" t="s">
         <v>30</v>
       </c>
@@ -5922,9 +5886,9 @@
         <v>682</v>
       </c>
       <c r="P53" s="12"/>
-      <c r="Q53" s="44"/>
-    </row>
-    <row r="54" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q53" s="43"/>
+    </row>
+    <row r="54" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="33" t="s">
         <v>30</v>
       </c>
@@ -5961,9 +5925,9 @@
         <v>682</v>
       </c>
       <c r="P54" s="12"/>
-      <c r="Q54" s="44"/>
-    </row>
-    <row r="55" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q54" s="43"/>
+    </row>
+    <row r="55" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="33" t="s">
         <v>30</v>
       </c>
@@ -6000,9 +5964,9 @@
         <v>682</v>
       </c>
       <c r="P55" s="12"/>
-      <c r="Q55" s="44"/>
-    </row>
-    <row r="56" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q55" s="43"/>
+    </row>
+    <row r="56" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="33" t="s">
         <v>30</v>
       </c>
@@ -6039,9 +6003,9 @@
         <v>682</v>
       </c>
       <c r="P56" s="12"/>
-      <c r="Q56" s="44"/>
-    </row>
-    <row r="57" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q56" s="43"/>
+    </row>
+    <row r="57" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="33" t="s">
         <v>30</v>
       </c>
@@ -6080,9 +6044,9 @@
         <v>682</v>
       </c>
       <c r="P57" s="12"/>
-      <c r="Q57" s="44"/>
-    </row>
-    <row r="58" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q57" s="43"/>
+    </row>
+    <row r="58" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="33" t="s">
         <v>700</v>
       </c>
@@ -6119,9 +6083,9 @@
         <v>682</v>
       </c>
       <c r="P58" s="12"/>
-      <c r="Q58" s="44"/>
-    </row>
-    <row r="59" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q58" s="43"/>
+    </row>
+    <row r="59" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="33" t="s">
         <v>700</v>
       </c>
@@ -6158,9 +6122,9 @@
         <v>682</v>
       </c>
       <c r="P59" s="12"/>
-      <c r="Q59" s="44"/>
-    </row>
-    <row r="60" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q59" s="43"/>
+    </row>
+    <row r="60" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="33" t="s">
         <v>702</v>
       </c>
@@ -6197,9 +6161,9 @@
         <v>682</v>
       </c>
       <c r="P60" s="12"/>
-      <c r="Q60" s="44"/>
-    </row>
-    <row r="61" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q60" s="43"/>
+    </row>
+    <row r="61" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="33" t="s">
         <v>702</v>
       </c>
@@ -6236,9 +6200,9 @@
         <v>682</v>
       </c>
       <c r="P61" s="12"/>
-      <c r="Q61" s="44"/>
-    </row>
-    <row r="62" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q61" s="43"/>
+    </row>
+    <row r="62" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="33" t="s">
         <v>702</v>
       </c>
@@ -6275,9 +6239,9 @@
         <v>682</v>
       </c>
       <c r="P62" s="12"/>
-      <c r="Q62" s="44"/>
-    </row>
-    <row r="63" spans="1:17" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q62" s="43"/>
+    </row>
+    <row r="63" spans="1:17" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="33" t="s">
         <v>848</v>
       </c>
@@ -6287,7 +6251,7 @@
       <c r="C63" s="32" t="s">
         <v>852</v>
       </c>
-      <c r="D63" s="56" t="s">
+      <c r="D63" s="55" t="s">
         <v>855</v>
       </c>
       <c r="E63" s="32" t="s">
@@ -6314,9 +6278,9 @@
         <v>682</v>
       </c>
       <c r="P63" s="12"/>
-      <c r="Q63" s="44"/>
-    </row>
-    <row r="64" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Q63" s="43"/>
+    </row>
+    <row r="64" spans="1:17" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A64" s="33" t="s">
         <v>848</v>
       </c>
@@ -6326,7 +6290,7 @@
       <c r="C64" s="32" t="s">
         <v>853</v>
       </c>
-      <c r="D64" s="56" t="s">
+      <c r="D64" s="55" t="s">
         <v>856</v>
       </c>
       <c r="E64" s="32" t="s">
@@ -6353,9 +6317,9 @@
         <v>682</v>
       </c>
       <c r="P64" s="12"/>
-      <c r="Q64" s="44"/>
-    </row>
-    <row r="65" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Q64" s="43"/>
+    </row>
+    <row r="65" spans="1:17" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A65" s="33" t="s">
         <v>848</v>
       </c>
@@ -6365,7 +6329,7 @@
       <c r="C65" s="32" t="s">
         <v>857</v>
       </c>
-      <c r="D65" s="56" t="s">
+      <c r="D65" s="55" t="s">
         <v>858</v>
       </c>
       <c r="E65" s="32" t="s">
@@ -6392,9 +6356,9 @@
         <v>682</v>
       </c>
       <c r="P65" s="12"/>
-      <c r="Q65" s="44"/>
-    </row>
-    <row r="66" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Q65" s="43"/>
+    </row>
+    <row r="66" spans="1:17" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A66" s="33" t="s">
         <v>848</v>
       </c>
@@ -6404,7 +6368,7 @@
       <c r="C66" s="32" t="s">
         <v>859</v>
       </c>
-      <c r="D66" s="56" t="s">
+      <c r="D66" s="55" t="s">
         <v>860</v>
       </c>
       <c r="E66" s="32" t="s">
@@ -6435,9 +6399,9 @@
         <v>682</v>
       </c>
       <c r="P66" s="12"/>
-      <c r="Q66" s="44"/>
-    </row>
-    <row r="67" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Q66" s="43"/>
+    </row>
+    <row r="67" spans="1:17" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A67" s="33" t="s">
         <v>880</v>
       </c>
@@ -6447,7 +6411,7 @@
       <c r="C67" s="32" t="s">
         <v>881</v>
       </c>
-      <c r="D67" s="56" t="s">
+      <c r="D67" s="55" t="s">
         <v>882</v>
       </c>
       <c r="E67" s="32" t="s">
@@ -6476,36 +6440,36 @@
         <v>682</v>
       </c>
       <c r="P67" s="12"/>
-      <c r="Q67" s="44"/>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A68" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B68" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C68" s="67" t="s">
+      <c r="Q67" s="43"/>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A68" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B68" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="D68" s="74" t="s">
+      <c r="D68" s="70" t="s">
         <v>546</v>
       </c>
-      <c r="E68" s="75"/>
-      <c r="F68" s="75"/>
-      <c r="G68" s="75"/>
-      <c r="H68" s="75"/>
-      <c r="I68" s="75"/>
-      <c r="J68" s="75"/>
-      <c r="K68" s="75"/>
-      <c r="L68" s="75"/>
-      <c r="M68" s="75"/>
-      <c r="N68" s="75"/>
-      <c r="O68" s="75"/>
-      <c r="P68" s="76"/>
-      <c r="Q68" s="44"/>
-    </row>
-    <row r="69" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E68" s="71"/>
+      <c r="F68" s="71"/>
+      <c r="G68" s="71"/>
+      <c r="H68" s="71"/>
+      <c r="I68" s="71"/>
+      <c r="J68" s="71"/>
+      <c r="K68" s="71"/>
+      <c r="L68" s="71"/>
+      <c r="M68" s="71"/>
+      <c r="N68" s="71"/>
+      <c r="O68" s="71"/>
+      <c r="P68" s="72"/>
+      <c r="Q68" s="43"/>
+    </row>
+    <row r="69" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="33" t="s">
         <v>30</v>
       </c>
@@ -6546,9 +6510,9 @@
         <v>682</v>
       </c>
       <c r="P69" s="12"/>
-      <c r="Q69" s="44"/>
-    </row>
-    <row r="70" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q69" s="43"/>
+    </row>
+    <row r="70" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="33" t="s">
         <v>30</v>
       </c>
@@ -6587,9 +6551,9 @@
         <v>682</v>
       </c>
       <c r="P70" s="12"/>
-      <c r="Q70" s="44"/>
-    </row>
-    <row r="71" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q70" s="43"/>
+    </row>
+    <row r="71" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="33" t="s">
         <v>30</v>
       </c>
@@ -6630,9 +6594,9 @@
         <v>682</v>
       </c>
       <c r="P71" s="12"/>
-      <c r="Q71" s="44"/>
-    </row>
-    <row r="72" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Q71" s="43"/>
+    </row>
+    <row r="72" spans="1:17" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A72" s="33" t="s">
         <v>848</v>
       </c>
@@ -6649,7 +6613,7 @@
         <v>6</v>
       </c>
       <c r="F72" s="32"/>
-      <c r="G72" s="42" t="s">
+      <c r="G72" s="41" t="s">
         <v>8</v>
       </c>
       <c r="H72" s="32" t="s">
@@ -6673,9 +6637,9 @@
         <v>682</v>
       </c>
       <c r="P72" s="12"/>
-      <c r="Q72" s="44"/>
-    </row>
-    <row r="73" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q72" s="43"/>
+    </row>
+    <row r="73" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="33" t="s">
         <v>30</v>
       </c>
@@ -6716,36 +6680,36 @@
         <v>682</v>
       </c>
       <c r="P73" s="12"/>
-      <c r="Q73" s="44"/>
-    </row>
-    <row r="74" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q73" s="43"/>
+    </row>
+    <row r="74" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="33" t="s">
         <v>30</v>
       </c>
       <c r="B74" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C74" s="42" t="s">
+      <c r="C74" s="41" t="s">
         <v>67</v>
       </c>
       <c r="D74" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="E74" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F74" s="42"/>
-      <c r="G74" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="H74" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="I74" s="42"/>
-      <c r="J74" s="43">
-        <v>1</v>
-      </c>
-      <c r="K74" s="43"/>
+      <c r="E74" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="F74" s="41"/>
+      <c r="G74" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="H74" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="I74" s="41"/>
+      <c r="J74" s="42">
+        <v>1</v>
+      </c>
+      <c r="K74" s="42"/>
       <c r="L74" s="35" t="s">
         <v>591</v>
       </c>
@@ -6759,9 +6723,9 @@
         <v>682</v>
       </c>
       <c r="P74" s="12"/>
-      <c r="Q74" s="44"/>
-    </row>
-    <row r="75" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q74" s="43"/>
+    </row>
+    <row r="75" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="33" t="s">
         <v>30</v>
       </c>
@@ -6802,9 +6766,9 @@
         <v>682</v>
       </c>
       <c r="P75" s="12"/>
-      <c r="Q75" s="44"/>
-    </row>
-    <row r="76" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q75" s="43"/>
+    </row>
+    <row r="76" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="33" t="s">
         <v>30</v>
       </c>
@@ -6841,9 +6805,9 @@
         <v>682</v>
       </c>
       <c r="P76" s="12"/>
-      <c r="Q76" s="44"/>
-    </row>
-    <row r="77" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q76" s="43"/>
+    </row>
+    <row r="77" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="33" t="s">
         <v>30</v>
       </c>
@@ -6880,9 +6844,9 @@
         <v>682</v>
       </c>
       <c r="P77" s="12"/>
-      <c r="Q77" s="44"/>
-    </row>
-    <row r="78" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q77" s="43"/>
+    </row>
+    <row r="78" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="33" t="s">
         <v>30</v>
       </c>
@@ -6919,9 +6883,9 @@
         <v>682</v>
       </c>
       <c r="P78" s="12"/>
-      <c r="Q78" s="44"/>
-    </row>
-    <row r="79" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q78" s="43"/>
+    </row>
+    <row r="79" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="33" t="s">
         <v>30</v>
       </c>
@@ -6958,9 +6922,9 @@
         <v>682</v>
       </c>
       <c r="P79" s="12"/>
-      <c r="Q79" s="44"/>
-    </row>
-    <row r="80" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q79" s="43"/>
+    </row>
+    <row r="80" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="33" t="s">
         <v>30</v>
       </c>
@@ -7005,9 +6969,9 @@
         <v>682</v>
       </c>
       <c r="P80" s="12"/>
-      <c r="Q80" s="44"/>
-    </row>
-    <row r="81" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q80" s="43"/>
+    </row>
+    <row r="81" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="33" t="s">
         <v>30</v>
       </c>
@@ -7044,9 +7008,9 @@
         <v>682</v>
       </c>
       <c r="P81" s="12"/>
-      <c r="Q81" s="44"/>
-    </row>
-    <row r="82" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q81" s="43"/>
+    </row>
+    <row r="82" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="33" t="s">
         <v>700</v>
       </c>
@@ -7083,9 +7047,9 @@
         <v>682</v>
       </c>
       <c r="P82" s="12"/>
-      <c r="Q82" s="44"/>
-    </row>
-    <row r="83" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q82" s="43"/>
+    </row>
+    <row r="83" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="33" t="s">
         <v>700</v>
       </c>
@@ -7122,9 +7086,9 @@
         <v>682</v>
       </c>
       <c r="P83" s="12"/>
-      <c r="Q83" s="44"/>
-    </row>
-    <row r="84" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q83" s="43"/>
+    </row>
+    <row r="84" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="33" t="s">
         <v>702</v>
       </c>
@@ -7161,9 +7125,9 @@
         <v>682</v>
       </c>
       <c r="P84" s="12"/>
-      <c r="Q84" s="44"/>
-    </row>
-    <row r="85" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q84" s="43"/>
+    </row>
+    <row r="85" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="33" t="s">
         <v>702</v>
       </c>
@@ -7200,9 +7164,9 @@
         <v>682</v>
       </c>
       <c r="P85" s="12"/>
-      <c r="Q85" s="44"/>
-    </row>
-    <row r="86" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q85" s="43"/>
+    </row>
+    <row r="86" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="33" t="s">
         <v>702</v>
       </c>
@@ -7239,9 +7203,9 @@
         <v>682</v>
       </c>
       <c r="P86" s="12"/>
-      <c r="Q86" s="44"/>
-    </row>
-    <row r="87" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q86" s="43"/>
+    </row>
+    <row r="87" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="33" t="s">
         <v>722</v>
       </c>
@@ -7278,9 +7242,9 @@
         <v>682</v>
       </c>
       <c r="P87" s="12"/>
-      <c r="Q87" s="44"/>
-    </row>
-    <row r="88" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q87" s="43"/>
+    </row>
+    <row r="88" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="33" t="s">
         <v>770</v>
       </c>
@@ -7317,9 +7281,9 @@
         <v>682</v>
       </c>
       <c r="P88" s="12"/>
-      <c r="Q88" s="44"/>
-    </row>
-    <row r="89" spans="1:17" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q88" s="43"/>
+    </row>
+    <row r="89" spans="1:17" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="33" t="s">
         <v>865</v>
       </c>
@@ -7358,9 +7322,9 @@
         <v>682</v>
       </c>
       <c r="P89" s="12"/>
-      <c r="Q89" s="44"/>
-    </row>
-    <row r="90" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q89" s="43"/>
+    </row>
+    <row r="90" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="33" t="s">
         <v>700</v>
       </c>
@@ -7397,9 +7361,9 @@
         <v>682</v>
       </c>
       <c r="P90" s="12"/>
-      <c r="Q90" s="44"/>
-    </row>
-    <row r="91" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Q90" s="43"/>
+    </row>
+    <row r="91" spans="1:17" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A91" s="33" t="s">
         <v>880</v>
       </c>
@@ -7409,7 +7373,7 @@
       <c r="C91" s="32" t="s">
         <v>884</v>
       </c>
-      <c r="D91" s="56" t="s">
+      <c r="D91" s="55" t="s">
         <v>883</v>
       </c>
       <c r="E91" s="32" t="s">
@@ -7438,36 +7402,36 @@
         <v>682</v>
       </c>
       <c r="P91" s="12"/>
-      <c r="Q91" s="44"/>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A92" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B92" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C92" s="67" t="s">
+      <c r="Q91" s="43"/>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A92" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B92" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C92" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="D92" s="74" t="s">
+      <c r="D92" s="70" t="s">
         <v>547</v>
       </c>
-      <c r="E92" s="75"/>
-      <c r="F92" s="75"/>
-      <c r="G92" s="75"/>
-      <c r="H92" s="75"/>
-      <c r="I92" s="75"/>
-      <c r="J92" s="75"/>
-      <c r="K92" s="75"/>
-      <c r="L92" s="75"/>
-      <c r="M92" s="75"/>
-      <c r="N92" s="75"/>
-      <c r="O92" s="75"/>
-      <c r="P92" s="76"/>
-      <c r="Q92" s="44"/>
-    </row>
-    <row r="93" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E92" s="71"/>
+      <c r="F92" s="71"/>
+      <c r="G92" s="71"/>
+      <c r="H92" s="71"/>
+      <c r="I92" s="71"/>
+      <c r="J92" s="71"/>
+      <c r="K92" s="71"/>
+      <c r="L92" s="71"/>
+      <c r="M92" s="71"/>
+      <c r="N92" s="71"/>
+      <c r="O92" s="71"/>
+      <c r="P92" s="72"/>
+      <c r="Q92" s="43"/>
+    </row>
+    <row r="93" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="33" t="s">
         <v>30</v>
       </c>
@@ -7506,9 +7470,9 @@
         <v>682</v>
       </c>
       <c r="P93" s="12"/>
-      <c r="Q93" s="44"/>
-    </row>
-    <row r="94" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q93" s="43"/>
+    </row>
+    <row r="94" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="33" t="s">
         <v>30</v>
       </c>
@@ -7545,9 +7509,9 @@
         <v>682</v>
       </c>
       <c r="P94" s="12"/>
-      <c r="Q94" s="44"/>
-    </row>
-    <row r="95" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q94" s="43"/>
+    </row>
+    <row r="95" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="33" t="s">
         <v>30</v>
       </c>
@@ -7584,9 +7548,9 @@
         <v>682</v>
       </c>
       <c r="P95" s="12"/>
-      <c r="Q95" s="44"/>
-    </row>
-    <row r="96" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q95" s="43"/>
+    </row>
+    <row r="96" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="33" t="s">
         <v>30</v>
       </c>
@@ -7625,9 +7589,9 @@
         <v>682</v>
       </c>
       <c r="P96" s="12"/>
-      <c r="Q96" s="44"/>
-    </row>
-    <row r="97" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q96" s="43"/>
+    </row>
+    <row r="97" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="33" t="s">
         <v>30</v>
       </c>
@@ -7664,9 +7628,9 @@
         <v>682</v>
       </c>
       <c r="P97" s="12"/>
-      <c r="Q97" s="44"/>
-    </row>
-    <row r="98" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q97" s="43"/>
+    </row>
+    <row r="98" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="33" t="s">
         <v>30</v>
       </c>
@@ -7703,9 +7667,9 @@
         <v>682</v>
       </c>
       <c r="P98" s="12"/>
-      <c r="Q98" s="44"/>
-    </row>
-    <row r="99" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q98" s="43"/>
+    </row>
+    <row r="99" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="33" t="s">
         <v>30</v>
       </c>
@@ -7742,9 +7706,9 @@
         <v>682</v>
       </c>
       <c r="P99" s="12"/>
-      <c r="Q99" s="44"/>
-    </row>
-    <row r="100" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q99" s="43"/>
+    </row>
+    <row r="100" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="33" t="s">
         <v>30</v>
       </c>
@@ -7783,9 +7747,9 @@
         <v>682</v>
       </c>
       <c r="P100" s="12"/>
-      <c r="Q100" s="44"/>
-    </row>
-    <row r="101" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q100" s="43"/>
+    </row>
+    <row r="101" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="33" t="s">
         <v>30</v>
       </c>
@@ -7822,9 +7786,9 @@
         <v>682</v>
       </c>
       <c r="P101" s="12"/>
-      <c r="Q101" s="44"/>
-    </row>
-    <row r="102" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q101" s="43"/>
+    </row>
+    <row r="102" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="33" t="s">
         <v>30</v>
       </c>
@@ -7863,9 +7827,9 @@
         <v>682</v>
       </c>
       <c r="P102" s="12"/>
-      <c r="Q102" s="44"/>
-    </row>
-    <row r="103" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q102" s="43"/>
+    </row>
+    <row r="103" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="33" t="s">
         <v>700</v>
       </c>
@@ -7902,9 +7866,9 @@
         <v>682</v>
       </c>
       <c r="P103" s="12"/>
-      <c r="Q103" s="44"/>
-    </row>
-    <row r="104" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q103" s="43"/>
+    </row>
+    <row r="104" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="33" t="s">
         <v>700</v>
       </c>
@@ -7941,9 +7905,9 @@
         <v>682</v>
       </c>
       <c r="P104" s="12"/>
-      <c r="Q104" s="44"/>
-    </row>
-    <row r="105" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q104" s="43"/>
+    </row>
+    <row r="105" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="33" t="s">
         <v>702</v>
       </c>
@@ -7980,9 +7944,9 @@
         <v>682</v>
       </c>
       <c r="P105" s="12"/>
-      <c r="Q105" s="44"/>
-    </row>
-    <row r="106" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q105" s="43"/>
+    </row>
+    <row r="106" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="33" t="s">
         <v>702</v>
       </c>
@@ -8019,9 +7983,9 @@
         <v>682</v>
       </c>
       <c r="P106" s="12"/>
-      <c r="Q106" s="44"/>
-    </row>
-    <row r="107" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q106" s="43"/>
+    </row>
+    <row r="107" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="33" t="s">
         <v>702</v>
       </c>
@@ -8058,9 +8022,9 @@
         <v>682</v>
       </c>
       <c r="P107" s="12"/>
-      <c r="Q107" s="44"/>
-    </row>
-    <row r="108" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q107" s="43"/>
+    </row>
+    <row r="108" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="33" t="s">
         <v>796</v>
       </c>
@@ -8097,9 +8061,9 @@
         <v>682</v>
       </c>
       <c r="P108" s="12"/>
-      <c r="Q108" s="44"/>
-    </row>
-    <row r="109" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Q108" s="43"/>
+    </row>
+    <row r="109" spans="1:17" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A109" s="33" t="s">
         <v>880</v>
       </c>
@@ -8109,7 +8073,7 @@
       <c r="C109" s="32" t="s">
         <v>885</v>
       </c>
-      <c r="D109" s="56" t="s">
+      <c r="D109" s="55" t="s">
         <v>886</v>
       </c>
       <c r="E109" s="32" t="s">
@@ -8138,9 +8102,9 @@
         <v>682</v>
       </c>
       <c r="P109" s="12"/>
-      <c r="Q109" s="44"/>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q109" s="43"/>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
         <v>30</v>
       </c>
@@ -8150,51 +8114,51 @@
       <c r="C110" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D110" s="77" t="s">
+      <c r="D110" s="67" t="s">
         <v>548</v>
       </c>
-      <c r="E110" s="78"/>
-      <c r="F110" s="78"/>
-      <c r="G110" s="78"/>
-      <c r="H110" s="78"/>
-      <c r="I110" s="78"/>
-      <c r="J110" s="78"/>
-      <c r="K110" s="78"/>
-      <c r="L110" s="78"/>
-      <c r="M110" s="78"/>
-      <c r="N110" s="78"/>
-      <c r="O110" s="78"/>
-      <c r="P110" s="79"/>
-      <c r="Q110" s="44"/>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A111" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B111" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C111" s="67" t="s">
+      <c r="E110" s="68"/>
+      <c r="F110" s="68"/>
+      <c r="G110" s="68"/>
+      <c r="H110" s="68"/>
+      <c r="I110" s="68"/>
+      <c r="J110" s="68"/>
+      <c r="K110" s="68"/>
+      <c r="L110" s="68"/>
+      <c r="M110" s="68"/>
+      <c r="N110" s="68"/>
+      <c r="O110" s="68"/>
+      <c r="P110" s="69"/>
+      <c r="Q110" s="43"/>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A111" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B111" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C111" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="D111" s="74" t="s">
+      <c r="D111" s="70" t="s">
         <v>548</v>
       </c>
-      <c r="E111" s="75"/>
-      <c r="F111" s="75"/>
-      <c r="G111" s="75"/>
-      <c r="H111" s="75"/>
-      <c r="I111" s="75"/>
-      <c r="J111" s="75"/>
-      <c r="K111" s="75"/>
-      <c r="L111" s="75"/>
-      <c r="M111" s="75"/>
-      <c r="N111" s="75"/>
-      <c r="O111" s="75"/>
-      <c r="P111" s="76"/>
-      <c r="Q111" s="44"/>
-    </row>
-    <row r="112" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E111" s="71"/>
+      <c r="F111" s="71"/>
+      <c r="G111" s="71"/>
+      <c r="H111" s="71"/>
+      <c r="I111" s="71"/>
+      <c r="J111" s="71"/>
+      <c r="K111" s="71"/>
+      <c r="L111" s="71"/>
+      <c r="M111" s="71"/>
+      <c r="N111" s="71"/>
+      <c r="O111" s="71"/>
+      <c r="P111" s="72"/>
+      <c r="Q111" s="43"/>
+    </row>
+    <row r="112" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="33" t="s">
         <v>30</v>
       </c>
@@ -8239,9 +8203,9 @@
         <v>682</v>
       </c>
       <c r="P112" s="12"/>
-      <c r="Q112" s="44"/>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q112" s="43"/>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
         <v>30</v>
       </c>
@@ -8251,51 +8215,51 @@
       <c r="C113" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D113" s="77" t="s">
+      <c r="D113" s="67" t="s">
         <v>549</v>
       </c>
-      <c r="E113" s="78"/>
-      <c r="F113" s="78"/>
-      <c r="G113" s="78"/>
-      <c r="H113" s="78"/>
-      <c r="I113" s="78"/>
-      <c r="J113" s="78"/>
-      <c r="K113" s="78"/>
-      <c r="L113" s="78"/>
-      <c r="M113" s="78"/>
-      <c r="N113" s="78"/>
-      <c r="O113" s="78"/>
-      <c r="P113" s="79"/>
-      <c r="Q113" s="44"/>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A114" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B114" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C114" s="67" t="s">
+      <c r="E113" s="68"/>
+      <c r="F113" s="68"/>
+      <c r="G113" s="68"/>
+      <c r="H113" s="68"/>
+      <c r="I113" s="68"/>
+      <c r="J113" s="68"/>
+      <c r="K113" s="68"/>
+      <c r="L113" s="68"/>
+      <c r="M113" s="68"/>
+      <c r="N113" s="68"/>
+      <c r="O113" s="68"/>
+      <c r="P113" s="69"/>
+      <c r="Q113" s="43"/>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A114" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B114" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C114" s="64" t="s">
         <v>110</v>
       </c>
-      <c r="D114" s="74" t="s">
+      <c r="D114" s="70" t="s">
         <v>549</v>
       </c>
-      <c r="E114" s="75"/>
-      <c r="F114" s="75"/>
-      <c r="G114" s="75"/>
-      <c r="H114" s="75"/>
-      <c r="I114" s="75"/>
-      <c r="J114" s="75"/>
-      <c r="K114" s="75"/>
-      <c r="L114" s="75"/>
-      <c r="M114" s="75"/>
-      <c r="N114" s="75"/>
-      <c r="O114" s="75"/>
-      <c r="P114" s="76"/>
-      <c r="Q114" s="44"/>
-    </row>
-    <row r="115" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E114" s="71"/>
+      <c r="F114" s="71"/>
+      <c r="G114" s="71"/>
+      <c r="H114" s="71"/>
+      <c r="I114" s="71"/>
+      <c r="J114" s="71"/>
+      <c r="K114" s="71"/>
+      <c r="L114" s="71"/>
+      <c r="M114" s="71"/>
+      <c r="N114" s="71"/>
+      <c r="O114" s="71"/>
+      <c r="P114" s="72"/>
+      <c r="Q114" s="43"/>
+    </row>
+    <row r="115" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="33" t="s">
         <v>30</v>
       </c>
@@ -8334,9 +8298,9 @@
         <v>682</v>
       </c>
       <c r="P115" s="12"/>
-      <c r="Q115" s="44"/>
-    </row>
-    <row r="116" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q115" s="43"/>
+    </row>
+    <row r="116" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="33" t="s">
         <v>30</v>
       </c>
@@ -8377,9 +8341,9 @@
         <v>682</v>
       </c>
       <c r="P116" s="12"/>
-      <c r="Q116" s="44"/>
-    </row>
-    <row r="117" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q116" s="43"/>
+    </row>
+    <row r="117" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="33" t="s">
         <v>30</v>
       </c>
@@ -8416,9 +8380,9 @@
         <v>682</v>
       </c>
       <c r="P117" s="12"/>
-      <c r="Q117" s="44"/>
-    </row>
-    <row r="118" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q117" s="43"/>
+    </row>
+    <row r="118" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="33" t="s">
         <v>30</v>
       </c>
@@ -8457,9 +8421,9 @@
         <v>682</v>
       </c>
       <c r="P118" s="12"/>
-      <c r="Q118" s="44"/>
-    </row>
-    <row r="119" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q118" s="43"/>
+    </row>
+    <row r="119" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="33" t="s">
         <v>30</v>
       </c>
@@ -8496,9 +8460,9 @@
         <v>682</v>
       </c>
       <c r="P119" s="12"/>
-      <c r="Q119" s="44"/>
-    </row>
-    <row r="120" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q119" s="43"/>
+    </row>
+    <row r="120" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="33" t="s">
         <v>30</v>
       </c>
@@ -8539,9 +8503,9 @@
         <v>682</v>
       </c>
       <c r="P120" s="12"/>
-      <c r="Q120" s="44"/>
-    </row>
-    <row r="121" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q120" s="43"/>
+    </row>
+    <row r="121" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="33" t="s">
         <v>867</v>
       </c>
@@ -8578,9 +8542,9 @@
         <v>682</v>
       </c>
       <c r="P121" s="12"/>
-      <c r="Q121" s="44"/>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q121" s="43"/>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A122" s="3" t="s">
         <v>30</v>
       </c>
@@ -8590,51 +8554,51 @@
       <c r="C122" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D122" s="77" t="s">
+      <c r="D122" s="67" t="s">
         <v>550</v>
       </c>
-      <c r="E122" s="78"/>
-      <c r="F122" s="78"/>
-      <c r="G122" s="78"/>
-      <c r="H122" s="78"/>
-      <c r="I122" s="78"/>
-      <c r="J122" s="78"/>
-      <c r="K122" s="78"/>
-      <c r="L122" s="78"/>
-      <c r="M122" s="78"/>
-      <c r="N122" s="78"/>
-      <c r="O122" s="78"/>
-      <c r="P122" s="79"/>
-      <c r="Q122" s="44"/>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A123" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B123" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C123" s="67" t="s">
+      <c r="E122" s="68"/>
+      <c r="F122" s="68"/>
+      <c r="G122" s="68"/>
+      <c r="H122" s="68"/>
+      <c r="I122" s="68"/>
+      <c r="J122" s="68"/>
+      <c r="K122" s="68"/>
+      <c r="L122" s="68"/>
+      <c r="M122" s="68"/>
+      <c r="N122" s="68"/>
+      <c r="O122" s="68"/>
+      <c r="P122" s="69"/>
+      <c r="Q122" s="43"/>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A123" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B123" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C123" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="D123" s="74" t="s">
+      <c r="D123" s="70" t="s">
         <v>551</v>
       </c>
-      <c r="E123" s="75"/>
-      <c r="F123" s="75"/>
-      <c r="G123" s="75"/>
-      <c r="H123" s="75"/>
-      <c r="I123" s="75"/>
-      <c r="J123" s="75"/>
-      <c r="K123" s="75"/>
-      <c r="L123" s="75"/>
-      <c r="M123" s="75"/>
-      <c r="N123" s="75"/>
-      <c r="O123" s="75"/>
-      <c r="P123" s="76"/>
-      <c r="Q123" s="44"/>
-    </row>
-    <row r="124" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E123" s="71"/>
+      <c r="F123" s="71"/>
+      <c r="G123" s="71"/>
+      <c r="H123" s="71"/>
+      <c r="I123" s="71"/>
+      <c r="J123" s="71"/>
+      <c r="K123" s="71"/>
+      <c r="L123" s="71"/>
+      <c r="M123" s="71"/>
+      <c r="N123" s="71"/>
+      <c r="O123" s="71"/>
+      <c r="P123" s="72"/>
+      <c r="Q123" s="43"/>
+    </row>
+    <row r="124" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="33" t="s">
         <v>30</v>
       </c>
@@ -8675,9 +8639,9 @@
         <v>591</v>
       </c>
       <c r="P124" s="12"/>
-      <c r="Q124" s="44"/>
-    </row>
-    <row r="125" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q124" s="43"/>
+    </row>
+    <row r="125" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="33" t="s">
         <v>30</v>
       </c>
@@ -8718,9 +8682,9 @@
         <v>591</v>
       </c>
       <c r="P125" s="12"/>
-      <c r="Q125" s="44"/>
-    </row>
-    <row r="126" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q125" s="43"/>
+    </row>
+    <row r="126" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="33" t="s">
         <v>30</v>
       </c>
@@ -8757,9 +8721,9 @@
         <v>591</v>
       </c>
       <c r="P126" s="12"/>
-      <c r="Q126" s="44"/>
-    </row>
-    <row r="127" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q126" s="43"/>
+    </row>
+    <row r="127" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="33" t="s">
         <v>30</v>
       </c>
@@ -8796,9 +8760,9 @@
         <v>591</v>
       </c>
       <c r="P127" s="12"/>
-      <c r="Q127" s="44"/>
-    </row>
-    <row r="128" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q127" s="43"/>
+    </row>
+    <row r="128" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="33" t="s">
         <v>30</v>
       </c>
@@ -8835,9 +8799,9 @@
         <v>591</v>
       </c>
       <c r="P128" s="12"/>
-      <c r="Q128" s="44"/>
-    </row>
-    <row r="129" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q128" s="43"/>
+    </row>
+    <row r="129" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="33" t="s">
         <v>30</v>
       </c>
@@ -8874,9 +8838,9 @@
         <v>591</v>
       </c>
       <c r="P129" s="12"/>
-      <c r="Q129" s="44"/>
-    </row>
-    <row r="130" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q129" s="43"/>
+    </row>
+    <row r="130" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="33" t="s">
         <v>30</v>
       </c>
@@ -8913,9 +8877,9 @@
         <v>591</v>
       </c>
       <c r="P130" s="12"/>
-      <c r="Q130" s="44"/>
-    </row>
-    <row r="131" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q130" s="43"/>
+    </row>
+    <row r="131" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="33" t="s">
         <v>30</v>
       </c>
@@ -8952,9 +8916,9 @@
         <v>591</v>
       </c>
       <c r="P131" s="12"/>
-      <c r="Q131" s="44"/>
-    </row>
-    <row r="132" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q131" s="43"/>
+    </row>
+    <row r="132" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="33" t="s">
         <v>722</v>
       </c>
@@ -8991,9 +8955,9 @@
         <v>591</v>
       </c>
       <c r="P132" s="12"/>
-      <c r="Q132" s="44"/>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q132" s="43"/>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
         <v>30</v>
       </c>
@@ -9003,51 +8967,51 @@
       <c r="C133" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D133" s="77" t="s">
+      <c r="D133" s="67" t="s">
         <v>552</v>
       </c>
-      <c r="E133" s="78"/>
-      <c r="F133" s="78"/>
-      <c r="G133" s="78"/>
-      <c r="H133" s="78"/>
-      <c r="I133" s="78"/>
-      <c r="J133" s="78"/>
-      <c r="K133" s="78"/>
-      <c r="L133" s="78"/>
-      <c r="M133" s="78"/>
-      <c r="N133" s="78"/>
-      <c r="O133" s="78"/>
-      <c r="P133" s="79"/>
-      <c r="Q133" s="44"/>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A134" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B134" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C134" s="67" t="s">
+      <c r="E133" s="68"/>
+      <c r="F133" s="68"/>
+      <c r="G133" s="68"/>
+      <c r="H133" s="68"/>
+      <c r="I133" s="68"/>
+      <c r="J133" s="68"/>
+      <c r="K133" s="68"/>
+      <c r="L133" s="68"/>
+      <c r="M133" s="68"/>
+      <c r="N133" s="68"/>
+      <c r="O133" s="68"/>
+      <c r="P133" s="69"/>
+      <c r="Q133" s="43"/>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A134" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B134" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C134" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="D134" s="74" t="s">
+      <c r="D134" s="70" t="s">
         <v>553</v>
       </c>
-      <c r="E134" s="75"/>
-      <c r="F134" s="75"/>
-      <c r="G134" s="75"/>
-      <c r="H134" s="75"/>
-      <c r="I134" s="75"/>
-      <c r="J134" s="75"/>
-      <c r="K134" s="75"/>
-      <c r="L134" s="75"/>
-      <c r="M134" s="75"/>
-      <c r="N134" s="75"/>
-      <c r="O134" s="75"/>
-      <c r="P134" s="76"/>
-      <c r="Q134" s="44"/>
-    </row>
-    <row r="135" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E134" s="71"/>
+      <c r="F134" s="71"/>
+      <c r="G134" s="71"/>
+      <c r="H134" s="71"/>
+      <c r="I134" s="71"/>
+      <c r="J134" s="71"/>
+      <c r="K134" s="71"/>
+      <c r="L134" s="71"/>
+      <c r="M134" s="71"/>
+      <c r="N134" s="71"/>
+      <c r="O134" s="71"/>
+      <c r="P134" s="72"/>
+      <c r="Q134" s="43"/>
+    </row>
+    <row r="135" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="33" t="s">
         <v>30</v>
       </c>
@@ -9088,9 +9052,9 @@
         <v>682</v>
       </c>
       <c r="P135" s="12"/>
-      <c r="Q135" s="44"/>
-    </row>
-    <row r="136" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q135" s="43"/>
+    </row>
+    <row r="136" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="33" t="s">
         <v>30</v>
       </c>
@@ -9129,9 +9093,9 @@
         <v>682</v>
       </c>
       <c r="P136" s="12"/>
-      <c r="Q136" s="44"/>
-    </row>
-    <row r="137" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q136" s="43"/>
+    </row>
+    <row r="137" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="33" t="s">
         <v>30</v>
       </c>
@@ -9168,9 +9132,9 @@
         <v>682</v>
       </c>
       <c r="P137" s="12"/>
-      <c r="Q137" s="44"/>
-    </row>
-    <row r="138" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q137" s="43"/>
+    </row>
+    <row r="138" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="33" t="s">
         <v>30</v>
       </c>
@@ -9209,9 +9173,9 @@
         <v>682</v>
       </c>
       <c r="P138" s="12"/>
-      <c r="Q138" s="44"/>
-    </row>
-    <row r="139" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q138" s="43"/>
+    </row>
+    <row r="139" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="33" t="s">
         <v>30</v>
       </c>
@@ -9250,9 +9214,9 @@
         <v>682</v>
       </c>
       <c r="P139" s="12"/>
-      <c r="Q139" s="44"/>
-    </row>
-    <row r="140" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q139" s="43"/>
+    </row>
+    <row r="140" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="33" t="s">
         <v>30</v>
       </c>
@@ -9291,9 +9255,9 @@
         <v>682</v>
       </c>
       <c r="P140" s="12"/>
-      <c r="Q140" s="44"/>
-    </row>
-    <row r="141" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q140" s="43"/>
+    </row>
+    <row r="141" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="33" t="s">
         <v>30</v>
       </c>
@@ -9330,9 +9294,9 @@
         <v>682</v>
       </c>
       <c r="P141" s="12"/>
-      <c r="Q141" s="44"/>
-    </row>
-    <row r="142" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q141" s="43"/>
+    </row>
+    <row r="142" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="33" t="s">
         <v>30</v>
       </c>
@@ -9369,9 +9333,9 @@
         <v>682</v>
       </c>
       <c r="P142" s="12"/>
-      <c r="Q142" s="44"/>
-    </row>
-    <row r="143" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q142" s="43"/>
+    </row>
+    <row r="143" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="33" t="s">
         <v>30</v>
       </c>
@@ -9408,9 +9372,9 @@
         <v>682</v>
       </c>
       <c r="P143" s="12"/>
-      <c r="Q143" s="44"/>
-    </row>
-    <row r="144" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q143" s="43"/>
+    </row>
+    <row r="144" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="33" t="s">
         <v>30</v>
       </c>
@@ -9447,9 +9411,9 @@
         <v>682</v>
       </c>
       <c r="P144" s="12"/>
-      <c r="Q144" s="44"/>
-    </row>
-    <row r="145" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q144" s="43"/>
+    </row>
+    <row r="145" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="33" t="s">
         <v>30</v>
       </c>
@@ -9488,9 +9452,9 @@
         <v>682</v>
       </c>
       <c r="P145" s="12"/>
-      <c r="Q145" s="44"/>
-    </row>
-    <row r="146" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q145" s="43"/>
+    </row>
+    <row r="146" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="33" t="s">
         <v>30</v>
       </c>
@@ -9529,9 +9493,9 @@
         <v>682</v>
       </c>
       <c r="P146" s="12"/>
-      <c r="Q146" s="44"/>
-    </row>
-    <row r="147" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q146" s="43"/>
+    </row>
+    <row r="147" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="33" t="s">
         <v>30</v>
       </c>
@@ -9568,9 +9532,9 @@
         <v>682</v>
       </c>
       <c r="P147" s="12"/>
-      <c r="Q147" s="44"/>
-    </row>
-    <row r="148" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q147" s="43"/>
+    </row>
+    <row r="148" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="33" t="s">
         <v>30</v>
       </c>
@@ -9607,9 +9571,9 @@
         <v>682</v>
       </c>
       <c r="P148" s="12"/>
-      <c r="Q148" s="44"/>
-    </row>
-    <row r="149" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q148" s="43"/>
+    </row>
+    <row r="149" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="33" t="s">
         <v>30</v>
       </c>
@@ -9646,9 +9610,9 @@
         <v>682</v>
       </c>
       <c r="P149" s="12"/>
-      <c r="Q149" s="44"/>
-    </row>
-    <row r="150" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q149" s="43"/>
+    </row>
+    <row r="150" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="33" t="s">
         <v>30</v>
       </c>
@@ -9685,9 +9649,9 @@
         <v>682</v>
       </c>
       <c r="P150" s="12"/>
-      <c r="Q150" s="44"/>
-    </row>
-    <row r="151" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q150" s="43"/>
+    </row>
+    <row r="151" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="33" t="s">
         <v>30</v>
       </c>
@@ -9724,9 +9688,9 @@
         <v>682</v>
       </c>
       <c r="P151" s="12"/>
-      <c r="Q151" s="44"/>
-    </row>
-    <row r="152" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q151" s="43"/>
+    </row>
+    <row r="152" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="33" t="s">
         <v>30</v>
       </c>
@@ -9765,9 +9729,9 @@
         <v>682</v>
       </c>
       <c r="P152" s="12"/>
-      <c r="Q152" s="44"/>
-    </row>
-    <row r="153" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q152" s="43"/>
+    </row>
+    <row r="153" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="33" t="s">
         <v>30</v>
       </c>
@@ -9806,9 +9770,9 @@
         <v>682</v>
       </c>
       <c r="P153" s="12"/>
-      <c r="Q153" s="44"/>
-    </row>
-    <row r="154" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q153" s="43"/>
+    </row>
+    <row r="154" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="33" t="s">
         <v>765</v>
       </c>
@@ -9847,9 +9811,9 @@
         <v>682</v>
       </c>
       <c r="P154" s="12"/>
-      <c r="Q154" s="44"/>
-    </row>
-    <row r="155" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q154" s="43"/>
+    </row>
+    <row r="155" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="33" t="s">
         <v>30</v>
       </c>
@@ -9888,9 +9852,9 @@
         <v>682</v>
       </c>
       <c r="P155" s="12"/>
-      <c r="Q155" s="44"/>
-    </row>
-    <row r="156" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q155" s="43"/>
+    </row>
+    <row r="156" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="33" t="s">
         <v>30</v>
       </c>
@@ -9929,9 +9893,9 @@
         <v>682</v>
       </c>
       <c r="P156" s="12"/>
-      <c r="Q156" s="44"/>
-    </row>
-    <row r="157" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q156" s="43"/>
+    </row>
+    <row r="157" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="33" t="s">
         <v>30</v>
       </c>
@@ -9970,9 +9934,9 @@
         <v>682</v>
       </c>
       <c r="P157" s="12"/>
-      <c r="Q157" s="44"/>
-    </row>
-    <row r="158" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q157" s="43"/>
+    </row>
+    <row r="158" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="33" t="s">
         <v>30</v>
       </c>
@@ -10011,9 +9975,9 @@
         <v>682</v>
       </c>
       <c r="P158" s="12"/>
-      <c r="Q158" s="44"/>
-    </row>
-    <row r="159" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q158" s="43"/>
+    </row>
+    <row r="159" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="33" t="s">
         <v>30</v>
       </c>
@@ -10052,9 +10016,9 @@
         <v>682</v>
       </c>
       <c r="P159" s="12"/>
-      <c r="Q159" s="44"/>
-    </row>
-    <row r="160" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q159" s="43"/>
+    </row>
+    <row r="160" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="33" t="s">
         <v>30</v>
       </c>
@@ -10093,9 +10057,9 @@
         <v>682</v>
       </c>
       <c r="P160" s="12"/>
-      <c r="Q160" s="44"/>
-    </row>
-    <row r="161" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q160" s="43"/>
+    </row>
+    <row r="161" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="33" t="s">
         <v>30</v>
       </c>
@@ -10134,9 +10098,9 @@
         <v>682</v>
       </c>
       <c r="P161" s="12"/>
-      <c r="Q161" s="44"/>
-    </row>
-    <row r="162" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q161" s="43"/>
+    </row>
+    <row r="162" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="33" t="s">
         <v>30</v>
       </c>
@@ -10173,9 +10137,9 @@
         <v>682</v>
       </c>
       <c r="P162" s="12"/>
-      <c r="Q162" s="44"/>
-    </row>
-    <row r="163" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q162" s="43"/>
+    </row>
+    <row r="163" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="33" t="s">
         <v>30</v>
       </c>
@@ -10212,9 +10176,9 @@
         <v>682</v>
       </c>
       <c r="P163" s="12"/>
-      <c r="Q163" s="44"/>
-    </row>
-    <row r="164" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q163" s="43"/>
+    </row>
+    <row r="164" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="33" t="s">
         <v>30</v>
       </c>
@@ -10251,9 +10215,9 @@
         <v>682</v>
       </c>
       <c r="P164" s="12"/>
-      <c r="Q164" s="44"/>
-    </row>
-    <row r="165" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q164" s="43"/>
+    </row>
+    <row r="165" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="33" t="s">
         <v>30</v>
       </c>
@@ -10290,9 +10254,9 @@
         <v>682</v>
       </c>
       <c r="P165" s="12"/>
-      <c r="Q165" s="44"/>
-    </row>
-    <row r="166" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q165" s="43"/>
+    </row>
+    <row r="166" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="33" t="s">
         <v>30</v>
       </c>
@@ -10331,9 +10295,9 @@
         <v>682</v>
       </c>
       <c r="P166" s="12"/>
-      <c r="Q166" s="44"/>
-    </row>
-    <row r="167" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q166" s="43"/>
+    </row>
+    <row r="167" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="33" t="s">
         <v>780</v>
       </c>
@@ -10370,9 +10334,9 @@
         <v>682</v>
       </c>
       <c r="P167" s="12"/>
-      <c r="Q167" s="44"/>
-    </row>
-    <row r="168" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q167" s="43"/>
+    </row>
+    <row r="168" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="33" t="s">
         <v>30</v>
       </c>
@@ -10411,9 +10375,9 @@
         <v>682</v>
       </c>
       <c r="P168" s="12"/>
-      <c r="Q168" s="44"/>
-    </row>
-    <row r="169" spans="1:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q168" s="43"/>
+    </row>
+    <row r="169" spans="1:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="33" t="s">
         <v>30</v>
       </c>
@@ -10452,9 +10416,9 @@
         <v>682</v>
       </c>
       <c r="P169" s="12"/>
-      <c r="Q169" s="44"/>
-    </row>
-    <row r="170" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Q169" s="43"/>
+    </row>
+    <row r="170" spans="1:17" ht="25" x14ac:dyDescent="0.35">
       <c r="A170" s="33" t="s">
         <v>780</v>
       </c>
@@ -10491,9 +10455,9 @@
         <v>682</v>
       </c>
       <c r="P170" s="12"/>
-      <c r="Q170" s="44"/>
-    </row>
-    <row r="171" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Q170" s="43"/>
+    </row>
+    <row r="171" spans="1:17" ht="25" x14ac:dyDescent="0.35">
       <c r="A171" s="33" t="s">
         <v>780</v>
       </c>
@@ -10532,9 +10496,9 @@
         <v>682</v>
       </c>
       <c r="P171" s="12"/>
-      <c r="Q171" s="44"/>
-    </row>
-    <row r="172" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q171" s="43"/>
+    </row>
+    <row r="172" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="33" t="s">
         <v>780</v>
       </c>
@@ -10571,9 +10535,9 @@
         <v>682</v>
       </c>
       <c r="P172" s="12"/>
-      <c r="Q172" s="44"/>
-    </row>
-    <row r="173" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Q172" s="43"/>
+    </row>
+    <row r="173" spans="1:17" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A173" s="33" t="s">
         <v>840</v>
       </c>
@@ -10612,9 +10576,9 @@
         <v>682</v>
       </c>
       <c r="P173" s="12"/>
-      <c r="Q173" s="44"/>
-    </row>
-    <row r="174" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Q173" s="43"/>
+    </row>
+    <row r="174" spans="1:17" ht="25" x14ac:dyDescent="0.35">
       <c r="A174" s="33" t="s">
         <v>840</v>
       </c>
@@ -10651,9 +10615,9 @@
         <v>682</v>
       </c>
       <c r="P174" s="12"/>
-      <c r="Q174" s="44"/>
-    </row>
-    <row r="175" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q174" s="43"/>
+    </row>
+    <row r="175" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="33" t="s">
         <v>840</v>
       </c>
@@ -10690,36 +10654,36 @@
         <v>682</v>
       </c>
       <c r="P175" s="12"/>
-      <c r="Q175" s="44"/>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A176" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B176" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C176" s="67" t="s">
+      <c r="Q175" s="43"/>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A176" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B176" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C176" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="D176" s="74" t="s">
+      <c r="D176" s="70" t="s">
         <v>554</v>
       </c>
-      <c r="E176" s="75"/>
-      <c r="F176" s="75"/>
-      <c r="G176" s="75"/>
-      <c r="H176" s="75"/>
-      <c r="I176" s="75"/>
-      <c r="J176" s="75"/>
-      <c r="K176" s="75"/>
-      <c r="L176" s="75"/>
-      <c r="M176" s="75"/>
-      <c r="N176" s="75"/>
-      <c r="O176" s="75"/>
-      <c r="P176" s="76"/>
-      <c r="Q176" s="44"/>
-    </row>
-    <row r="177" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E176" s="71"/>
+      <c r="F176" s="71"/>
+      <c r="G176" s="71"/>
+      <c r="H176" s="71"/>
+      <c r="I176" s="71"/>
+      <c r="J176" s="71"/>
+      <c r="K176" s="71"/>
+      <c r="L176" s="71"/>
+      <c r="M176" s="71"/>
+      <c r="N176" s="71"/>
+      <c r="O176" s="71"/>
+      <c r="P176" s="72"/>
+      <c r="Q176" s="43"/>
+    </row>
+    <row r="177" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="33" t="s">
         <v>30</v>
       </c>
@@ -10758,9 +10722,9 @@
         <v>682</v>
       </c>
       <c r="P177" s="12"/>
-      <c r="Q177" s="44"/>
-    </row>
-    <row r="178" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q177" s="43"/>
+    </row>
+    <row r="178" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="33" t="s">
         <v>30</v>
       </c>
@@ -10799,9 +10763,9 @@
         <v>682</v>
       </c>
       <c r="P178" s="12"/>
-      <c r="Q178" s="44"/>
-    </row>
-    <row r="179" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q178" s="43"/>
+    </row>
+    <row r="179" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="33" t="s">
         <v>30</v>
       </c>
@@ -10838,9 +10802,9 @@
         <v>682</v>
       </c>
       <c r="P179" s="12"/>
-      <c r="Q179" s="44"/>
-    </row>
-    <row r="180" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q179" s="43"/>
+    </row>
+    <row r="180" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="33" t="s">
         <v>30</v>
       </c>
@@ -10877,9 +10841,9 @@
         <v>682</v>
       </c>
       <c r="P180" s="12"/>
-      <c r="Q180" s="44"/>
-    </row>
-    <row r="181" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q180" s="43"/>
+    </row>
+    <row r="181" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="33" t="s">
         <v>30</v>
       </c>
@@ -10916,9 +10880,9 @@
         <v>682</v>
       </c>
       <c r="P181" s="12"/>
-      <c r="Q181" s="44"/>
-    </row>
-    <row r="182" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q181" s="43"/>
+    </row>
+    <row r="182" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="33" t="s">
         <v>30</v>
       </c>
@@ -10955,9 +10919,9 @@
         <v>682</v>
       </c>
       <c r="P182" s="12"/>
-      <c r="Q182" s="44"/>
-    </row>
-    <row r="183" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q182" s="43"/>
+    </row>
+    <row r="183" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="33" t="s">
         <v>30</v>
       </c>
@@ -10996,9 +10960,9 @@
         <v>682</v>
       </c>
       <c r="P183" s="12"/>
-      <c r="Q183" s="44"/>
-    </row>
-    <row r="184" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q183" s="43"/>
+    </row>
+    <row r="184" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="33" t="s">
         <v>30</v>
       </c>
@@ -11035,9 +10999,9 @@
         <v>682</v>
       </c>
       <c r="P184" s="12"/>
-      <c r="Q184" s="44"/>
-    </row>
-    <row r="185" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q184" s="43"/>
+    </row>
+    <row r="185" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="33" t="s">
         <v>30</v>
       </c>
@@ -11074,9 +11038,9 @@
         <v>682</v>
       </c>
       <c r="P185" s="12"/>
-      <c r="Q185" s="44"/>
-    </row>
-    <row r="186" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q185" s="43"/>
+    </row>
+    <row r="186" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="33" t="s">
         <v>30</v>
       </c>
@@ -11113,9 +11077,9 @@
         <v>682</v>
       </c>
       <c r="P186" s="12"/>
-      <c r="Q186" s="44"/>
-    </row>
-    <row r="187" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q186" s="43"/>
+    </row>
+    <row r="187" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="33" t="s">
         <v>700</v>
       </c>
@@ -11154,9 +11118,9 @@
         <v>682</v>
       </c>
       <c r="P187" s="12"/>
-      <c r="Q187" s="44"/>
-    </row>
-    <row r="188" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q187" s="43"/>
+    </row>
+    <row r="188" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="33" t="s">
         <v>700</v>
       </c>
@@ -11193,9 +11157,9 @@
         <v>682</v>
       </c>
       <c r="P188" s="12"/>
-      <c r="Q188" s="44"/>
-    </row>
-    <row r="189" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q188" s="43"/>
+    </row>
+    <row r="189" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="33" t="s">
         <v>722</v>
       </c>
@@ -11232,36 +11196,36 @@
         <v>682</v>
       </c>
       <c r="P189" s="12"/>
-      <c r="Q189" s="44"/>
-    </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A190" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B190" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C190" s="67" t="s">
+      <c r="Q189" s="43"/>
+    </row>
+    <row r="190" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A190" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B190" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C190" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="D190" s="74" t="s">
+      <c r="D190" s="70" t="s">
         <v>555</v>
       </c>
-      <c r="E190" s="75"/>
-      <c r="F190" s="75"/>
-      <c r="G190" s="75"/>
-      <c r="H190" s="75"/>
-      <c r="I190" s="75"/>
-      <c r="J190" s="75"/>
-      <c r="K190" s="75"/>
-      <c r="L190" s="75"/>
-      <c r="M190" s="75"/>
-      <c r="N190" s="75"/>
-      <c r="O190" s="75"/>
-      <c r="P190" s="76"/>
-      <c r="Q190" s="44"/>
-    </row>
-    <row r="191" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E190" s="71"/>
+      <c r="F190" s="71"/>
+      <c r="G190" s="71"/>
+      <c r="H190" s="71"/>
+      <c r="I190" s="71"/>
+      <c r="J190" s="71"/>
+      <c r="K190" s="71"/>
+      <c r="L190" s="71"/>
+      <c r="M190" s="71"/>
+      <c r="N190" s="71"/>
+      <c r="O190" s="71"/>
+      <c r="P190" s="72"/>
+      <c r="Q190" s="43"/>
+    </row>
+    <row r="191" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="33" t="s">
         <v>30</v>
       </c>
@@ -11300,9 +11264,9 @@
         <v>682</v>
       </c>
       <c r="P191" s="12"/>
-      <c r="Q191" s="44"/>
-    </row>
-    <row r="192" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q191" s="43"/>
+    </row>
+    <row r="192" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="33" t="s">
         <v>30</v>
       </c>
@@ -11341,9 +11305,9 @@
         <v>682</v>
       </c>
       <c r="P192" s="12"/>
-      <c r="Q192" s="44"/>
-    </row>
-    <row r="193" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q192" s="43"/>
+    </row>
+    <row r="193" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="33" t="s">
         <v>30</v>
       </c>
@@ -11380,9 +11344,9 @@
         <v>682</v>
       </c>
       <c r="P193" s="12"/>
-      <c r="Q193" s="44"/>
-    </row>
-    <row r="194" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q193" s="43"/>
+    </row>
+    <row r="194" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="33" t="s">
         <v>30</v>
       </c>
@@ -11419,9 +11383,9 @@
         <v>682</v>
       </c>
       <c r="P194" s="12"/>
-      <c r="Q194" s="44"/>
-    </row>
-    <row r="195" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q194" s="43"/>
+    </row>
+    <row r="195" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="33" t="s">
         <v>30</v>
       </c>
@@ -11458,9 +11422,9 @@
         <v>682</v>
       </c>
       <c r="P195" s="12"/>
-      <c r="Q195" s="44"/>
-    </row>
-    <row r="196" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q195" s="43"/>
+    </row>
+    <row r="196" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="33" t="s">
         <v>30</v>
       </c>
@@ -11497,9 +11461,9 @@
         <v>682</v>
       </c>
       <c r="P196" s="12"/>
-      <c r="Q196" s="44"/>
-    </row>
-    <row r="197" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q196" s="43"/>
+    </row>
+    <row r="197" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="33" t="s">
         <v>30</v>
       </c>
@@ -11538,9 +11502,9 @@
         <v>682</v>
       </c>
       <c r="P197" s="12"/>
-      <c r="Q197" s="44"/>
-    </row>
-    <row r="198" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q197" s="43"/>
+    </row>
+    <row r="198" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="33" t="s">
         <v>30</v>
       </c>
@@ -11577,9 +11541,9 @@
         <v>682</v>
       </c>
       <c r="P198" s="12"/>
-      <c r="Q198" s="44"/>
-    </row>
-    <row r="199" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q198" s="43"/>
+    </row>
+    <row r="199" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="33" t="s">
         <v>30</v>
       </c>
@@ -11616,9 +11580,9 @@
         <v>682</v>
       </c>
       <c r="P199" s="12"/>
-      <c r="Q199" s="44"/>
-    </row>
-    <row r="200" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q199" s="43"/>
+    </row>
+    <row r="200" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="33" t="s">
         <v>30</v>
       </c>
@@ -11655,9 +11619,9 @@
         <v>682</v>
       </c>
       <c r="P200" s="12"/>
-      <c r="Q200" s="44"/>
-    </row>
-    <row r="201" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q200" s="43"/>
+    </row>
+    <row r="201" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="33" t="s">
         <v>700</v>
       </c>
@@ -11694,9 +11658,9 @@
         <v>682</v>
       </c>
       <c r="P201" s="12"/>
-      <c r="Q201" s="44"/>
-    </row>
-    <row r="202" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q201" s="43"/>
+    </row>
+    <row r="202" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="33" t="s">
         <v>722</v>
       </c>
@@ -11733,36 +11697,36 @@
         <v>682</v>
       </c>
       <c r="P202" s="12"/>
-      <c r="Q202" s="44"/>
-    </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A203" s="67" t="s">
+      <c r="Q202" s="43"/>
+    </row>
+    <row r="203" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A203" s="64" t="s">
         <v>890</v>
       </c>
-      <c r="B203" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C203" s="67" t="s">
+      <c r="B203" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C203" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="D203" s="74" t="s">
+      <c r="D203" s="70" t="s">
         <v>555</v>
       </c>
-      <c r="E203" s="75"/>
-      <c r="F203" s="75"/>
-      <c r="G203" s="75"/>
-      <c r="H203" s="75"/>
-      <c r="I203" s="75"/>
-      <c r="J203" s="75"/>
-      <c r="K203" s="75"/>
-      <c r="L203" s="75"/>
-      <c r="M203" s="75"/>
-      <c r="N203" s="75"/>
-      <c r="O203" s="75"/>
-      <c r="P203" s="76"/>
-      <c r="Q203" s="44"/>
-    </row>
-    <row r="204" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E203" s="71"/>
+      <c r="F203" s="71"/>
+      <c r="G203" s="71"/>
+      <c r="H203" s="71"/>
+      <c r="I203" s="71"/>
+      <c r="J203" s="71"/>
+      <c r="K203" s="71"/>
+      <c r="L203" s="71"/>
+      <c r="M203" s="71"/>
+      <c r="N203" s="71"/>
+      <c r="O203" s="71"/>
+      <c r="P203" s="72"/>
+      <c r="Q203" s="43"/>
+    </row>
+    <row r="204" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="33" t="s">
         <v>890</v>
       </c>
@@ -11799,9 +11763,9 @@
         <v>682</v>
       </c>
       <c r="P204" s="12"/>
-      <c r="Q204" s="44"/>
-    </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q204" s="43"/>
+    </row>
+    <row r="205" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A205" s="3" t="s">
         <v>30</v>
       </c>
@@ -11811,51 +11775,51 @@
       <c r="C205" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D205" s="77" t="s">
+      <c r="D205" s="67" t="s">
         <v>556</v>
       </c>
-      <c r="E205" s="78"/>
-      <c r="F205" s="78"/>
-      <c r="G205" s="78"/>
-      <c r="H205" s="78"/>
-      <c r="I205" s="78"/>
-      <c r="J205" s="78"/>
-      <c r="K205" s="78"/>
-      <c r="L205" s="78"/>
-      <c r="M205" s="78"/>
-      <c r="N205" s="78"/>
-      <c r="O205" s="78"/>
-      <c r="P205" s="79"/>
-      <c r="Q205" s="44"/>
-    </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A206" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B206" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C206" s="67" t="s">
+      <c r="E205" s="68"/>
+      <c r="F205" s="68"/>
+      <c r="G205" s="68"/>
+      <c r="H205" s="68"/>
+      <c r="I205" s="68"/>
+      <c r="J205" s="68"/>
+      <c r="K205" s="68"/>
+      <c r="L205" s="68"/>
+      <c r="M205" s="68"/>
+      <c r="N205" s="68"/>
+      <c r="O205" s="68"/>
+      <c r="P205" s="69"/>
+      <c r="Q205" s="43"/>
+    </row>
+    <row r="206" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A206" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B206" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C206" s="64" t="s">
         <v>255</v>
       </c>
-      <c r="D206" s="74" t="s">
+      <c r="D206" s="70" t="s">
         <v>556</v>
       </c>
-      <c r="E206" s="75"/>
-      <c r="F206" s="75"/>
-      <c r="G206" s="75"/>
-      <c r="H206" s="75"/>
-      <c r="I206" s="75"/>
-      <c r="J206" s="75"/>
-      <c r="K206" s="75"/>
-      <c r="L206" s="75"/>
-      <c r="M206" s="75"/>
-      <c r="N206" s="75"/>
-      <c r="O206" s="75"/>
-      <c r="P206" s="76"/>
-      <c r="Q206" s="44"/>
-    </row>
-    <row r="207" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E206" s="71"/>
+      <c r="F206" s="71"/>
+      <c r="G206" s="71"/>
+      <c r="H206" s="71"/>
+      <c r="I206" s="71"/>
+      <c r="J206" s="71"/>
+      <c r="K206" s="71"/>
+      <c r="L206" s="71"/>
+      <c r="M206" s="71"/>
+      <c r="N206" s="71"/>
+      <c r="O206" s="71"/>
+      <c r="P206" s="72"/>
+      <c r="Q206" s="43"/>
+    </row>
+    <row r="207" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="33" t="s">
         <v>30</v>
       </c>
@@ -11896,9 +11860,9 @@
       <c r="P207" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q207" s="44"/>
-    </row>
-    <row r="208" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q207" s="43"/>
+    </row>
+    <row r="208" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="33" t="s">
         <v>30</v>
       </c>
@@ -11939,9 +11903,9 @@
       <c r="P208" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q208" s="44"/>
-    </row>
-    <row r="209" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q208" s="43"/>
+    </row>
+    <row r="209" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="33" t="s">
         <v>30</v>
       </c>
@@ -11982,9 +11946,9 @@
       <c r="P209" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q209" s="44"/>
-    </row>
-    <row r="210" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q209" s="43"/>
+    </row>
+    <row r="210" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="33" t="s">
         <v>30</v>
       </c>
@@ -12025,9 +11989,9 @@
       <c r="P210" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q210" s="44"/>
-    </row>
-    <row r="211" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q210" s="43"/>
+    </row>
+    <row r="211" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="33" t="s">
         <v>30</v>
       </c>
@@ -12068,9 +12032,9 @@
       <c r="P211" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q211" s="44"/>
-    </row>
-    <row r="212" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q211" s="43"/>
+    </row>
+    <row r="212" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="33" t="s">
         <v>30</v>
       </c>
@@ -12111,9 +12075,9 @@
       <c r="P212" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q212" s="44"/>
-    </row>
-    <row r="213" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q212" s="43"/>
+    </row>
+    <row r="213" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="33" t="s">
         <v>30</v>
       </c>
@@ -12154,9 +12118,9 @@
       <c r="P213" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q213" s="44"/>
-    </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q213" s="43"/>
+    </row>
+    <row r="214" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A214" s="3" t="s">
         <v>30</v>
       </c>
@@ -12166,51 +12130,51 @@
       <c r="C214" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="D214" s="77" t="s">
+      <c r="D214" s="67" t="s">
         <v>557</v>
       </c>
-      <c r="E214" s="78"/>
-      <c r="F214" s="78"/>
-      <c r="G214" s="78"/>
-      <c r="H214" s="78"/>
-      <c r="I214" s="78"/>
-      <c r="J214" s="78"/>
-      <c r="K214" s="78"/>
-      <c r="L214" s="78"/>
-      <c r="M214" s="78"/>
-      <c r="N214" s="78"/>
-      <c r="O214" s="78"/>
-      <c r="P214" s="79"/>
-      <c r="Q214" s="44"/>
-    </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A215" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B215" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C215" s="67" t="s">
+      <c r="E214" s="68"/>
+      <c r="F214" s="68"/>
+      <c r="G214" s="68"/>
+      <c r="H214" s="68"/>
+      <c r="I214" s="68"/>
+      <c r="J214" s="68"/>
+      <c r="K214" s="68"/>
+      <c r="L214" s="68"/>
+      <c r="M214" s="68"/>
+      <c r="N214" s="68"/>
+      <c r="O214" s="68"/>
+      <c r="P214" s="69"/>
+      <c r="Q214" s="43"/>
+    </row>
+    <row r="215" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A215" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B215" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C215" s="64" t="s">
         <v>272</v>
       </c>
-      <c r="D215" s="74" t="s">
+      <c r="D215" s="70" t="s">
         <v>270</v>
       </c>
-      <c r="E215" s="75"/>
-      <c r="F215" s="75"/>
-      <c r="G215" s="75"/>
-      <c r="H215" s="75"/>
-      <c r="I215" s="75"/>
-      <c r="J215" s="75"/>
-      <c r="K215" s="75"/>
-      <c r="L215" s="75"/>
-      <c r="M215" s="75"/>
-      <c r="N215" s="75"/>
-      <c r="O215" s="75"/>
-      <c r="P215" s="76"/>
-      <c r="Q215" s="44"/>
-    </row>
-    <row r="216" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E215" s="71"/>
+      <c r="F215" s="71"/>
+      <c r="G215" s="71"/>
+      <c r="H215" s="71"/>
+      <c r="I215" s="71"/>
+      <c r="J215" s="71"/>
+      <c r="K215" s="71"/>
+      <c r="L215" s="71"/>
+      <c r="M215" s="71"/>
+      <c r="N215" s="71"/>
+      <c r="O215" s="71"/>
+      <c r="P215" s="72"/>
+      <c r="Q215" s="43"/>
+    </row>
+    <row r="216" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="33" t="s">
         <v>30</v>
       </c>
@@ -12247,36 +12211,36 @@
         <v>682</v>
       </c>
       <c r="P216" s="12"/>
-      <c r="Q216" s="44"/>
-    </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A217" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B217" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C217" s="67" t="s">
+      <c r="Q216" s="43"/>
+    </row>
+    <row r="217" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A217" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B217" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C217" s="64" t="s">
         <v>277</v>
       </c>
-      <c r="D217" s="74" t="s">
+      <c r="D217" s="70" t="s">
         <v>275</v>
       </c>
-      <c r="E217" s="75"/>
-      <c r="F217" s="75"/>
-      <c r="G217" s="75"/>
-      <c r="H217" s="75"/>
-      <c r="I217" s="75"/>
-      <c r="J217" s="75"/>
-      <c r="K217" s="75"/>
-      <c r="L217" s="75"/>
-      <c r="M217" s="75"/>
-      <c r="N217" s="75"/>
-      <c r="O217" s="75"/>
-      <c r="P217" s="76"/>
-      <c r="Q217" s="44"/>
-    </row>
-    <row r="218" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E217" s="71"/>
+      <c r="F217" s="71"/>
+      <c r="G217" s="71"/>
+      <c r="H217" s="71"/>
+      <c r="I217" s="71"/>
+      <c r="J217" s="71"/>
+      <c r="K217" s="71"/>
+      <c r="L217" s="71"/>
+      <c r="M217" s="71"/>
+      <c r="N217" s="71"/>
+      <c r="O217" s="71"/>
+      <c r="P217" s="72"/>
+      <c r="Q217" s="43"/>
+    </row>
+    <row r="218" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="33" t="s">
         <v>30</v>
       </c>
@@ -12313,36 +12277,36 @@
         <v>682</v>
       </c>
       <c r="P218" s="12"/>
-      <c r="Q218" s="44"/>
-    </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A219" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B219" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C219" s="67" t="s">
+      <c r="Q218" s="43"/>
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A219" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B219" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C219" s="64" t="s">
         <v>280</v>
       </c>
-      <c r="D219" s="74" t="s">
+      <c r="D219" s="70" t="s">
         <v>558</v>
       </c>
-      <c r="E219" s="75"/>
-      <c r="F219" s="75"/>
-      <c r="G219" s="75"/>
-      <c r="H219" s="75"/>
-      <c r="I219" s="75"/>
-      <c r="J219" s="75"/>
-      <c r="K219" s="75"/>
-      <c r="L219" s="75"/>
-      <c r="M219" s="75"/>
-      <c r="N219" s="75"/>
-      <c r="O219" s="75"/>
-      <c r="P219" s="76"/>
-      <c r="Q219" s="44"/>
-    </row>
-    <row r="220" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E219" s="71"/>
+      <c r="F219" s="71"/>
+      <c r="G219" s="71"/>
+      <c r="H219" s="71"/>
+      <c r="I219" s="71"/>
+      <c r="J219" s="71"/>
+      <c r="K219" s="71"/>
+      <c r="L219" s="71"/>
+      <c r="M219" s="71"/>
+      <c r="N219" s="71"/>
+      <c r="O219" s="71"/>
+      <c r="P219" s="72"/>
+      <c r="Q219" s="43"/>
+    </row>
+    <row r="220" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="33" t="s">
         <v>30</v>
       </c>
@@ -12381,9 +12345,9 @@
       <c r="P220" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q220" s="44"/>
-    </row>
-    <row r="221" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q220" s="43"/>
+    </row>
+    <row r="221" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="33" t="s">
         <v>30</v>
       </c>
@@ -12422,9 +12386,9 @@
       <c r="P221" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q221" s="44"/>
-    </row>
-    <row r="222" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q221" s="43"/>
+    </row>
+    <row r="222" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="33" t="s">
         <v>30</v>
       </c>
@@ -12463,9 +12427,9 @@
       <c r="P222" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q222" s="44"/>
-    </row>
-    <row r="223" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q222" s="43"/>
+    </row>
+    <row r="223" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="33" t="s">
         <v>30</v>
       </c>
@@ -12504,9 +12468,9 @@
       <c r="P223" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q223" s="44"/>
-    </row>
-    <row r="224" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q223" s="43"/>
+    </row>
+    <row r="224" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="33" t="s">
         <v>30</v>
       </c>
@@ -12545,9 +12509,9 @@
       <c r="P224" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q224" s="44"/>
-    </row>
-    <row r="225" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q224" s="43"/>
+    </row>
+    <row r="225" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="33" t="s">
         <v>30</v>
       </c>
@@ -12586,9 +12550,9 @@
       <c r="P225" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q225" s="44"/>
-    </row>
-    <row r="226" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q225" s="43"/>
+    </row>
+    <row r="226" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="33" t="s">
         <v>30</v>
       </c>
@@ -12627,9 +12591,9 @@
       <c r="P226" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q226" s="44"/>
-    </row>
-    <row r="227" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q226" s="43"/>
+    </row>
+    <row r="227" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="33" t="s">
         <v>30</v>
       </c>
@@ -12668,9 +12632,9 @@
       <c r="P227" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q227" s="44"/>
-    </row>
-    <row r="228" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q227" s="43"/>
+    </row>
+    <row r="228" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="33" t="s">
         <v>877</v>
       </c>
@@ -12709,9 +12673,9 @@
       <c r="P228" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q228" s="44"/>
-    </row>
-    <row r="229" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q228" s="43"/>
+    </row>
+    <row r="229" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="33" t="s">
         <v>875</v>
       </c>
@@ -12750,9 +12714,9 @@
       <c r="P229" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q229" s="44"/>
-    </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q229" s="43"/>
+    </row>
+    <row r="230" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A230" s="3" t="s">
         <v>30</v>
       </c>
@@ -12762,51 +12726,51 @@
       <c r="C230" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="D230" s="77" t="s">
+      <c r="D230" s="67" t="s">
         <v>559</v>
       </c>
-      <c r="E230" s="78"/>
-      <c r="F230" s="78"/>
-      <c r="G230" s="78"/>
-      <c r="H230" s="78"/>
-      <c r="I230" s="78"/>
-      <c r="J230" s="78"/>
-      <c r="K230" s="78"/>
-      <c r="L230" s="78"/>
-      <c r="M230" s="78"/>
-      <c r="N230" s="78"/>
-      <c r="O230" s="78"/>
-      <c r="P230" s="79"/>
-      <c r="Q230" s="44"/>
-    </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A231" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B231" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C231" s="67" t="s">
+      <c r="E230" s="68"/>
+      <c r="F230" s="68"/>
+      <c r="G230" s="68"/>
+      <c r="H230" s="68"/>
+      <c r="I230" s="68"/>
+      <c r="J230" s="68"/>
+      <c r="K230" s="68"/>
+      <c r="L230" s="68"/>
+      <c r="M230" s="68"/>
+      <c r="N230" s="68"/>
+      <c r="O230" s="68"/>
+      <c r="P230" s="69"/>
+      <c r="Q230" s="43"/>
+    </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A231" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B231" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C231" s="64" t="s">
         <v>297</v>
       </c>
-      <c r="D231" s="74" t="s">
+      <c r="D231" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="E231" s="75"/>
-      <c r="F231" s="75"/>
-      <c r="G231" s="75"/>
-      <c r="H231" s="75"/>
-      <c r="I231" s="75"/>
-      <c r="J231" s="75"/>
-      <c r="K231" s="75"/>
-      <c r="L231" s="75"/>
-      <c r="M231" s="75"/>
-      <c r="N231" s="75"/>
-      <c r="O231" s="75"/>
-      <c r="P231" s="76"/>
-      <c r="Q231" s="44"/>
-    </row>
-    <row r="232" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E231" s="71"/>
+      <c r="F231" s="71"/>
+      <c r="G231" s="71"/>
+      <c r="H231" s="71"/>
+      <c r="I231" s="71"/>
+      <c r="J231" s="71"/>
+      <c r="K231" s="71"/>
+      <c r="L231" s="71"/>
+      <c r="M231" s="71"/>
+      <c r="N231" s="71"/>
+      <c r="O231" s="71"/>
+      <c r="P231" s="72"/>
+      <c r="Q231" s="43"/>
+    </row>
+    <row r="232" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="33" t="s">
         <v>890</v>
       </c>
@@ -12849,9 +12813,9 @@
       <c r="P232" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q232" s="44"/>
-    </row>
-    <row r="233" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q232" s="43"/>
+    </row>
+    <row r="233" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="33" t="s">
         <v>890</v>
       </c>
@@ -12894,9 +12858,9 @@
       <c r="P233" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q233" s="44"/>
-    </row>
-    <row r="234" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q233" s="43"/>
+    </row>
+    <row r="234" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="33" t="s">
         <v>890</v>
       </c>
@@ -12939,9 +12903,9 @@
       <c r="P234" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q234" s="44"/>
-    </row>
-    <row r="235" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q234" s="43"/>
+    </row>
+    <row r="235" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="33" t="s">
         <v>30</v>
       </c>
@@ -12982,9 +12946,9 @@
       <c r="P235" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q235" s="44"/>
-    </row>
-    <row r="236" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q235" s="43"/>
+    </row>
+    <row r="236" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="33" t="s">
         <v>30</v>
       </c>
@@ -13025,9 +12989,9 @@
       <c r="P236" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q236" s="44"/>
-    </row>
-    <row r="237" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q236" s="43"/>
+    </row>
+    <row r="237" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="33" t="s">
         <v>30</v>
       </c>
@@ -13066,9 +13030,9 @@
       <c r="P237" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q237" s="44"/>
-    </row>
-    <row r="238" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q237" s="43"/>
+    </row>
+    <row r="238" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="33" t="s">
         <v>30</v>
       </c>
@@ -13107,9 +13071,9 @@
       <c r="P238" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q238" s="44"/>
-    </row>
-    <row r="239" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q238" s="43"/>
+    </row>
+    <row r="239" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="33" t="s">
         <v>30</v>
       </c>
@@ -13148,9 +13112,9 @@
       <c r="P239" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q239" s="44"/>
-    </row>
-    <row r="240" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Q239" s="43"/>
+    </row>
+    <row r="240" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A240" s="33" t="s">
         <v>780</v>
       </c>
@@ -13189,9 +13153,9 @@
       <c r="P240" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q240" s="44"/>
-    </row>
-    <row r="241" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q240" s="43"/>
+    </row>
+    <row r="241" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="33" t="s">
         <v>30</v>
       </c>
@@ -13230,9 +13194,9 @@
       <c r="P241" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q241" s="44"/>
-    </row>
-    <row r="242" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q241" s="43"/>
+    </row>
+    <row r="242" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="33" t="s">
         <v>30</v>
       </c>
@@ -13271,9 +13235,9 @@
       <c r="P242" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q242" s="44"/>
-    </row>
-    <row r="243" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q242" s="43"/>
+    </row>
+    <row r="243" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="33" t="s">
         <v>30</v>
       </c>
@@ -13312,9 +13276,9 @@
       <c r="P243" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q243" s="44"/>
-    </row>
-    <row r="244" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q243" s="43"/>
+    </row>
+    <row r="244" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="33" t="s">
         <v>890</v>
       </c>
@@ -13324,7 +13288,7 @@
       <c r="C244" s="32" t="s">
         <v>888</v>
       </c>
-      <c r="D244" s="68" t="s">
+      <c r="D244" s="65" t="s">
         <v>889</v>
       </c>
       <c r="E244" s="32" t="s">
@@ -13357,7 +13321,7 @@
       </c>
       <c r="Q244" s="19"/>
     </row>
-    <row r="245" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="33" t="s">
         <v>890</v>
       </c>
@@ -13367,7 +13331,7 @@
       <c r="C245" s="32" t="s">
         <v>891</v>
       </c>
-      <c r="D245" s="68" t="s">
+      <c r="D245" s="65" t="s">
         <v>892</v>
       </c>
       <c r="E245" s="32" t="s">
@@ -13400,34 +13364,34 @@
       </c>
       <c r="Q245" s="19"/>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A246" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B246" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C246" s="67" t="s">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A246" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B246" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C246" s="64" t="s">
         <v>321</v>
       </c>
-      <c r="D246" s="74" t="s">
+      <c r="D246" s="70" t="s">
         <v>561</v>
       </c>
-      <c r="E246" s="75"/>
-      <c r="F246" s="75"/>
-      <c r="G246" s="75"/>
-      <c r="H246" s="75"/>
-      <c r="I246" s="75"/>
-      <c r="J246" s="75"/>
-      <c r="K246" s="75"/>
-      <c r="L246" s="75"/>
-      <c r="M246" s="75"/>
-      <c r="N246" s="75"/>
-      <c r="O246" s="75"/>
-      <c r="P246" s="76"/>
-      <c r="Q246" s="44"/>
-    </row>
-    <row r="247" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E246" s="71"/>
+      <c r="F246" s="71"/>
+      <c r="G246" s="71"/>
+      <c r="H246" s="71"/>
+      <c r="I246" s="71"/>
+      <c r="J246" s="71"/>
+      <c r="K246" s="71"/>
+      <c r="L246" s="71"/>
+      <c r="M246" s="71"/>
+      <c r="N246" s="71"/>
+      <c r="O246" s="71"/>
+      <c r="P246" s="72"/>
+      <c r="Q246" s="43"/>
+    </row>
+    <row r="247" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="33" t="s">
         <v>30</v>
       </c>
@@ -13466,9 +13430,9 @@
         <v>695</v>
       </c>
       <c r="P247" s="12"/>
-      <c r="Q247" s="44"/>
-    </row>
-    <row r="248" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q247" s="43"/>
+    </row>
+    <row r="248" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="33" t="s">
         <v>770</v>
       </c>
@@ -13507,9 +13471,9 @@
         <v>682</v>
       </c>
       <c r="P248" s="12"/>
-      <c r="Q248" s="44"/>
-    </row>
-    <row r="249" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q248" s="43"/>
+    </row>
+    <row r="249" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="33" t="s">
         <v>30</v>
       </c>
@@ -13548,9 +13512,9 @@
         <v>695</v>
       </c>
       <c r="P249" s="12"/>
-      <c r="Q249" s="44"/>
-    </row>
-    <row r="250" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q249" s="43"/>
+    </row>
+    <row r="250" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="33" t="s">
         <v>770</v>
       </c>
@@ -13589,9 +13553,9 @@
         <v>682</v>
       </c>
       <c r="P250" s="12"/>
-      <c r="Q250" s="44"/>
-    </row>
-    <row r="251" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q250" s="43"/>
+    </row>
+    <row r="251" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="33" t="s">
         <v>30</v>
       </c>
@@ -13632,9 +13596,9 @@
       <c r="P251" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q251" s="44"/>
-    </row>
-    <row r="252" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q251" s="43"/>
+    </row>
+    <row r="252" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="33" t="s">
         <v>770</v>
       </c>
@@ -13675,9 +13639,9 @@
       <c r="P252" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q252" s="44"/>
-    </row>
-    <row r="253" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q252" s="43"/>
+    </row>
+    <row r="253" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="33" t="s">
         <v>30</v>
       </c>
@@ -13716,9 +13680,9 @@
       <c r="P253" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q253" s="44"/>
-    </row>
-    <row r="254" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q253" s="43"/>
+    </row>
+    <row r="254" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="33" t="s">
         <v>30</v>
       </c>
@@ -13757,9 +13721,9 @@
       <c r="P254" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q254" s="44"/>
-    </row>
-    <row r="255" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q254" s="43"/>
+    </row>
+    <row r="255" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="33" t="s">
         <v>848</v>
       </c>
@@ -13800,9 +13764,9 @@
       <c r="P255" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q255" s="44"/>
-    </row>
-    <row r="256" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q255" s="43"/>
+    </row>
+    <row r="256" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="33" t="s">
         <v>30</v>
       </c>
@@ -13841,9 +13805,9 @@
       <c r="P256" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q256" s="44"/>
-    </row>
-    <row r="257" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q256" s="43"/>
+    </row>
+    <row r="257" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="33" t="s">
         <v>702</v>
       </c>
@@ -13884,9 +13848,9 @@
       <c r="P257" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q257" s="44"/>
-    </row>
-    <row r="258" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q257" s="43"/>
+    </row>
+    <row r="258" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="33" t="s">
         <v>770</v>
       </c>
@@ -13927,36 +13891,36 @@
       <c r="P258" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q258" s="44"/>
-    </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A259" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B259" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C259" s="67" t="s">
+      <c r="Q258" s="43"/>
+    </row>
+    <row r="259" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A259" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B259" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C259" s="64" t="s">
         <v>321</v>
       </c>
-      <c r="D259" s="74" t="s">
+      <c r="D259" s="70" t="s">
         <v>562</v>
       </c>
-      <c r="E259" s="75"/>
-      <c r="F259" s="75"/>
-      <c r="G259" s="75"/>
-      <c r="H259" s="75"/>
-      <c r="I259" s="75"/>
-      <c r="J259" s="75"/>
-      <c r="K259" s="75"/>
-      <c r="L259" s="75"/>
-      <c r="M259" s="75"/>
-      <c r="N259" s="75"/>
-      <c r="O259" s="75"/>
-      <c r="P259" s="76"/>
-      <c r="Q259" s="44"/>
-    </row>
-    <row r="260" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E259" s="71"/>
+      <c r="F259" s="71"/>
+      <c r="G259" s="71"/>
+      <c r="H259" s="71"/>
+      <c r="I259" s="71"/>
+      <c r="J259" s="71"/>
+      <c r="K259" s="71"/>
+      <c r="L259" s="71"/>
+      <c r="M259" s="71"/>
+      <c r="N259" s="71"/>
+      <c r="O259" s="71"/>
+      <c r="P259" s="72"/>
+      <c r="Q259" s="43"/>
+    </row>
+    <row r="260" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="33" t="s">
         <v>30</v>
       </c>
@@ -13997,9 +13961,9 @@
       <c r="P260" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q260" s="44"/>
-    </row>
-    <row r="261" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q260" s="43"/>
+    </row>
+    <row r="261" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="33" t="s">
         <v>770</v>
       </c>
@@ -14040,9 +14004,9 @@
       <c r="P261" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q261" s="44"/>
-    </row>
-    <row r="262" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q261" s="43"/>
+    </row>
+    <row r="262" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="33" t="s">
         <v>30</v>
       </c>
@@ -14083,9 +14047,9 @@
       <c r="P262" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q262" s="44"/>
-    </row>
-    <row r="263" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q262" s="43"/>
+    </row>
+    <row r="263" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="33" t="s">
         <v>30</v>
       </c>
@@ -14126,9 +14090,9 @@
       <c r="P263" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q263" s="44"/>
-    </row>
-    <row r="264" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q263" s="43"/>
+    </row>
+    <row r="264" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="33" t="s">
         <v>30</v>
       </c>
@@ -14169,9 +14133,9 @@
       <c r="P264" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q264" s="44"/>
-    </row>
-    <row r="265" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q264" s="43"/>
+    </row>
+    <row r="265" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="33" t="s">
         <v>770</v>
       </c>
@@ -14212,9 +14176,9 @@
       <c r="P265" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q265" s="44"/>
-    </row>
-    <row r="266" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q265" s="43"/>
+    </row>
+    <row r="266" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="33" t="s">
         <v>30</v>
       </c>
@@ -14255,9 +14219,9 @@
       <c r="P266" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q266" s="44"/>
-    </row>
-    <row r="267" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q266" s="43"/>
+    </row>
+    <row r="267" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="33" t="s">
         <v>770</v>
       </c>
@@ -14298,9 +14262,9 @@
       <c r="P267" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q267" s="44"/>
-    </row>
-    <row r="268" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q267" s="43"/>
+    </row>
+    <row r="268" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="33" t="s">
         <v>30</v>
       </c>
@@ -14341,9 +14305,9 @@
       <c r="P268" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q268" s="44"/>
-    </row>
-    <row r="269" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q268" s="43"/>
+    </row>
+    <row r="269" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="33" t="s">
         <v>770</v>
       </c>
@@ -14384,9 +14348,9 @@
       <c r="P269" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q269" s="44"/>
-    </row>
-    <row r="270" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q269" s="43"/>
+    </row>
+    <row r="270" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="33" t="s">
         <v>828</v>
       </c>
@@ -14429,9 +14393,9 @@
       <c r="P270" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q270" s="44"/>
-    </row>
-    <row r="271" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q270" s="43"/>
+    </row>
+    <row r="271" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="33" t="s">
         <v>828</v>
       </c>
@@ -14474,9 +14438,9 @@
       <c r="P271" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q271" s="44"/>
-    </row>
-    <row r="272" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q271" s="43"/>
+    </row>
+    <row r="272" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="33" t="s">
         <v>30</v>
       </c>
@@ -14517,9 +14481,9 @@
       <c r="P272" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q272" s="44"/>
-    </row>
-    <row r="273" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q272" s="43"/>
+    </row>
+    <row r="273" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="33" t="s">
         <v>770</v>
       </c>
@@ -14560,9 +14524,9 @@
       <c r="P273" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q273" s="44"/>
-    </row>
-    <row r="274" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q273" s="43"/>
+    </row>
+    <row r="274" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="33" t="s">
         <v>30</v>
       </c>
@@ -14603,9 +14567,9 @@
       <c r="P274" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q274" s="44"/>
-    </row>
-    <row r="275" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q274" s="43"/>
+    </row>
+    <row r="275" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="33" t="s">
         <v>770</v>
       </c>
@@ -14646,9 +14610,9 @@
       <c r="P275" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q275" s="44"/>
-    </row>
-    <row r="276" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q275" s="43"/>
+    </row>
+    <row r="276" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="33" t="s">
         <v>30</v>
       </c>
@@ -14689,9 +14653,9 @@
       <c r="P276" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q276" s="44"/>
-    </row>
-    <row r="277" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q276" s="43"/>
+    </row>
+    <row r="277" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="33" t="s">
         <v>770</v>
       </c>
@@ -14732,9 +14696,9 @@
       <c r="P277" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q277" s="44"/>
-    </row>
-    <row r="278" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q277" s="43"/>
+    </row>
+    <row r="278" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="33" t="s">
         <v>828</v>
       </c>
@@ -14775,9 +14739,9 @@
       <c r="P278" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q278" s="44"/>
-    </row>
-    <row r="279" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q278" s="43"/>
+    </row>
+    <row r="279" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="33" t="s">
         <v>828</v>
       </c>
@@ -14818,9 +14782,9 @@
       <c r="P279" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q279" s="44"/>
-    </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q279" s="43"/>
+    </row>
+    <row r="280" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A280" s="3" t="s">
         <v>30</v>
       </c>
@@ -14830,51 +14794,51 @@
       <c r="C280" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="D280" s="77" t="s">
+      <c r="D280" s="67" t="s">
         <v>563</v>
       </c>
-      <c r="E280" s="78"/>
-      <c r="F280" s="78"/>
-      <c r="G280" s="78"/>
-      <c r="H280" s="78"/>
-      <c r="I280" s="78"/>
-      <c r="J280" s="78"/>
-      <c r="K280" s="78"/>
-      <c r="L280" s="78"/>
-      <c r="M280" s="78"/>
-      <c r="N280" s="78"/>
-      <c r="O280" s="78"/>
-      <c r="P280" s="79"/>
-      <c r="Q280" s="44"/>
-    </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A281" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B281" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C281" s="67" t="s">
+      <c r="E280" s="68"/>
+      <c r="F280" s="68"/>
+      <c r="G280" s="68"/>
+      <c r="H280" s="68"/>
+      <c r="I280" s="68"/>
+      <c r="J280" s="68"/>
+      <c r="K280" s="68"/>
+      <c r="L280" s="68"/>
+      <c r="M280" s="68"/>
+      <c r="N280" s="68"/>
+      <c r="O280" s="68"/>
+      <c r="P280" s="69"/>
+      <c r="Q280" s="43"/>
+    </row>
+    <row r="281" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A281" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B281" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C281" s="64" t="s">
         <v>356</v>
       </c>
-      <c r="D281" s="74" t="s">
+      <c r="D281" s="70" t="s">
         <v>563</v>
       </c>
-      <c r="E281" s="75"/>
-      <c r="F281" s="75"/>
-      <c r="G281" s="75"/>
-      <c r="H281" s="75"/>
-      <c r="I281" s="75"/>
-      <c r="J281" s="75"/>
-      <c r="K281" s="75"/>
-      <c r="L281" s="75"/>
-      <c r="M281" s="75"/>
-      <c r="N281" s="75"/>
-      <c r="O281" s="75"/>
-      <c r="P281" s="76"/>
-      <c r="Q281" s="44"/>
-    </row>
-    <row r="282" spans="1:17" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E281" s="71"/>
+      <c r="F281" s="71"/>
+      <c r="G281" s="71"/>
+      <c r="H281" s="71"/>
+      <c r="I281" s="71"/>
+      <c r="J281" s="71"/>
+      <c r="K281" s="71"/>
+      <c r="L281" s="71"/>
+      <c r="M281" s="71"/>
+      <c r="N281" s="71"/>
+      <c r="O281" s="71"/>
+      <c r="P281" s="72"/>
+      <c r="Q281" s="43"/>
+    </row>
+    <row r="282" spans="1:17" ht="73.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="33" t="s">
         <v>30</v>
       </c>
@@ -14921,11 +14885,11 @@
       <c r="P282" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="Q282" s="44"/>
-    </row>
-    <row r="283" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A283" s="33" t="s">
-        <v>30</v>
+      <c r="Q282" s="43"/>
+    </row>
+    <row r="283" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A283" s="45" t="s">
+        <v>932</v>
       </c>
       <c r="B283" s="33" t="s">
         <v>3</v>
@@ -14946,7 +14910,9 @@
       <c r="J283" s="35">
         <v>41183</v>
       </c>
-      <c r="K283" s="35"/>
+      <c r="K283" s="56">
+        <v>46110</v>
+      </c>
       <c r="L283" s="35" t="s">
         <v>591</v>
       </c>
@@ -14962,11 +14928,13 @@
       <c r="P283" s="13" t="s">
         <v>601</v>
       </c>
-      <c r="Q283" s="44"/>
-    </row>
-    <row r="284" spans="1:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A284" s="33" t="s">
-        <v>30</v>
+      <c r="Q283" s="38" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="284" spans="1:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A284" s="45" t="s">
+        <v>932</v>
       </c>
       <c r="B284" s="33" t="s">
         <v>3</v>
@@ -14993,7 +14961,9 @@
       <c r="J284" s="35">
         <v>1</v>
       </c>
-      <c r="K284" s="35"/>
+      <c r="K284" s="56">
+        <v>46110</v>
+      </c>
       <c r="L284" s="35" t="s">
         <v>591</v>
       </c>
@@ -15009,11 +14979,13 @@
       <c r="P284" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q284" s="44"/>
-    </row>
-    <row r="285" spans="1:17" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A285" s="33" t="s">
-        <v>30</v>
+      <c r="Q284" s="38" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="285" spans="1:17" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A285" s="45" t="s">
+        <v>932</v>
       </c>
       <c r="B285" s="33" t="s">
         <v>3</v>
@@ -15040,7 +15012,9 @@
       <c r="J285" s="35">
         <v>1</v>
       </c>
-      <c r="K285" s="35"/>
+      <c r="K285" s="56">
+        <v>46110</v>
+      </c>
       <c r="L285" s="35" t="s">
         <v>591</v>
       </c>
@@ -15056,11 +15030,13 @@
       <c r="P285" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q285" s="44"/>
-    </row>
-    <row r="286" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A286" s="33" t="s">
-        <v>30</v>
+      <c r="Q285" s="38" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="286" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A286" s="45" t="s">
+        <v>932</v>
       </c>
       <c r="B286" s="33" t="s">
         <v>3</v>
@@ -15087,7 +15063,9 @@
       <c r="J286" s="35">
         <v>1</v>
       </c>
-      <c r="K286" s="35"/>
+      <c r="K286" s="56">
+        <v>46110</v>
+      </c>
       <c r="L286" s="35" t="s">
         <v>591</v>
       </c>
@@ -15103,9 +15081,11 @@
       <c r="P286" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q286" s="44"/>
-    </row>
-    <row r="287" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q286" s="38" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="287" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="33" t="s">
         <v>30</v>
       </c>
@@ -15152,11 +15132,11 @@
       <c r="P287" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="Q287" s="44"/>
-    </row>
-    <row r="288" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="33" t="s">
-        <v>30</v>
+      <c r="Q287" s="43"/>
+    </row>
+    <row r="288" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A288" s="45" t="s">
+        <v>932</v>
       </c>
       <c r="B288" s="33" t="s">
         <v>3</v>
@@ -15177,7 +15157,9 @@
       <c r="J288" s="35">
         <v>41183</v>
       </c>
-      <c r="K288" s="35"/>
+      <c r="K288" s="56">
+        <v>46110</v>
+      </c>
       <c r="L288" s="35" t="s">
         <v>591</v>
       </c>
@@ -15193,11 +15175,13 @@
       <c r="P288" s="13" t="s">
         <v>601</v>
       </c>
-      <c r="Q288" s="44"/>
-    </row>
-    <row r="289" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A289" s="33" t="s">
-        <v>30</v>
+      <c r="Q288" s="38" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="289" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A289" s="45" t="s">
+        <v>932</v>
       </c>
       <c r="B289" s="33" t="s">
         <v>3</v>
@@ -15224,7 +15208,9 @@
       <c r="J289" s="35">
         <v>1</v>
       </c>
-      <c r="K289" s="35"/>
+      <c r="K289" s="56">
+        <v>46110</v>
+      </c>
       <c r="L289" s="35" t="s">
         <v>591</v>
       </c>
@@ -15240,9 +15226,11 @@
       <c r="P289" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q289" s="44"/>
-    </row>
-    <row r="290" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q289" s="38" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="290" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="33" t="s">
         <v>700</v>
       </c>
@@ -15281,9 +15269,9 @@
       <c r="P290" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q290" s="44"/>
-    </row>
-    <row r="291" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q290" s="43"/>
+    </row>
+    <row r="291" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="33" t="s">
         <v>722</v>
       </c>
@@ -15322,9 +15310,9 @@
       <c r="P291" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q291" s="44"/>
-    </row>
-    <row r="292" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q291" s="43"/>
+    </row>
+    <row r="292" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="33" t="s">
         <v>722</v>
       </c>
@@ -15363,9 +15351,9 @@
       <c r="P292" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="Q292" s="44"/>
-    </row>
-    <row r="293" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q292" s="43"/>
+    </row>
+    <row r="293" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="33" t="s">
         <v>722</v>
       </c>
@@ -15404,9 +15392,9 @@
       <c r="P293" s="13" t="s">
         <v>601</v>
       </c>
-      <c r="Q293" s="44"/>
-    </row>
-    <row r="294" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q293" s="43"/>
+    </row>
+    <row r="294" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="33" t="s">
         <v>722</v>
       </c>
@@ -15445,9 +15433,9 @@
       <c r="P294" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q294" s="44"/>
-    </row>
-    <row r="295" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q294" s="43"/>
+    </row>
+    <row r="295" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="33" t="s">
         <v>796</v>
       </c>
@@ -15488,9 +15476,9 @@
         <v>695</v>
       </c>
       <c r="P295" s="13"/>
-      <c r="Q295" s="44"/>
-    </row>
-    <row r="296" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q295" s="43"/>
+    </row>
+    <row r="296" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="33" t="s">
         <v>796</v>
       </c>
@@ -15531,9 +15519,9 @@
         <v>682</v>
       </c>
       <c r="P296" s="13"/>
-      <c r="Q296" s="44"/>
-    </row>
-    <row r="297" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q296" s="43"/>
+    </row>
+    <row r="297" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="33" t="s">
         <v>796</v>
       </c>
@@ -15574,9 +15562,9 @@
         <v>695</v>
       </c>
       <c r="P297" s="13"/>
-      <c r="Q297" s="44"/>
-    </row>
-    <row r="298" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q297" s="43"/>
+    </row>
+    <row r="298" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="33" t="s">
         <v>796</v>
       </c>
@@ -15617,9 +15605,9 @@
         <v>682</v>
       </c>
       <c r="P298" s="13"/>
-      <c r="Q298" s="44"/>
-    </row>
-    <row r="299" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q298" s="43"/>
+    </row>
+    <row r="299" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="33" t="s">
         <v>796</v>
       </c>
@@ -15660,9 +15648,9 @@
         <v>695</v>
       </c>
       <c r="P299" s="13"/>
-      <c r="Q299" s="44"/>
-    </row>
-    <row r="300" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q299" s="43"/>
+    </row>
+    <row r="300" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="33" t="s">
         <v>796</v>
       </c>
@@ -15703,9 +15691,9 @@
         <v>682</v>
       </c>
       <c r="P300" s="13"/>
-      <c r="Q300" s="44"/>
-    </row>
-    <row r="301" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q300" s="43"/>
+    </row>
+    <row r="301" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="33" t="s">
         <v>796</v>
       </c>
@@ -15746,9 +15734,9 @@
         <v>695</v>
       </c>
       <c r="P301" s="13"/>
-      <c r="Q301" s="44"/>
-    </row>
-    <row r="302" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q301" s="43"/>
+    </row>
+    <row r="302" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="33" t="s">
         <v>796</v>
       </c>
@@ -15789,9 +15777,9 @@
         <v>682</v>
       </c>
       <c r="P302" s="13"/>
-      <c r="Q302" s="44"/>
-    </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q302" s="43"/>
+    </row>
+    <row r="303" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A303" s="3" t="s">
         <v>30</v>
       </c>
@@ -15801,51 +15789,51 @@
       <c r="C303" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="D303" s="77" t="s">
+      <c r="D303" s="67" t="s">
         <v>564</v>
       </c>
-      <c r="E303" s="78"/>
-      <c r="F303" s="78"/>
-      <c r="G303" s="78"/>
-      <c r="H303" s="78"/>
-      <c r="I303" s="78"/>
-      <c r="J303" s="78"/>
-      <c r="K303" s="78"/>
-      <c r="L303" s="78"/>
-      <c r="M303" s="78"/>
-      <c r="N303" s="78"/>
-      <c r="O303" s="78"/>
-      <c r="P303" s="79"/>
-      <c r="Q303" s="44"/>
-    </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A304" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B304" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C304" s="67" t="s">
+      <c r="E303" s="68"/>
+      <c r="F303" s="68"/>
+      <c r="G303" s="68"/>
+      <c r="H303" s="68"/>
+      <c r="I303" s="68"/>
+      <c r="J303" s="68"/>
+      <c r="K303" s="68"/>
+      <c r="L303" s="68"/>
+      <c r="M303" s="68"/>
+      <c r="N303" s="68"/>
+      <c r="O303" s="68"/>
+      <c r="P303" s="69"/>
+      <c r="Q303" s="43"/>
+    </row>
+    <row r="304" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A304" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B304" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C304" s="64" t="s">
         <v>370</v>
       </c>
-      <c r="D304" s="74" t="s">
+      <c r="D304" s="70" t="s">
         <v>564</v>
       </c>
-      <c r="E304" s="75"/>
-      <c r="F304" s="75"/>
-      <c r="G304" s="75"/>
-      <c r="H304" s="75"/>
-      <c r="I304" s="75"/>
-      <c r="J304" s="75"/>
-      <c r="K304" s="75"/>
-      <c r="L304" s="75"/>
-      <c r="M304" s="75"/>
-      <c r="N304" s="75"/>
-      <c r="O304" s="75"/>
-      <c r="P304" s="76"/>
-      <c r="Q304" s="44"/>
-    </row>
-    <row r="305" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E304" s="71"/>
+      <c r="F304" s="71"/>
+      <c r="G304" s="71"/>
+      <c r="H304" s="71"/>
+      <c r="I304" s="71"/>
+      <c r="J304" s="71"/>
+      <c r="K304" s="71"/>
+      <c r="L304" s="71"/>
+      <c r="M304" s="71"/>
+      <c r="N304" s="71"/>
+      <c r="O304" s="71"/>
+      <c r="P304" s="72"/>
+      <c r="Q304" s="43"/>
+    </row>
+    <row r="305" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="33" t="s">
         <v>30</v>
       </c>
@@ -15884,9 +15872,9 @@
       <c r="P305" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="Q305" s="44"/>
-    </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q305" s="43"/>
+    </row>
+    <row r="306" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A306" s="3" t="s">
         <v>30</v>
       </c>
@@ -15896,51 +15884,51 @@
       <c r="C306" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="D306" s="77" t="s">
+      <c r="D306" s="67" t="s">
         <v>373</v>
       </c>
-      <c r="E306" s="78"/>
-      <c r="F306" s="78"/>
-      <c r="G306" s="78"/>
-      <c r="H306" s="78"/>
-      <c r="I306" s="78"/>
-      <c r="J306" s="78"/>
-      <c r="K306" s="78"/>
-      <c r="L306" s="78"/>
-      <c r="M306" s="78"/>
-      <c r="N306" s="78"/>
-      <c r="O306" s="78"/>
-      <c r="P306" s="79"/>
-      <c r="Q306" s="44"/>
-    </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A307" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B307" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C307" s="67" t="s">
+      <c r="E306" s="68"/>
+      <c r="F306" s="68"/>
+      <c r="G306" s="68"/>
+      <c r="H306" s="68"/>
+      <c r="I306" s="68"/>
+      <c r="J306" s="68"/>
+      <c r="K306" s="68"/>
+      <c r="L306" s="68"/>
+      <c r="M306" s="68"/>
+      <c r="N306" s="68"/>
+      <c r="O306" s="68"/>
+      <c r="P306" s="69"/>
+      <c r="Q306" s="43"/>
+    </row>
+    <row r="307" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A307" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B307" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C307" s="64" t="s">
         <v>374</v>
       </c>
-      <c r="D307" s="74" t="s">
+      <c r="D307" s="70" t="s">
         <v>373</v>
       </c>
-      <c r="E307" s="75"/>
-      <c r="F307" s="75"/>
-      <c r="G307" s="75"/>
-      <c r="H307" s="75"/>
-      <c r="I307" s="75"/>
-      <c r="J307" s="75"/>
-      <c r="K307" s="75"/>
-      <c r="L307" s="75"/>
-      <c r="M307" s="75"/>
-      <c r="N307" s="75"/>
-      <c r="O307" s="75"/>
-      <c r="P307" s="76"/>
-      <c r="Q307" s="44"/>
-    </row>
-    <row r="308" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E307" s="71"/>
+      <c r="F307" s="71"/>
+      <c r="G307" s="71"/>
+      <c r="H307" s="71"/>
+      <c r="I307" s="71"/>
+      <c r="J307" s="71"/>
+      <c r="K307" s="71"/>
+      <c r="L307" s="71"/>
+      <c r="M307" s="71"/>
+      <c r="N307" s="71"/>
+      <c r="O307" s="71"/>
+      <c r="P307" s="72"/>
+      <c r="Q307" s="43"/>
+    </row>
+    <row r="308" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="33" t="s">
         <v>30</v>
       </c>
@@ -15985,9 +15973,9 @@
         <v>682</v>
       </c>
       <c r="P308" s="12"/>
-      <c r="Q308" s="44"/>
-    </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q308" s="43"/>
+    </row>
+    <row r="309" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A309" s="3" t="s">
         <v>30</v>
       </c>
@@ -15997,51 +15985,51 @@
       <c r="C309" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="D309" s="77" t="s">
+      <c r="D309" s="67" t="s">
         <v>565</v>
       </c>
-      <c r="E309" s="78"/>
-      <c r="F309" s="78"/>
-      <c r="G309" s="78"/>
-      <c r="H309" s="78"/>
-      <c r="I309" s="78"/>
-      <c r="J309" s="78"/>
-      <c r="K309" s="78"/>
-      <c r="L309" s="78"/>
-      <c r="M309" s="78"/>
-      <c r="N309" s="78"/>
-      <c r="O309" s="78"/>
-      <c r="P309" s="79"/>
-      <c r="Q309" s="44"/>
-    </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A310" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B310" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C310" s="67" t="s">
+      <c r="E309" s="68"/>
+      <c r="F309" s="68"/>
+      <c r="G309" s="68"/>
+      <c r="H309" s="68"/>
+      <c r="I309" s="68"/>
+      <c r="J309" s="68"/>
+      <c r="K309" s="68"/>
+      <c r="L309" s="68"/>
+      <c r="M309" s="68"/>
+      <c r="N309" s="68"/>
+      <c r="O309" s="68"/>
+      <c r="P309" s="69"/>
+      <c r="Q309" s="43"/>
+    </row>
+    <row r="310" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A310" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B310" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C310" s="64" t="s">
         <v>378</v>
       </c>
-      <c r="D310" s="74" t="s">
+      <c r="D310" s="70" t="s">
         <v>565</v>
       </c>
-      <c r="E310" s="75"/>
-      <c r="F310" s="75"/>
-      <c r="G310" s="75"/>
-      <c r="H310" s="75"/>
-      <c r="I310" s="75"/>
-      <c r="J310" s="75"/>
-      <c r="K310" s="75"/>
-      <c r="L310" s="75"/>
-      <c r="M310" s="75"/>
-      <c r="N310" s="75"/>
-      <c r="O310" s="75"/>
-      <c r="P310" s="76"/>
-      <c r="Q310" s="44"/>
-    </row>
-    <row r="311" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E310" s="71"/>
+      <c r="F310" s="71"/>
+      <c r="G310" s="71"/>
+      <c r="H310" s="71"/>
+      <c r="I310" s="71"/>
+      <c r="J310" s="71"/>
+      <c r="K310" s="71"/>
+      <c r="L310" s="71"/>
+      <c r="M310" s="71"/>
+      <c r="N310" s="71"/>
+      <c r="O310" s="71"/>
+      <c r="P310" s="72"/>
+      <c r="Q310" s="43"/>
+    </row>
+    <row r="311" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="33" t="s">
         <v>30</v>
       </c>
@@ -16080,9 +16068,9 @@
         <v>695</v>
       </c>
       <c r="P311" s="12"/>
-      <c r="Q311" s="44"/>
-    </row>
-    <row r="312" spans="1:17" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q311" s="43"/>
+    </row>
+    <row r="312" spans="1:17" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="33" t="s">
         <v>780</v>
       </c>
@@ -16121,9 +16109,9 @@
         <v>695</v>
       </c>
       <c r="P312" s="12"/>
-      <c r="Q312" s="44"/>
-    </row>
-    <row r="313" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q312" s="43"/>
+    </row>
+    <row r="313" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="33" t="s">
         <v>30</v>
       </c>
@@ -16162,9 +16150,9 @@
         <v>695</v>
       </c>
       <c r="P313" s="12"/>
-      <c r="Q313" s="44"/>
-    </row>
-    <row r="314" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q313" s="43"/>
+    </row>
+    <row r="314" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="33" t="s">
         <v>30</v>
       </c>
@@ -16203,9 +16191,9 @@
         <v>695</v>
       </c>
       <c r="P314" s="12"/>
-      <c r="Q314" s="44"/>
-    </row>
-    <row r="315" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q314" s="43"/>
+    </row>
+    <row r="315" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="33" t="s">
         <v>30</v>
       </c>
@@ -16244,9 +16232,9 @@
         <v>695</v>
       </c>
       <c r="P315" s="12"/>
-      <c r="Q315" s="44"/>
-    </row>
-    <row r="316" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q315" s="43"/>
+    </row>
+    <row r="316" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="33" t="s">
         <v>30</v>
       </c>
@@ -16285,9 +16273,9 @@
         <v>695</v>
       </c>
       <c r="P316" s="12"/>
-      <c r="Q316" s="44"/>
-    </row>
-    <row r="317" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q316" s="43"/>
+    </row>
+    <row r="317" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="33" t="s">
         <v>30</v>
       </c>
@@ -16326,9 +16314,9 @@
         <v>695</v>
       </c>
       <c r="P317" s="12"/>
-      <c r="Q317" s="44"/>
-    </row>
-    <row r="318" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q317" s="43"/>
+    </row>
+    <row r="318" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="33" t="s">
         <v>30</v>
       </c>
@@ -16367,9 +16355,9 @@
         <v>695</v>
       </c>
       <c r="P318" s="12"/>
-      <c r="Q318" s="44"/>
-    </row>
-    <row r="319" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q318" s="43"/>
+    </row>
+    <row r="319" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="33" t="s">
         <v>30</v>
       </c>
@@ -16408,9 +16396,9 @@
         <v>695</v>
       </c>
       <c r="P319" s="12"/>
-      <c r="Q319" s="44"/>
-    </row>
-    <row r="320" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q319" s="43"/>
+    </row>
+    <row r="320" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="33" t="s">
         <v>30</v>
       </c>
@@ -16449,9 +16437,9 @@
         <v>695</v>
       </c>
       <c r="P320" s="12"/>
-      <c r="Q320" s="44"/>
-    </row>
-    <row r="321" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q320" s="43"/>
+    </row>
+    <row r="321" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="33" t="s">
         <v>30</v>
       </c>
@@ -16490,9 +16478,9 @@
         <v>695</v>
       </c>
       <c r="P321" s="12"/>
-      <c r="Q321" s="44"/>
-    </row>
-    <row r="322" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q321" s="43"/>
+    </row>
+    <row r="322" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="33" t="s">
         <v>30</v>
       </c>
@@ -16531,9 +16519,9 @@
         <v>695</v>
       </c>
       <c r="P322" s="12"/>
-      <c r="Q322" s="44"/>
-    </row>
-    <row r="323" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q322" s="43"/>
+    </row>
+    <row r="323" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="33" t="s">
         <v>30</v>
       </c>
@@ -16572,9 +16560,9 @@
         <v>695</v>
       </c>
       <c r="P323" s="12"/>
-      <c r="Q323" s="44"/>
-    </row>
-    <row r="324" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q323" s="43"/>
+    </row>
+    <row r="324" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="33" t="s">
         <v>30</v>
       </c>
@@ -16613,9 +16601,9 @@
         <v>695</v>
       </c>
       <c r="P324" s="12"/>
-      <c r="Q324" s="44"/>
-    </row>
-    <row r="325" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q324" s="43"/>
+    </row>
+    <row r="325" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="33" t="s">
         <v>30</v>
       </c>
@@ -16652,9 +16640,9 @@
         <v>695</v>
       </c>
       <c r="P325" s="12"/>
-      <c r="Q325" s="44"/>
-    </row>
-    <row r="326" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q325" s="43"/>
+    </row>
+    <row r="326" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="33" t="s">
         <v>30</v>
       </c>
@@ -16691,9 +16679,9 @@
         <v>695</v>
       </c>
       <c r="P326" s="12"/>
-      <c r="Q326" s="44"/>
-    </row>
-    <row r="327" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q326" s="43"/>
+    </row>
+    <row r="327" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A327" s="3" t="s">
         <v>30</v>
       </c>
@@ -16703,51 +16691,51 @@
       <c r="C327" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="D327" s="77" t="s">
+      <c r="D327" s="67" t="s">
         <v>566</v>
       </c>
-      <c r="E327" s="78"/>
-      <c r="F327" s="78"/>
-      <c r="G327" s="78"/>
-      <c r="H327" s="78"/>
-      <c r="I327" s="78"/>
-      <c r="J327" s="78"/>
-      <c r="K327" s="78"/>
-      <c r="L327" s="78"/>
-      <c r="M327" s="78"/>
-      <c r="N327" s="78"/>
-      <c r="O327" s="78"/>
-      <c r="P327" s="79"/>
-      <c r="Q327" s="44"/>
-    </row>
-    <row r="328" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A328" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B328" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C328" s="67" t="s">
+      <c r="E327" s="68"/>
+      <c r="F327" s="68"/>
+      <c r="G327" s="68"/>
+      <c r="H327" s="68"/>
+      <c r="I327" s="68"/>
+      <c r="J327" s="68"/>
+      <c r="K327" s="68"/>
+      <c r="L327" s="68"/>
+      <c r="M327" s="68"/>
+      <c r="N327" s="68"/>
+      <c r="O327" s="68"/>
+      <c r="P327" s="69"/>
+      <c r="Q327" s="43"/>
+    </row>
+    <row r="328" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A328" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B328" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C328" s="64" t="s">
         <v>411</v>
       </c>
-      <c r="D328" s="74" t="s">
+      <c r="D328" s="70" t="s">
         <v>566</v>
       </c>
-      <c r="E328" s="75"/>
-      <c r="F328" s="75"/>
-      <c r="G328" s="75"/>
-      <c r="H328" s="75"/>
-      <c r="I328" s="75"/>
-      <c r="J328" s="75"/>
-      <c r="K328" s="75"/>
-      <c r="L328" s="75"/>
-      <c r="M328" s="75"/>
-      <c r="N328" s="75"/>
-      <c r="O328" s="75"/>
-      <c r="P328" s="76"/>
-      <c r="Q328" s="44"/>
-    </row>
-    <row r="329" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E328" s="71"/>
+      <c r="F328" s="71"/>
+      <c r="G328" s="71"/>
+      <c r="H328" s="71"/>
+      <c r="I328" s="71"/>
+      <c r="J328" s="71"/>
+      <c r="K328" s="71"/>
+      <c r="L328" s="71"/>
+      <c r="M328" s="71"/>
+      <c r="N328" s="71"/>
+      <c r="O328" s="71"/>
+      <c r="P328" s="72"/>
+      <c r="Q328" s="43"/>
+    </row>
+    <row r="329" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="33" t="s">
         <v>30</v>
       </c>
@@ -16784,9 +16772,9 @@
         <v>695</v>
       </c>
       <c r="P329" s="12"/>
-      <c r="Q329" s="44"/>
-    </row>
-    <row r="330" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q329" s="43"/>
+    </row>
+    <row r="330" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="33" t="s">
         <v>30</v>
       </c>
@@ -16823,9 +16811,9 @@
         <v>695</v>
       </c>
       <c r="P330" s="12"/>
-      <c r="Q330" s="44"/>
-    </row>
-    <row r="331" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q330" s="43"/>
+    </row>
+    <row r="331" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="33" t="s">
         <v>722</v>
       </c>
@@ -16862,9 +16850,9 @@
         <v>695</v>
       </c>
       <c r="P331" s="12"/>
-      <c r="Q331" s="44"/>
-    </row>
-    <row r="332" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q331" s="43"/>
+    </row>
+    <row r="332" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="33" t="s">
         <v>30</v>
       </c>
@@ -16901,9 +16889,9 @@
         <v>695</v>
       </c>
       <c r="P332" s="12"/>
-      <c r="Q332" s="44"/>
-    </row>
-    <row r="333" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q332" s="43"/>
+    </row>
+    <row r="333" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="33" t="s">
         <v>30</v>
       </c>
@@ -16940,9 +16928,9 @@
         <v>695</v>
       </c>
       <c r="P333" s="12"/>
-      <c r="Q333" s="44"/>
-    </row>
-    <row r="334" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q333" s="43"/>
+    </row>
+    <row r="334" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="33" t="s">
         <v>30</v>
       </c>
@@ -16979,9 +16967,9 @@
         <v>695</v>
       </c>
       <c r="P334" s="12"/>
-      <c r="Q334" s="44"/>
-    </row>
-    <row r="335" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q334" s="43"/>
+    </row>
+    <row r="335" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="33" t="s">
         <v>30</v>
       </c>
@@ -17018,9 +17006,9 @@
         <v>695</v>
       </c>
       <c r="P335" s="12"/>
-      <c r="Q335" s="44"/>
-    </row>
-    <row r="336" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q335" s="43"/>
+    </row>
+    <row r="336" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="33" t="s">
         <v>30</v>
       </c>
@@ -17057,9 +17045,9 @@
         <v>695</v>
       </c>
       <c r="P336" s="12"/>
-      <c r="Q336" s="44"/>
-    </row>
-    <row r="337" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q336" s="43"/>
+    </row>
+    <row r="337" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="33" t="s">
         <v>30</v>
       </c>
@@ -17096,9 +17084,9 @@
         <v>695</v>
       </c>
       <c r="P337" s="12"/>
-      <c r="Q337" s="44"/>
-    </row>
-    <row r="338" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q337" s="43"/>
+    </row>
+    <row r="338" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="33" t="s">
         <v>30</v>
       </c>
@@ -17135,9 +17123,9 @@
         <v>695</v>
       </c>
       <c r="P338" s="12"/>
-      <c r="Q338" s="44"/>
-    </row>
-    <row r="339" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q338" s="43"/>
+    </row>
+    <row r="339" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="33" t="s">
         <v>30</v>
       </c>
@@ -17174,9 +17162,9 @@
         <v>695</v>
       </c>
       <c r="P339" s="12"/>
-      <c r="Q339" s="44"/>
-    </row>
-    <row r="340" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q339" s="43"/>
+    </row>
+    <row r="340" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="33" t="s">
         <v>30</v>
       </c>
@@ -17213,9 +17201,9 @@
         <v>695</v>
       </c>
       <c r="P340" s="12"/>
-      <c r="Q340" s="44"/>
-    </row>
-    <row r="341" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q340" s="43"/>
+    </row>
+    <row r="341" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="33" t="s">
         <v>30</v>
       </c>
@@ -17252,9 +17240,9 @@
         <v>695</v>
       </c>
       <c r="P341" s="12"/>
-      <c r="Q341" s="44"/>
-    </row>
-    <row r="342" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q341" s="43"/>
+    </row>
+    <row r="342" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="33" t="s">
         <v>30</v>
       </c>
@@ -17291,9 +17279,9 @@
         <v>695</v>
       </c>
       <c r="P342" s="12"/>
-      <c r="Q342" s="44"/>
-    </row>
-    <row r="343" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q342" s="43"/>
+    </row>
+    <row r="343" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="33" t="s">
         <v>30</v>
       </c>
@@ -17330,9 +17318,9 @@
         <v>695</v>
       </c>
       <c r="P343" s="12"/>
-      <c r="Q343" s="44"/>
-    </row>
-    <row r="344" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q343" s="43"/>
+    </row>
+    <row r="344" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="33" t="s">
         <v>30</v>
       </c>
@@ -17369,9 +17357,9 @@
         <v>695</v>
       </c>
       <c r="P344" s="12"/>
-      <c r="Q344" s="44"/>
-    </row>
-    <row r="345" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q344" s="43"/>
+    </row>
+    <row r="345" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="33" t="s">
         <v>30</v>
       </c>
@@ -17408,9 +17396,9 @@
         <v>695</v>
       </c>
       <c r="P345" s="12"/>
-      <c r="Q345" s="44"/>
-    </row>
-    <row r="346" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q345" s="43"/>
+    </row>
+    <row r="346" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="33" t="s">
         <v>30</v>
       </c>
@@ -17447,9 +17435,9 @@
         <v>695</v>
       </c>
       <c r="P346" s="12"/>
-      <c r="Q346" s="44"/>
-    </row>
-    <row r="347" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q346" s="43"/>
+    </row>
+    <row r="347" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="33" t="s">
         <v>30</v>
       </c>
@@ -17486,9 +17474,9 @@
         <v>695</v>
       </c>
       <c r="P347" s="12"/>
-      <c r="Q347" s="44"/>
-    </row>
-    <row r="348" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q347" s="43"/>
+    </row>
+    <row r="348" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="33" t="s">
         <v>30</v>
       </c>
@@ -17525,9 +17513,9 @@
         <v>695</v>
       </c>
       <c r="P348" s="12"/>
-      <c r="Q348" s="44"/>
-    </row>
-    <row r="349" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q348" s="43"/>
+    </row>
+    <row r="349" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="33" t="s">
         <v>30</v>
       </c>
@@ -17564,9 +17552,9 @@
         <v>695</v>
       </c>
       <c r="P349" s="12"/>
-      <c r="Q349" s="44"/>
-    </row>
-    <row r="350" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q349" s="43"/>
+    </row>
+    <row r="350" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="33" t="s">
         <v>30</v>
       </c>
@@ -17603,9 +17591,9 @@
         <v>695</v>
       </c>
       <c r="P350" s="12"/>
-      <c r="Q350" s="44"/>
-    </row>
-    <row r="351" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q350" s="43"/>
+    </row>
+    <row r="351" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="33" t="s">
         <v>30</v>
       </c>
@@ -17642,9 +17630,9 @@
         <v>695</v>
       </c>
       <c r="P351" s="12"/>
-      <c r="Q351" s="44"/>
-    </row>
-    <row r="352" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q351" s="43"/>
+    </row>
+    <row r="352" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="33" t="s">
         <v>30</v>
       </c>
@@ -17681,9 +17669,9 @@
         <v>695</v>
       </c>
       <c r="P352" s="12"/>
-      <c r="Q352" s="44"/>
-    </row>
-    <row r="353" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q352" s="43"/>
+    </row>
+    <row r="353" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="33" t="s">
         <v>879</v>
       </c>
@@ -17722,9 +17710,9 @@
         <v>695</v>
       </c>
       <c r="P353" s="12"/>
-      <c r="Q353" s="44"/>
-    </row>
-    <row r="354" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q353" s="43"/>
+    </row>
+    <row r="354" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="33" t="s">
         <v>30</v>
       </c>
@@ -17761,9 +17749,9 @@
         <v>695</v>
       </c>
       <c r="P354" s="12"/>
-      <c r="Q354" s="44"/>
-    </row>
-    <row r="355" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q354" s="43"/>
+    </row>
+    <row r="355" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="33" t="s">
         <v>30</v>
       </c>
@@ -17800,9 +17788,9 @@
         <v>695</v>
       </c>
       <c r="P355" s="12"/>
-      <c r="Q355" s="44"/>
-    </row>
-    <row r="356" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q355" s="43"/>
+    </row>
+    <row r="356" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="33" t="s">
         <v>848</v>
       </c>
@@ -17839,9 +17827,9 @@
         <v>695</v>
       </c>
       <c r="P356" s="12"/>
-      <c r="Q356" s="44"/>
-    </row>
-    <row r="357" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q356" s="43"/>
+    </row>
+    <row r="357" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="33" t="s">
         <v>30</v>
       </c>
@@ -17878,9 +17866,9 @@
         <v>695</v>
       </c>
       <c r="P357" s="12"/>
-      <c r="Q357" s="44"/>
-    </row>
-    <row r="358" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q357" s="43"/>
+    </row>
+    <row r="358" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="33" t="s">
         <v>30</v>
       </c>
@@ -17917,32 +17905,32 @@
         <v>695</v>
       </c>
       <c r="P358" s="12"/>
-      <c r="Q358" s="44"/>
-    </row>
-    <row r="359" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q358" s="43"/>
+    </row>
+    <row r="359" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="33" t="s">
         <v>30</v>
       </c>
       <c r="B359" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C359" s="42" t="s">
+      <c r="C359" s="41" t="s">
         <v>470</v>
       </c>
-      <c r="D359" s="45" t="s">
+      <c r="D359" s="44" t="s">
         <v>471</v>
       </c>
-      <c r="E359" s="42"/>
-      <c r="F359" s="42"/>
-      <c r="G359" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="H359" s="42"/>
-      <c r="I359" s="42"/>
-      <c r="J359" s="43">
+      <c r="E359" s="41"/>
+      <c r="F359" s="41"/>
+      <c r="G359" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="H359" s="41"/>
+      <c r="I359" s="41"/>
+      <c r="J359" s="42">
         <v>41722</v>
       </c>
-      <c r="K359" s="43"/>
+      <c r="K359" s="42"/>
       <c r="L359" s="35" t="s">
         <v>591</v>
       </c>
@@ -17956,9 +17944,9 @@
         <v>695</v>
       </c>
       <c r="P359" s="12"/>
-      <c r="Q359" s="44"/>
-    </row>
-    <row r="360" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q359" s="43"/>
+    </row>
+    <row r="360" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="33" t="s">
         <v>30</v>
       </c>
@@ -17995,9 +17983,9 @@
         <v>695</v>
       </c>
       <c r="P360" s="12"/>
-      <c r="Q360" s="44"/>
-    </row>
-    <row r="361" spans="1:17" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q360" s="43"/>
+    </row>
+    <row r="361" spans="1:17" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="33" t="s">
         <v>848</v>
       </c>
@@ -18034,9 +18022,9 @@
         <v>695</v>
       </c>
       <c r="P361" s="12"/>
-      <c r="Q361" s="44"/>
-    </row>
-    <row r="362" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q361" s="43"/>
+    </row>
+    <row r="362" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A362" s="3" t="s">
         <v>30</v>
       </c>
@@ -18046,223 +18034,215 @@
       <c r="C362" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="D362" s="77" t="s">
+      <c r="D362" s="67" t="s">
         <v>567</v>
       </c>
-      <c r="E362" s="78"/>
-      <c r="F362" s="78"/>
-      <c r="G362" s="78"/>
-      <c r="H362" s="78"/>
-      <c r="I362" s="78"/>
-      <c r="J362" s="78"/>
-      <c r="K362" s="78"/>
-      <c r="L362" s="78"/>
-      <c r="M362" s="78"/>
-      <c r="N362" s="78"/>
-      <c r="O362" s="78"/>
-      <c r="P362" s="79"/>
-      <c r="Q362" s="44"/>
-    </row>
-    <row r="363" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A363" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B363" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C363" s="67" t="s">
+      <c r="E362" s="68"/>
+      <c r="F362" s="68"/>
+      <c r="G362" s="68"/>
+      <c r="H362" s="68"/>
+      <c r="I362" s="68"/>
+      <c r="J362" s="68"/>
+      <c r="K362" s="68"/>
+      <c r="L362" s="68"/>
+      <c r="M362" s="68"/>
+      <c r="N362" s="68"/>
+      <c r="O362" s="68"/>
+      <c r="P362" s="69"/>
+      <c r="Q362" s="43"/>
+    </row>
+    <row r="363" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A363" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B363" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C363" s="64" t="s">
         <v>474</v>
       </c>
-      <c r="D363" s="74" t="s">
+      <c r="D363" s="70" t="s">
         <v>568</v>
       </c>
-      <c r="E363" s="75"/>
-      <c r="F363" s="75"/>
-      <c r="G363" s="75"/>
-      <c r="H363" s="75"/>
-      <c r="I363" s="75"/>
-      <c r="J363" s="75"/>
-      <c r="K363" s="75"/>
-      <c r="L363" s="75"/>
-      <c r="M363" s="75"/>
-      <c r="N363" s="75"/>
-      <c r="O363" s="75"/>
-      <c r="P363" s="76"/>
-      <c r="Q363" s="44"/>
-    </row>
-    <row r="364" spans="1:17" s="60" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A364" s="46" t="s">
+      <c r="E363" s="71"/>
+      <c r="F363" s="71"/>
+      <c r="G363" s="71"/>
+      <c r="H363" s="71"/>
+      <c r="I363" s="71"/>
+      <c r="J363" s="71"/>
+      <c r="K363" s="71"/>
+      <c r="L363" s="71"/>
+      <c r="M363" s="71"/>
+      <c r="N363" s="71"/>
+      <c r="O363" s="71"/>
+      <c r="P363" s="72"/>
+      <c r="Q363" s="43"/>
+    </row>
+    <row r="364" spans="1:17" s="57" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A364" s="33" t="s">
         <v>913</v>
       </c>
-      <c r="B364" s="46" t="s">
+      <c r="B364" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C364" s="38" t="s">
+      <c r="C364" s="32" t="s">
         <v>472</v>
       </c>
-      <c r="D364" s="72" t="s">
+      <c r="D364" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="E364" s="38"/>
-      <c r="F364" s="38"/>
-      <c r="G364" s="38"/>
-      <c r="H364" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I364" s="38"/>
-      <c r="J364" s="57">
-        <v>1</v>
-      </c>
-      <c r="K364" s="57">
+      <c r="E364" s="32"/>
+      <c r="F364" s="32"/>
+      <c r="G364" s="32"/>
+      <c r="H364" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I364" s="32"/>
+      <c r="J364" s="35">
+        <v>1</v>
+      </c>
+      <c r="K364" s="35">
         <v>46841</v>
       </c>
-      <c r="L364" s="57" t="s">
-        <v>591</v>
-      </c>
-      <c r="M364" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="N364" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="O364" s="59" t="s">
+      <c r="L364" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="M364" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="N364" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="O364" s="37" t="s">
         <v>695</v>
       </c>
-      <c r="P364" s="65"/>
-      <c r="Q364" s="39" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="365" spans="1:17" s="60" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A365" s="46" t="s">
+      <c r="P364" s="62"/>
+      <c r="Q364" s="38"/>
+    </row>
+    <row r="365" spans="1:17" s="57" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A365" s="33" t="s">
         <v>913</v>
       </c>
-      <c r="B365" s="46" t="s">
+      <c r="B365" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C365" s="38" t="s">
+      <c r="C365" s="32" t="s">
         <v>476</v>
       </c>
-      <c r="D365" s="72" t="s">
+      <c r="D365" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="E365" s="38"/>
-      <c r="F365" s="38"/>
-      <c r="G365" s="38"/>
-      <c r="H365" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I365" s="38"/>
-      <c r="J365" s="57">
-        <v>1</v>
-      </c>
-      <c r="K365" s="57">
+      <c r="E365" s="32"/>
+      <c r="F365" s="32"/>
+      <c r="G365" s="32"/>
+      <c r="H365" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I365" s="32"/>
+      <c r="J365" s="35">
+        <v>1</v>
+      </c>
+      <c r="K365" s="35">
         <v>46841</v>
       </c>
-      <c r="L365" s="57" t="s">
-        <v>591</v>
-      </c>
-      <c r="M365" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="N365" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="O365" s="59" t="s">
+      <c r="L365" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="M365" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="N365" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="O365" s="37" t="s">
         <v>695</v>
       </c>
-      <c r="P365" s="65"/>
-      <c r="Q365" s="39" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="366" spans="1:17" s="60" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A366" s="46" t="s">
+      <c r="P365" s="62"/>
+      <c r="Q365" s="38"/>
+    </row>
+    <row r="366" spans="1:17" s="57" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A366" s="33" t="s">
         <v>913</v>
       </c>
-      <c r="B366" s="46" t="s">
+      <c r="B366" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C366" s="38" t="s">
+      <c r="C366" s="32" t="s">
         <v>478</v>
       </c>
-      <c r="D366" s="72" t="s">
+      <c r="D366" s="7" t="s">
         <v>479</v>
       </c>
-      <c r="E366" s="38"/>
-      <c r="F366" s="38"/>
-      <c r="G366" s="38"/>
-      <c r="H366" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I366" s="38"/>
-      <c r="J366" s="57">
-        <v>1</v>
-      </c>
-      <c r="K366" s="57">
+      <c r="E366" s="32"/>
+      <c r="F366" s="32"/>
+      <c r="G366" s="32"/>
+      <c r="H366" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I366" s="32"/>
+      <c r="J366" s="35">
+        <v>1</v>
+      </c>
+      <c r="K366" s="35">
         <v>46841</v>
       </c>
-      <c r="L366" s="57" t="s">
-        <v>591</v>
-      </c>
-      <c r="M366" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="N366" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="O366" s="59" t="s">
+      <c r="L366" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="M366" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="N366" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="O366" s="37" t="s">
         <v>695</v>
       </c>
-      <c r="P366" s="65"/>
-      <c r="Q366" s="39" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="367" spans="1:17" s="60" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A367" s="46" t="s">
+      <c r="P366" s="62"/>
+      <c r="Q366" s="38"/>
+    </row>
+    <row r="367" spans="1:17" s="57" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A367" s="33" t="s">
         <v>913</v>
       </c>
-      <c r="B367" s="46" t="s">
+      <c r="B367" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C367" s="38" t="s">
+      <c r="C367" s="32" t="s">
         <v>480</v>
       </c>
-      <c r="D367" s="72" t="s">
+      <c r="D367" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="E367" s="38"/>
-      <c r="F367" s="38"/>
-      <c r="G367" s="38"/>
-      <c r="H367" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I367" s="38"/>
-      <c r="J367" s="57">
-        <v>1</v>
-      </c>
-      <c r="K367" s="57">
+      <c r="E367" s="32"/>
+      <c r="F367" s="32"/>
+      <c r="G367" s="32"/>
+      <c r="H367" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I367" s="32"/>
+      <c r="J367" s="35">
+        <v>1</v>
+      </c>
+      <c r="K367" s="35">
         <v>46841</v>
       </c>
-      <c r="L367" s="57" t="s">
-        <v>591</v>
-      </c>
-      <c r="M367" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="N367" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="O367" s="59" t="s">
+      <c r="L367" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="M367" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="N367" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="O367" s="37" t="s">
         <v>695</v>
       </c>
-      <c r="P367" s="65"/>
-      <c r="Q367" s="39" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="368" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P367" s="62"/>
+      <c r="Q367" s="38"/>
+    </row>
+    <row r="368" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="33" t="s">
         <v>30</v>
       </c>
@@ -18299,52 +18279,50 @@
         <v>695</v>
       </c>
       <c r="P368" s="12"/>
-      <c r="Q368" s="44"/>
-    </row>
-    <row r="369" spans="1:17" s="60" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A369" s="46" t="s">
+      <c r="Q368" s="43"/>
+    </row>
+    <row r="369" spans="1:17" s="57" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A369" s="33" t="s">
         <v>913</v>
       </c>
-      <c r="B369" s="46" t="s">
+      <c r="B369" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C369" s="38" t="s">
+      <c r="C369" s="32" t="s">
         <v>483</v>
       </c>
-      <c r="D369" s="72" t="s">
+      <c r="D369" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="E369" s="38"/>
-      <c r="F369" s="38"/>
-      <c r="G369" s="38"/>
-      <c r="H369" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I369" s="38"/>
-      <c r="J369" s="57">
-        <v>1</v>
-      </c>
-      <c r="K369" s="57">
+      <c r="E369" s="32"/>
+      <c r="F369" s="32"/>
+      <c r="G369" s="32"/>
+      <c r="H369" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I369" s="32"/>
+      <c r="J369" s="35">
+        <v>1</v>
+      </c>
+      <c r="K369" s="35">
         <v>46841</v>
       </c>
-      <c r="L369" s="57" t="s">
-        <v>591</v>
-      </c>
-      <c r="M369" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="N369" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="O369" s="59" t="s">
+      <c r="L369" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="M369" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="N369" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="O369" s="37" t="s">
         <v>695</v>
       </c>
-      <c r="P369" s="65"/>
-      <c r="Q369" s="39" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="370" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P369" s="62"/>
+      <c r="Q369" s="38"/>
+    </row>
+    <row r="370" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="33" t="s">
         <v>30</v>
       </c>
@@ -18381,32 +18359,32 @@
         <v>695</v>
       </c>
       <c r="P370" s="12"/>
-      <c r="Q370" s="44"/>
-    </row>
-    <row r="371" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q370" s="43"/>
+    </row>
+    <row r="371" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="33" t="s">
         <v>30</v>
       </c>
       <c r="B371" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C371" s="42" t="s">
+      <c r="C371" s="41" t="s">
         <v>487</v>
       </c>
-      <c r="D371" s="45" t="s">
+      <c r="D371" s="44" t="s">
         <v>488</v>
       </c>
-      <c r="E371" s="42"/>
-      <c r="F371" s="42"/>
-      <c r="G371" s="42"/>
-      <c r="H371" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="I371" s="42"/>
-      <c r="J371" s="43">
+      <c r="E371" s="41"/>
+      <c r="F371" s="41"/>
+      <c r="G371" s="41"/>
+      <c r="H371" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="I371" s="41"/>
+      <c r="J371" s="42">
         <v>41365</v>
       </c>
-      <c r="K371" s="43"/>
+      <c r="K371" s="42"/>
       <c r="L371" s="35" t="s">
         <v>591</v>
       </c>
@@ -18420,165 +18398,159 @@
         <v>695</v>
       </c>
       <c r="P371" s="12"/>
-      <c r="Q371" s="44"/>
-    </row>
-    <row r="372" spans="1:17" s="60" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A372" s="46" t="s">
+      <c r="Q371" s="43"/>
+    </row>
+    <row r="372" spans="1:17" s="57" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A372" s="33" t="s">
         <v>913</v>
       </c>
-      <c r="B372" s="46" t="s">
+      <c r="B372" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C372" s="69" t="s">
+      <c r="C372" s="41" t="s">
         <v>489</v>
       </c>
-      <c r="D372" s="70" t="s">
+      <c r="D372" s="44" t="s">
         <v>490</v>
       </c>
-      <c r="E372" s="69"/>
-      <c r="F372" s="69"/>
-      <c r="G372" s="69"/>
-      <c r="H372" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I372" s="69"/>
-      <c r="J372" s="71">
-        <v>1</v>
-      </c>
-      <c r="K372" s="57">
+      <c r="E372" s="41"/>
+      <c r="F372" s="41"/>
+      <c r="G372" s="41"/>
+      <c r="H372" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="I372" s="41"/>
+      <c r="J372" s="42">
+        <v>1</v>
+      </c>
+      <c r="K372" s="35">
         <v>46841</v>
       </c>
-      <c r="L372" s="57" t="s">
-        <v>591</v>
-      </c>
-      <c r="M372" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="N372" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="O372" s="59" t="s">
+      <c r="L372" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="M372" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="N372" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="O372" s="37" t="s">
         <v>695</v>
       </c>
-      <c r="P372" s="65"/>
-      <c r="Q372" s="39" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="373" spans="1:17" s="60" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A373" s="46" t="s">
+      <c r="P372" s="62"/>
+      <c r="Q372" s="38"/>
+    </row>
+    <row r="373" spans="1:17" s="57" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A373" s="33" t="s">
         <v>913</v>
       </c>
-      <c r="B373" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="C373" s="69" t="s">
-        <v>927</v>
-      </c>
-      <c r="D373" s="70" t="s">
-        <v>928</v>
-      </c>
-      <c r="E373" s="69"/>
-      <c r="F373" s="69"/>
-      <c r="G373" s="69"/>
-      <c r="H373" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I373" s="69"/>
-      <c r="J373" s="71">
+      <c r="B373" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C373" s="41" t="s">
+        <v>925</v>
+      </c>
+      <c r="D373" s="44" t="s">
+        <v>926</v>
+      </c>
+      <c r="E373" s="41"/>
+      <c r="F373" s="41"/>
+      <c r="G373" s="41"/>
+      <c r="H373" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="I373" s="41"/>
+      <c r="J373" s="42">
         <v>45931</v>
       </c>
-      <c r="K373" s="71"/>
-      <c r="L373" s="57" t="s">
-        <v>591</v>
-      </c>
-      <c r="M373" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="N373" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="O373" s="59" t="s">
+      <c r="K373" s="42"/>
+      <c r="L373" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="M373" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="N373" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="O373" s="37" t="s">
         <v>695</v>
       </c>
-      <c r="P373" s="73" t="s">
+      <c r="P373" s="66" t="s">
         <v>596</v>
       </c>
-      <c r="Q373" s="39" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="374" spans="1:17" s="60" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A374" s="46" t="s">
+      <c r="Q373" s="38"/>
+    </row>
+    <row r="374" spans="1:17" s="57" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A374" s="33" t="s">
         <v>913</v>
       </c>
-      <c r="B374" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="C374" s="69" t="s">
+      <c r="B374" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C374" s="41" t="s">
         <v>914</v>
       </c>
-      <c r="D374" s="70" t="s">
+      <c r="D374" s="44" t="s">
         <v>915</v>
       </c>
-      <c r="E374" s="69"/>
-      <c r="F374" s="69"/>
-      <c r="G374" s="69"/>
-      <c r="H374" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I374" s="69"/>
-      <c r="J374" s="71">
+      <c r="E374" s="41"/>
+      <c r="F374" s="41"/>
+      <c r="G374" s="41"/>
+      <c r="H374" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="I374" s="41"/>
+      <c r="J374" s="42">
         <v>45931</v>
       </c>
-      <c r="K374" s="71"/>
-      <c r="L374" s="57" t="s">
-        <v>591</v>
-      </c>
-      <c r="M374" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="N374" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="O374" s="59" t="s">
+      <c r="K374" s="42"/>
+      <c r="L374" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="M374" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="N374" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="O374" s="37" t="s">
         <v>695</v>
       </c>
-      <c r="P374" s="73" t="s">
+      <c r="P374" s="66" t="s">
         <v>596</v>
       </c>
-      <c r="Q374" s="39" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="375" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A375" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B375" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C375" s="67" t="s">
+      <c r="Q374" s="38"/>
+    </row>
+    <row r="375" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A375" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B375" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C375" s="64" t="s">
         <v>493</v>
       </c>
-      <c r="D375" s="74" t="s">
+      <c r="D375" s="70" t="s">
         <v>569</v>
       </c>
-      <c r="E375" s="75"/>
-      <c r="F375" s="75"/>
-      <c r="G375" s="75"/>
-      <c r="H375" s="75"/>
-      <c r="I375" s="75"/>
-      <c r="J375" s="75"/>
-      <c r="K375" s="75"/>
-      <c r="L375" s="75"/>
-      <c r="M375" s="75"/>
-      <c r="N375" s="75"/>
-      <c r="O375" s="75"/>
-      <c r="P375" s="76"/>
-      <c r="Q375" s="44"/>
-    </row>
-    <row r="376" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E375" s="71"/>
+      <c r="F375" s="71"/>
+      <c r="G375" s="71"/>
+      <c r="H375" s="71"/>
+      <c r="I375" s="71"/>
+      <c r="J375" s="71"/>
+      <c r="K375" s="71"/>
+      <c r="L375" s="71"/>
+      <c r="M375" s="71"/>
+      <c r="N375" s="71"/>
+      <c r="O375" s="71"/>
+      <c r="P375" s="72"/>
+      <c r="Q375" s="43"/>
+    </row>
+    <row r="376" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="33" t="s">
         <v>30</v>
       </c>
@@ -18615,9 +18587,9 @@
         <v>695</v>
       </c>
       <c r="P376" s="12"/>
-      <c r="Q376" s="44"/>
-    </row>
-    <row r="377" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q376" s="43"/>
+    </row>
+    <row r="377" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="33" t="s">
         <v>30</v>
       </c>
@@ -18654,9 +18626,9 @@
         <v>695</v>
       </c>
       <c r="P377" s="12"/>
-      <c r="Q377" s="44"/>
-    </row>
-    <row r="378" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q377" s="43"/>
+    </row>
+    <row r="378" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="33" t="s">
         <v>30</v>
       </c>
@@ -18693,9 +18665,9 @@
         <v>695</v>
       </c>
       <c r="P378" s="12"/>
-      <c r="Q378" s="44"/>
-    </row>
-    <row r="379" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q378" s="43"/>
+    </row>
+    <row r="379" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="33" t="s">
         <v>30</v>
       </c>
@@ -18732,9 +18704,9 @@
         <v>695</v>
       </c>
       <c r="P379" s="12"/>
-      <c r="Q379" s="44"/>
-    </row>
-    <row r="380" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q379" s="43"/>
+    </row>
+    <row r="380" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="33" t="s">
         <v>30</v>
       </c>
@@ -18771,9 +18743,9 @@
         <v>695</v>
       </c>
       <c r="P380" s="12"/>
-      <c r="Q380" s="44"/>
-    </row>
-    <row r="381" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q380" s="43"/>
+    </row>
+    <row r="381" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="33" t="s">
         <v>30</v>
       </c>
@@ -18810,9 +18782,9 @@
         <v>695</v>
       </c>
       <c r="P381" s="12"/>
-      <c r="Q381" s="44"/>
-    </row>
-    <row r="382" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q381" s="43"/>
+    </row>
+    <row r="382" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="33" t="s">
         <v>30</v>
       </c>
@@ -18849,9 +18821,9 @@
         <v>695</v>
       </c>
       <c r="P382" s="12"/>
-      <c r="Q382" s="44"/>
-    </row>
-    <row r="383" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q382" s="43"/>
+    </row>
+    <row r="383" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="33" t="s">
         <v>30</v>
       </c>
@@ -18888,9 +18860,9 @@
         <v>695</v>
       </c>
       <c r="P383" s="12"/>
-      <c r="Q383" s="44"/>
-    </row>
-    <row r="384" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q383" s="43"/>
+    </row>
+    <row r="384" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="33" t="s">
         <v>30</v>
       </c>
@@ -18927,9 +18899,9 @@
         <v>695</v>
       </c>
       <c r="P384" s="12"/>
-      <c r="Q384" s="44"/>
-    </row>
-    <row r="385" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q384" s="43"/>
+    </row>
+    <row r="385" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="33" t="s">
         <v>30</v>
       </c>
@@ -18966,9 +18938,9 @@
         <v>695</v>
       </c>
       <c r="P385" s="12"/>
-      <c r="Q385" s="44"/>
-    </row>
-    <row r="386" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q385" s="43"/>
+    </row>
+    <row r="386" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="33" t="s">
         <v>30</v>
       </c>
@@ -19005,9 +18977,9 @@
         <v>695</v>
       </c>
       <c r="P386" s="12"/>
-      <c r="Q386" s="44"/>
-    </row>
-    <row r="387" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q386" s="43"/>
+    </row>
+    <row r="387" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="33" t="s">
         <v>30</v>
       </c>
@@ -19044,32 +19016,32 @@
         <v>695</v>
       </c>
       <c r="P387" s="12"/>
-      <c r="Q387" s="44"/>
-    </row>
-    <row r="388" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q387" s="43"/>
+    </row>
+    <row r="388" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="33" t="s">
         <v>30</v>
       </c>
       <c r="B388" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C388" s="42" t="s">
+      <c r="C388" s="41" t="s">
         <v>516</v>
       </c>
-      <c r="D388" s="45" t="s">
+      <c r="D388" s="44" t="s">
         <v>517</v>
       </c>
-      <c r="E388" s="42"/>
-      <c r="F388" s="42"/>
-      <c r="G388" s="42"/>
-      <c r="H388" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="I388" s="42"/>
-      <c r="J388" s="43">
+      <c r="E388" s="41"/>
+      <c r="F388" s="41"/>
+      <c r="G388" s="41"/>
+      <c r="H388" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="I388" s="41"/>
+      <c r="J388" s="42">
         <v>41365</v>
       </c>
-      <c r="K388" s="43"/>
+      <c r="K388" s="42"/>
       <c r="L388" s="35" t="s">
         <v>591</v>
       </c>
@@ -19083,36 +19055,36 @@
         <v>695</v>
       </c>
       <c r="P388" s="12"/>
-      <c r="Q388" s="44"/>
-    </row>
-    <row r="389" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A389" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B389" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C389" s="67" t="s">
+      <c r="Q388" s="43"/>
+    </row>
+    <row r="389" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A389" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B389" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C389" s="64" t="s">
         <v>520</v>
       </c>
-      <c r="D389" s="74" t="s">
+      <c r="D389" s="70" t="s">
         <v>570</v>
       </c>
-      <c r="E389" s="75"/>
-      <c r="F389" s="75"/>
-      <c r="G389" s="75"/>
-      <c r="H389" s="75"/>
-      <c r="I389" s="75"/>
-      <c r="J389" s="75"/>
-      <c r="K389" s="75"/>
-      <c r="L389" s="75"/>
-      <c r="M389" s="75"/>
-      <c r="N389" s="75"/>
-      <c r="O389" s="75"/>
-      <c r="P389" s="76"/>
-      <c r="Q389" s="44"/>
-    </row>
-    <row r="390" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E389" s="71"/>
+      <c r="F389" s="71"/>
+      <c r="G389" s="71"/>
+      <c r="H389" s="71"/>
+      <c r="I389" s="71"/>
+      <c r="J389" s="71"/>
+      <c r="K389" s="71"/>
+      <c r="L389" s="71"/>
+      <c r="M389" s="71"/>
+      <c r="N389" s="71"/>
+      <c r="O389" s="71"/>
+      <c r="P389" s="72"/>
+      <c r="Q389" s="43"/>
+    </row>
+    <row r="390" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="33" t="s">
         <v>30</v>
       </c>
@@ -19149,9 +19121,9 @@
         <v>695</v>
       </c>
       <c r="P390" s="12"/>
-      <c r="Q390" s="44"/>
-    </row>
-    <row r="391" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q390" s="43"/>
+    </row>
+    <row r="391" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="33" t="s">
         <v>30</v>
       </c>
@@ -19188,9 +19160,9 @@
         <v>695</v>
       </c>
       <c r="P391" s="12"/>
-      <c r="Q391" s="44"/>
-    </row>
-    <row r="392" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q391" s="43"/>
+    </row>
+    <row r="392" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="33" t="s">
         <v>30</v>
       </c>
@@ -19227,50 +19199,48 @@
         <v>695</v>
       </c>
       <c r="P392" s="12"/>
-      <c r="Q392" s="44"/>
-    </row>
-    <row r="393" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A393" s="46" t="s">
+      <c r="Q392" s="43"/>
+    </row>
+    <row r="393" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A393" s="33" t="s">
+        <v>929</v>
+      </c>
+      <c r="B393" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C393" s="32" t="s">
+        <v>930</v>
+      </c>
+      <c r="D393" s="32" t="s">
         <v>931</v>
       </c>
-      <c r="B393" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="C393" s="38" t="s">
-        <v>932</v>
-      </c>
-      <c r="D393" s="38" t="s">
-        <v>933</v>
-      </c>
-      <c r="E393" s="38"/>
-      <c r="F393" s="38"/>
-      <c r="G393" s="38"/>
-      <c r="H393" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I393" s="38"/>
-      <c r="J393" s="57">
+      <c r="E393" s="32"/>
+      <c r="F393" s="32"/>
+      <c r="G393" s="32"/>
+      <c r="H393" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I393" s="32"/>
+      <c r="J393" s="35">
         <v>45901</v>
       </c>
-      <c r="K393" s="57"/>
-      <c r="L393" s="57" t="s">
-        <v>591</v>
-      </c>
-      <c r="M393" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="N393" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="O393" s="59" t="s">
+      <c r="K393" s="35"/>
+      <c r="L393" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="M393" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="N393" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="O393" s="37" t="s">
         <v>695</v>
       </c>
-      <c r="P393" s="65"/>
-      <c r="Q393" s="39" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="394" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P393" s="62"/>
+      <c r="Q393" s="38"/>
+    </row>
+    <row r="394" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A394" s="3" t="s">
         <v>30</v>
       </c>
@@ -19280,51 +19250,51 @@
       <c r="C394" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="D394" s="77" t="s">
+      <c r="D394" s="67" t="s">
         <v>571</v>
       </c>
-      <c r="E394" s="78"/>
-      <c r="F394" s="78"/>
-      <c r="G394" s="78"/>
-      <c r="H394" s="78"/>
-      <c r="I394" s="78"/>
-      <c r="J394" s="78"/>
-      <c r="K394" s="78"/>
-      <c r="L394" s="78"/>
-      <c r="M394" s="78"/>
-      <c r="N394" s="78"/>
-      <c r="O394" s="78"/>
-      <c r="P394" s="79"/>
-      <c r="Q394" s="44"/>
-    </row>
-    <row r="395" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A395" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B395" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C395" s="67" t="s">
+      <c r="E394" s="68"/>
+      <c r="F394" s="68"/>
+      <c r="G394" s="68"/>
+      <c r="H394" s="68"/>
+      <c r="I394" s="68"/>
+      <c r="J394" s="68"/>
+      <c r="K394" s="68"/>
+      <c r="L394" s="68"/>
+      <c r="M394" s="68"/>
+      <c r="N394" s="68"/>
+      <c r="O394" s="68"/>
+      <c r="P394" s="69"/>
+      <c r="Q394" s="43"/>
+    </row>
+    <row r="395" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A395" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B395" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C395" s="64" t="s">
         <v>527</v>
       </c>
-      <c r="D395" s="74" t="s">
+      <c r="D395" s="70" t="s">
         <v>571</v>
       </c>
-      <c r="E395" s="75"/>
-      <c r="F395" s="75"/>
-      <c r="G395" s="75"/>
-      <c r="H395" s="75"/>
-      <c r="I395" s="75"/>
-      <c r="J395" s="75"/>
-      <c r="K395" s="75"/>
-      <c r="L395" s="75"/>
-      <c r="M395" s="75"/>
-      <c r="N395" s="75"/>
-      <c r="O395" s="75"/>
-      <c r="P395" s="76"/>
-      <c r="Q395" s="44"/>
-    </row>
-    <row r="396" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E395" s="71"/>
+      <c r="F395" s="71"/>
+      <c r="G395" s="71"/>
+      <c r="H395" s="71"/>
+      <c r="I395" s="71"/>
+      <c r="J395" s="71"/>
+      <c r="K395" s="71"/>
+      <c r="L395" s="71"/>
+      <c r="M395" s="71"/>
+      <c r="N395" s="71"/>
+      <c r="O395" s="71"/>
+      <c r="P395" s="72"/>
+      <c r="Q395" s="43"/>
+    </row>
+    <row r="396" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="33" t="s">
         <v>30</v>
       </c>
@@ -19367,9 +19337,9 @@
         <v>695</v>
       </c>
       <c r="P396" s="12"/>
-      <c r="Q396" s="44"/>
-    </row>
-    <row r="397" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q396" s="43"/>
+    </row>
+    <row r="397" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="33" t="s">
         <v>30</v>
       </c>
@@ -19412,9 +19382,9 @@
         <v>695</v>
       </c>
       <c r="P397" s="12"/>
-      <c r="Q397" s="44"/>
-    </row>
-    <row r="398" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q397" s="43"/>
+    </row>
+    <row r="398" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="33" t="s">
         <v>30</v>
       </c>
@@ -19457,9 +19427,9 @@
         <v>695</v>
       </c>
       <c r="P398" s="12"/>
-      <c r="Q398" s="44"/>
-    </row>
-    <row r="399" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q398" s="43"/>
+    </row>
+    <row r="399" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="33" t="s">
         <v>30</v>
       </c>
@@ -19502,9 +19472,9 @@
         <v>695</v>
       </c>
       <c r="P399" s="12"/>
-      <c r="Q399" s="44"/>
-    </row>
-    <row r="400" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q399" s="43"/>
+    </row>
+    <row r="400" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="33" t="s">
         <v>30</v>
       </c>
@@ -19543,9 +19513,9 @@
         <v>695</v>
       </c>
       <c r="P400" s="12"/>
-      <c r="Q400" s="44"/>
-    </row>
-    <row r="401" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q400" s="43"/>
+    </row>
+    <row r="401" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="33" t="s">
         <v>30</v>
       </c>
@@ -19584,9 +19554,9 @@
         <v>695</v>
       </c>
       <c r="P401" s="12"/>
-      <c r="Q401" s="44"/>
-    </row>
-    <row r="402" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q401" s="43"/>
+    </row>
+    <row r="402" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A402" s="3" t="s">
         <v>30</v>
       </c>
@@ -19596,51 +19566,51 @@
       <c r="C402" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="D402" s="77" t="s">
+      <c r="D402" s="67" t="s">
         <v>583</v>
       </c>
-      <c r="E402" s="78"/>
-      <c r="F402" s="78"/>
-      <c r="G402" s="78"/>
-      <c r="H402" s="78"/>
-      <c r="I402" s="78"/>
-      <c r="J402" s="78"/>
-      <c r="K402" s="78"/>
-      <c r="L402" s="78"/>
-      <c r="M402" s="78"/>
-      <c r="N402" s="78"/>
-      <c r="O402" s="78"/>
-      <c r="P402" s="79"/>
-      <c r="Q402" s="44"/>
-    </row>
-    <row r="403" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A403" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B403" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C403" s="67" t="s">
+      <c r="E402" s="68"/>
+      <c r="F402" s="68"/>
+      <c r="G402" s="68"/>
+      <c r="H402" s="68"/>
+      <c r="I402" s="68"/>
+      <c r="J402" s="68"/>
+      <c r="K402" s="68"/>
+      <c r="L402" s="68"/>
+      <c r="M402" s="68"/>
+      <c r="N402" s="68"/>
+      <c r="O402" s="68"/>
+      <c r="P402" s="69"/>
+      <c r="Q402" s="43"/>
+    </row>
+    <row r="403" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A403" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B403" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C403" s="64" t="s">
         <v>582</v>
       </c>
-      <c r="D403" s="74" t="s">
+      <c r="D403" s="70" t="s">
         <v>583</v>
       </c>
-      <c r="E403" s="75"/>
-      <c r="F403" s="75"/>
-      <c r="G403" s="75"/>
-      <c r="H403" s="75"/>
-      <c r="I403" s="75"/>
-      <c r="J403" s="75"/>
-      <c r="K403" s="75"/>
-      <c r="L403" s="75"/>
-      <c r="M403" s="75"/>
-      <c r="N403" s="75"/>
-      <c r="O403" s="75"/>
-      <c r="P403" s="76"/>
-      <c r="Q403" s="44"/>
-    </row>
-    <row r="404" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="E403" s="71"/>
+      <c r="F403" s="71"/>
+      <c r="G403" s="71"/>
+      <c r="H403" s="71"/>
+      <c r="I403" s="71"/>
+      <c r="J403" s="71"/>
+      <c r="K403" s="71"/>
+      <c r="L403" s="71"/>
+      <c r="M403" s="71"/>
+      <c r="N403" s="71"/>
+      <c r="O403" s="71"/>
+      <c r="P403" s="72"/>
+      <c r="Q403" s="43"/>
+    </row>
+    <row r="404" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A404" s="33" t="s">
         <v>30</v>
       </c>
@@ -19685,9 +19655,9 @@
         <v>591</v>
       </c>
       <c r="P404" s="12"/>
-      <c r="Q404" s="44"/>
-    </row>
-    <row r="405" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q404" s="43"/>
+    </row>
+    <row r="405" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A405" s="3" t="s">
         <v>30</v>
       </c>
@@ -19697,51 +19667,51 @@
       <c r="C405" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="D405" s="77" t="s">
+      <c r="D405" s="67" t="s">
         <v>588</v>
       </c>
-      <c r="E405" s="78"/>
-      <c r="F405" s="78"/>
-      <c r="G405" s="78"/>
-      <c r="H405" s="78"/>
-      <c r="I405" s="78"/>
-      <c r="J405" s="78"/>
-      <c r="K405" s="78"/>
-      <c r="L405" s="78"/>
-      <c r="M405" s="78"/>
-      <c r="N405" s="78"/>
-      <c r="O405" s="78"/>
-      <c r="P405" s="79"/>
-      <c r="Q405" s="44"/>
-    </row>
-    <row r="406" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A406" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B406" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C406" s="67" t="s">
+      <c r="E405" s="68"/>
+      <c r="F405" s="68"/>
+      <c r="G405" s="68"/>
+      <c r="H405" s="68"/>
+      <c r="I405" s="68"/>
+      <c r="J405" s="68"/>
+      <c r="K405" s="68"/>
+      <c r="L405" s="68"/>
+      <c r="M405" s="68"/>
+      <c r="N405" s="68"/>
+      <c r="O405" s="68"/>
+      <c r="P405" s="69"/>
+      <c r="Q405" s="43"/>
+    </row>
+    <row r="406" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A406" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B406" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C406" s="64" t="s">
         <v>587</v>
       </c>
-      <c r="D406" s="74" t="s">
+      <c r="D406" s="70" t="s">
         <v>588</v>
       </c>
-      <c r="E406" s="75"/>
-      <c r="F406" s="75"/>
-      <c r="G406" s="75"/>
-      <c r="H406" s="75"/>
-      <c r="I406" s="75"/>
-      <c r="J406" s="75"/>
-      <c r="K406" s="75"/>
-      <c r="L406" s="75"/>
-      <c r="M406" s="75"/>
-      <c r="N406" s="75"/>
-      <c r="O406" s="75"/>
-      <c r="P406" s="76"/>
-      <c r="Q406" s="44"/>
-    </row>
-    <row r="407" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="E406" s="71"/>
+      <c r="F406" s="71"/>
+      <c r="G406" s="71"/>
+      <c r="H406" s="71"/>
+      <c r="I406" s="71"/>
+      <c r="J406" s="71"/>
+      <c r="K406" s="71"/>
+      <c r="L406" s="71"/>
+      <c r="M406" s="71"/>
+      <c r="N406" s="71"/>
+      <c r="O406" s="71"/>
+      <c r="P406" s="72"/>
+      <c r="Q406" s="43"/>
+    </row>
+    <row r="407" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A407" s="33" t="s">
         <v>30</v>
       </c>
@@ -19786,7 +19756,7 @@
         <v>591</v>
       </c>
       <c r="P407" s="12"/>
-      <c r="Q407" s="44"/>
+      <c r="Q407" s="43"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:Q407" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -19796,17 +19766,32 @@
     <filterColumn colId="7" showButton="0"/>
   </autoFilter>
   <mergeCells count="53">
-    <mergeCell ref="D362:P362"/>
-    <mergeCell ref="D363:P363"/>
-    <mergeCell ref="D375:P375"/>
-    <mergeCell ref="D310:P310"/>
-    <mergeCell ref="D190:P190"/>
-    <mergeCell ref="D205:P205"/>
-    <mergeCell ref="D230:P230"/>
-    <mergeCell ref="D246:P246"/>
-    <mergeCell ref="D259:P259"/>
-    <mergeCell ref="D219:P219"/>
-    <mergeCell ref="D203:P203"/>
+    <mergeCell ref="D123:P123"/>
+    <mergeCell ref="D133:P133"/>
+    <mergeCell ref="D134:P134"/>
+    <mergeCell ref="D47:P47"/>
+    <mergeCell ref="D68:P68"/>
+    <mergeCell ref="D92:P92"/>
+    <mergeCell ref="D110:P110"/>
+    <mergeCell ref="D111:P111"/>
+    <mergeCell ref="D113:P113"/>
+    <mergeCell ref="D114:P114"/>
+    <mergeCell ref="D402:P402"/>
+    <mergeCell ref="D403:P403"/>
+    <mergeCell ref="D405:P405"/>
+    <mergeCell ref="D406:P406"/>
+    <mergeCell ref="D280:P280"/>
+    <mergeCell ref="D327:P327"/>
+    <mergeCell ref="D389:P389"/>
+    <mergeCell ref="D394:P394"/>
+    <mergeCell ref="D395:P395"/>
+    <mergeCell ref="D281:P281"/>
+    <mergeCell ref="D303:P303"/>
+    <mergeCell ref="D304:P304"/>
+    <mergeCell ref="D306:P306"/>
+    <mergeCell ref="D307:P307"/>
+    <mergeCell ref="D309:P309"/>
+    <mergeCell ref="D328:P328"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="E2:I2"/>
     <mergeCell ref="D231:P231"/>
@@ -19823,32 +19808,17 @@
     <mergeCell ref="D217:P217"/>
     <mergeCell ref="D42:P42"/>
     <mergeCell ref="D46:P46"/>
-    <mergeCell ref="D402:P402"/>
-    <mergeCell ref="D403:P403"/>
-    <mergeCell ref="D405:P405"/>
-    <mergeCell ref="D406:P406"/>
-    <mergeCell ref="D280:P280"/>
-    <mergeCell ref="D327:P327"/>
-    <mergeCell ref="D389:P389"/>
-    <mergeCell ref="D394:P394"/>
-    <mergeCell ref="D395:P395"/>
-    <mergeCell ref="D281:P281"/>
-    <mergeCell ref="D303:P303"/>
-    <mergeCell ref="D304:P304"/>
-    <mergeCell ref="D306:P306"/>
-    <mergeCell ref="D307:P307"/>
-    <mergeCell ref="D309:P309"/>
-    <mergeCell ref="D328:P328"/>
-    <mergeCell ref="D123:P123"/>
-    <mergeCell ref="D133:P133"/>
-    <mergeCell ref="D134:P134"/>
-    <mergeCell ref="D47:P47"/>
-    <mergeCell ref="D68:P68"/>
-    <mergeCell ref="D92:P92"/>
-    <mergeCell ref="D110:P110"/>
-    <mergeCell ref="D111:P111"/>
-    <mergeCell ref="D113:P113"/>
-    <mergeCell ref="D114:P114"/>
+    <mergeCell ref="D362:P362"/>
+    <mergeCell ref="D363:P363"/>
+    <mergeCell ref="D375:P375"/>
+    <mergeCell ref="D310:P310"/>
+    <mergeCell ref="D190:P190"/>
+    <mergeCell ref="D205:P205"/>
+    <mergeCell ref="D230:P230"/>
+    <mergeCell ref="D246:P246"/>
+    <mergeCell ref="D259:P259"/>
+    <mergeCell ref="D219:P219"/>
+    <mergeCell ref="D203:P203"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M1:N1 M3:N1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -19982,42 +19952,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="11.5703125" style="47"/>
-    <col min="4" max="4" width="49.140625" style="47" customWidth="1"/>
-    <col min="5" max="11" width="11.5703125" style="47"/>
-    <col min="12" max="12" width="20.85546875" style="47" customWidth="1"/>
-    <col min="13" max="13" width="16.28515625" style="47" customWidth="1"/>
-    <col min="14" max="14" width="20" style="47" customWidth="1"/>
-    <col min="15" max="15" width="70" style="47" customWidth="1"/>
-    <col min="16" max="16384" width="11.5703125" style="47"/>
+    <col min="1" max="3" width="11.54296875" style="46"/>
+    <col min="4" max="4" width="49.1796875" style="46" customWidth="1"/>
+    <col min="5" max="11" width="11.54296875" style="46"/>
+    <col min="12" max="12" width="20.81640625" style="46" customWidth="1"/>
+    <col min="13" max="13" width="16.26953125" style="46" customWidth="1"/>
+    <col min="14" max="14" width="20" style="46" customWidth="1"/>
+    <col min="15" max="15" width="70" style="46" customWidth="1"/>
+    <col min="16" max="16384" width="11.54296875" style="46"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="66" t="s">
+    <row r="1" spans="1:16" ht="39" x14ac:dyDescent="0.35">
+      <c r="A1" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="63" t="s">
         <v>572</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="D1" s="63" t="s">
         <v>573</v>
       </c>
-      <c r="E1" s="81" t="s">
+      <c r="E1" s="74" t="s">
         <v>574</v>
       </c>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="66" t="s">
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="63" t="s">
         <v>575</v>
       </c>
-      <c r="K1" s="66" t="s">
+      <c r="K1" s="63" t="s">
         <v>576</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -20032,21 +20002,21 @@
       <c r="O1" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="P1" s="41" t="s">
+      <c r="P1" s="40" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="54" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
+    <row r="2" spans="1:16" s="53" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="43" t="s">
         <v>796</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="43" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="29" t="s">
         <v>776</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="47" t="s">
         <v>778</v>
       </c>
       <c r="E2" s="29" t="s">
@@ -20055,38 +20025,38 @@
       <c r="F2" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="49">
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="48">
         <v>43684</v>
       </c>
-      <c r="K2" s="40"/>
+      <c r="K2" s="39"/>
       <c r="L2" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="50" t="s">
-        <v>8</v>
-      </c>
-      <c r="N2" s="51" t="s">
+      <c r="M2" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="50" t="s">
         <v>624</v>
       </c>
-      <c r="O2" s="52" t="s">
+      <c r="O2" s="51" t="s">
         <v>672</v>
       </c>
-      <c r="P2" s="53"/>
-    </row>
-    <row r="3" spans="1:16" s="54" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="44" t="s">
+      <c r="P2" s="52"/>
+    </row>
+    <row r="3" spans="1:16" s="53" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="43" t="s">
         <v>796</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="43" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="29" t="s">
         <v>777</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="47" t="s">
         <v>779</v>
       </c>
       <c r="E3" s="29" t="s">
@@ -20095,32 +20065,32 @@
       <c r="F3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="49">
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="48">
         <v>43684</v>
       </c>
-      <c r="K3" s="40"/>
+      <c r="K3" s="39"/>
       <c r="L3" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" s="51" t="s">
+      <c r="M3" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="50" t="s">
         <v>624</v>
       </c>
-      <c r="O3" s="52" t="s">
+      <c r="O3" s="51" t="s">
         <v>672</v>
       </c>
-      <c r="P3" s="53"/>
-    </row>
-    <row r="4" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="44" t="s">
+      <c r="P3" s="52"/>
+    </row>
+    <row r="4" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="43" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="27" t="s">
@@ -20138,7 +20108,7 @@
       </c>
       <c r="H4" s="30"/>
       <c r="I4" s="30"/>
-      <c r="J4" s="55">
+      <c r="J4" s="54">
         <v>1</v>
       </c>
       <c r="K4" s="25"/>
@@ -20148,19 +20118,19 @@
       <c r="M4" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="51" t="s">
+      <c r="N4" s="50" t="s">
         <v>624</v>
       </c>
-      <c r="O4" s="52" t="s">
+      <c r="O4" s="51" t="s">
         <v>672</v>
       </c>
       <c r="P4" s="25"/>
     </row>
-    <row r="5" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="44" t="s">
+    <row r="5" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="43" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="27" t="s">
@@ -20178,7 +20148,7 @@
       </c>
       <c r="H5" s="30"/>
       <c r="I5" s="30"/>
-      <c r="J5" s="55">
+      <c r="J5" s="54">
         <v>1</v>
       </c>
       <c r="K5" s="25"/>
@@ -20188,19 +20158,19 @@
       <c r="M5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="51" t="s">
+      <c r="N5" s="50" t="s">
         <v>624</v>
       </c>
-      <c r="O5" s="52" t="s">
+      <c r="O5" s="51" t="s">
         <v>672</v>
       </c>
       <c r="P5" s="25"/>
     </row>
-    <row r="6" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="44" t="s">
+    <row r="6" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="43" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="27" t="s">
@@ -20216,7 +20186,7 @@
       <c r="G6" s="30"/>
       <c r="H6" s="30"/>
       <c r="I6" s="30"/>
-      <c r="J6" s="55">
+      <c r="J6" s="54">
         <v>1</v>
       </c>
       <c r="K6" s="25"/>
@@ -20226,19 +20196,19 @@
       <c r="M6" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="N6" s="51" t="s">
+      <c r="N6" s="50" t="s">
         <v>624</v>
       </c>
-      <c r="O6" s="52" t="s">
+      <c r="O6" s="51" t="s">
         <v>672</v>
       </c>
       <c r="P6" s="25"/>
     </row>
-    <row r="7" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="44" t="s">
+    <row r="7" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="43" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="27" t="s">
@@ -20256,7 +20226,7 @@
       </c>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="55">
+      <c r="J7" s="54">
         <v>1</v>
       </c>
       <c r="K7" s="25"/>
@@ -20266,19 +20236,19 @@
       <c r="M7" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="N7" s="51" t="s">
+      <c r="N7" s="50" t="s">
         <v>624</v>
       </c>
-      <c r="O7" s="52" t="s">
+      <c r="O7" s="51" t="s">
         <v>672</v>
       </c>
       <c r="P7" s="25"/>
     </row>
-    <row r="8" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="44" t="s">
+    <row r="8" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="43" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="27" t="s">
@@ -20298,7 +20268,7 @@
       <c r="I8" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J8" s="55">
+      <c r="J8" s="54">
         <v>1</v>
       </c>
       <c r="K8" s="25"/>
@@ -20308,19 +20278,19 @@
       <c r="M8" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="N8" s="51" t="s">
+      <c r="N8" s="50" t="s">
         <v>624</v>
       </c>
-      <c r="O8" s="52" t="s">
+      <c r="O8" s="51" t="s">
         <v>672</v>
       </c>
       <c r="P8" s="25"/>
     </row>
-    <row r="9" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="44" t="s">
+    <row r="9" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="43" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="27" t="s">
@@ -20340,7 +20310,7 @@
       <c r="I9" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="55">
+      <c r="J9" s="54">
         <v>1</v>
       </c>
       <c r="K9" s="25"/>
@@ -20350,19 +20320,19 @@
       <c r="M9" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="N9" s="51" t="s">
+      <c r="N9" s="50" t="s">
         <v>624</v>
       </c>
-      <c r="O9" s="52" t="s">
+      <c r="O9" s="51" t="s">
         <v>672</v>
       </c>
       <c r="P9" s="25"/>
     </row>
-    <row r="10" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="44" t="s">
+    <row r="10" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="43" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="27" t="s">
@@ -20380,7 +20350,7 @@
       </c>
       <c r="H10" s="30"/>
       <c r="I10" s="30"/>
-      <c r="J10" s="55">
+      <c r="J10" s="54">
         <v>1</v>
       </c>
       <c r="K10" s="25"/>
@@ -20390,19 +20360,19 @@
       <c r="M10" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="N10" s="51" t="s">
+      <c r="N10" s="50" t="s">
         <v>624</v>
       </c>
-      <c r="O10" s="52" t="s">
+      <c r="O10" s="51" t="s">
         <v>672</v>
       </c>
       <c r="P10" s="25"/>
     </row>
-    <row r="11" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="44" t="s">
+    <row r="11" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="43" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="27" t="s">
@@ -20420,7 +20390,7 @@
       </c>
       <c r="H11" s="30"/>
       <c r="I11" s="30"/>
-      <c r="J11" s="55">
+      <c r="J11" s="54">
         <v>1</v>
       </c>
       <c r="K11" s="25"/>
@@ -20430,19 +20400,19 @@
       <c r="M11" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="51" t="s">
+      <c r="N11" s="50" t="s">
         <v>624</v>
       </c>
-      <c r="O11" s="52" t="s">
+      <c r="O11" s="51" t="s">
         <v>672</v>
       </c>
       <c r="P11" s="25"/>
     </row>
-    <row r="12" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="44" t="s">
+    <row r="12" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="43" t="s">
         <v>796</v>
       </c>
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="43" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="27" t="s">
@@ -20458,7 +20428,7 @@
       <c r="G12" s="30"/>
       <c r="H12" s="30"/>
       <c r="I12" s="30"/>
-      <c r="J12" s="55">
+      <c r="J12" s="54">
         <v>43685</v>
       </c>
       <c r="K12" s="25"/>
@@ -20468,19 +20438,19 @@
       <c r="M12" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="51" t="s">
+      <c r="N12" s="50" t="s">
         <v>624</v>
       </c>
-      <c r="O12" s="52" t="s">
+      <c r="O12" s="51" t="s">
         <v>672</v>
       </c>
-      <c r="P12" s="44"/>
-    </row>
-    <row r="13" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="44" t="s">
+      <c r="P12" s="43"/>
+    </row>
+    <row r="13" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="43" t="s">
         <v>796</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="43" t="s">
         <v>3</v>
       </c>
       <c r="C13" s="27" t="s">
@@ -20496,7 +20466,7 @@
       <c r="G13" s="30"/>
       <c r="H13" s="30"/>
       <c r="I13" s="30"/>
-      <c r="J13" s="55">
+      <c r="J13" s="54">
         <v>43685</v>
       </c>
       <c r="K13" s="25"/>
@@ -20506,19 +20476,19 @@
       <c r="M13" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="N13" s="51" t="s">
+      <c r="N13" s="50" t="s">
         <v>624</v>
       </c>
-      <c r="O13" s="52" t="s">
+      <c r="O13" s="51" t="s">
         <v>672</v>
       </c>
-      <c r="P13" s="44"/>
-    </row>
-    <row r="14" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="44" t="s">
+      <c r="P13" s="43"/>
+    </row>
+    <row r="14" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="43" t="s">
         <v>796</v>
       </c>
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="43" t="s">
         <v>3</v>
       </c>
       <c r="C14" s="27" t="s">
@@ -20534,7 +20504,7 @@
       <c r="G14" s="30"/>
       <c r="H14" s="30"/>
       <c r="I14" s="30"/>
-      <c r="J14" s="55">
+      <c r="J14" s="54">
         <v>43685</v>
       </c>
       <c r="K14" s="25"/>
@@ -20544,19 +20514,19 @@
       <c r="M14" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="51" t="s">
+      <c r="N14" s="50" t="s">
         <v>624</v>
       </c>
-      <c r="O14" s="52" t="s">
+      <c r="O14" s="51" t="s">
         <v>672</v>
       </c>
-      <c r="P14" s="44"/>
-    </row>
-    <row r="15" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="44" t="s">
+      <c r="P14" s="43"/>
+    </row>
+    <row r="15" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="43" t="s">
         <v>796</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="43" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="27" t="s">
@@ -20572,7 +20542,7 @@
       <c r="G15" s="30"/>
       <c r="H15" s="30"/>
       <c r="I15" s="30"/>
-      <c r="J15" s="55">
+      <c r="J15" s="54">
         <v>43685</v>
       </c>
       <c r="K15" s="25"/>
@@ -20582,19 +20552,19 @@
       <c r="M15" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="N15" s="51" t="s">
+      <c r="N15" s="50" t="s">
         <v>624</v>
       </c>
-      <c r="O15" s="52" t="s">
+      <c r="O15" s="51" t="s">
         <v>672</v>
       </c>
-      <c r="P15" s="44"/>
-    </row>
-    <row r="16" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="44" t="s">
+      <c r="P15" s="43"/>
+    </row>
+    <row r="16" spans="1:16" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="43" t="s">
         <v>867</v>
       </c>
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="43" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="27" t="s">
@@ -20612,7 +20582,7 @@
       </c>
       <c r="H16" s="30"/>
       <c r="I16" s="30"/>
-      <c r="J16" s="55">
+      <c r="J16" s="54">
         <v>44546</v>
       </c>
       <c r="K16" s="25"/>
@@ -20622,13 +20592,13 @@
       <c r="M16" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="N16" s="51" t="s">
+      <c r="N16" s="50" t="s">
         <v>624</v>
       </c>
-      <c r="O16" s="52" t="s">
+      <c r="O16" s="51" t="s">
         <v>672</v>
       </c>
-      <c r="P16" s="44"/>
+      <c r="P16" s="43"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P16" xr:uid="{00000000-0009-0000-0000-000001000000}">
@@ -20661,16 +20631,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="3" max="3" width="25.81640625" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="59.28515625" customWidth="1"/>
+    <col min="5" max="5" width="59.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>614</v>
       </c>
@@ -20687,7 +20657,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>615</v>
       </c>
@@ -20702,7 +20672,7 @@
       </c>
       <c r="E2" s="8"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="25" t="s">
         <v>623</v>
       </c>
@@ -20717,7 +20687,7 @@
       </c>
       <c r="E3" s="8"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>619</v>
       </c>
@@ -20746,23 +20716,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="14"/>
+    <col min="1" max="1" width="11.453125" style="14"/>
     <col min="2" max="3" width="57" style="14" customWidth="1"/>
-    <col min="4" max="4" width="74.140625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" style="14" customWidth="1"/>
-    <col min="6" max="16384" width="11.42578125" style="14"/>
+    <col min="4" max="4" width="74.1796875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="25.7265625" style="14" customWidth="1"/>
+    <col min="6" max="16384" width="11.453125" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="84" t="s">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="77" t="s">
         <v>604</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>607</v>
       </c>
@@ -20773,7 +20743,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="87" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>605</v>
       </c>
@@ -20784,16 +20754,16 @@
         <v>685</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="87" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="80" t="s">
         <v>606</v>
       </c>
-      <c r="B9" s="88"/>
-      <c r="C9" s="88"/>
-      <c r="D9" s="88"/>
-      <c r="E9" s="88"/>
-    </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="81"/>
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+    </row>
+    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
         <v>572</v>
       </c>
@@ -20810,7 +20780,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>592</v>
       </c>
@@ -20823,7 +20793,7 @@
       </c>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>594</v>
       </c>
@@ -20840,7 +20810,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>595</v>
       </c>
@@ -20857,7 +20827,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="31" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" s="31" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="20" t="s">
         <v>597</v>
       </c>
@@ -20872,7 +20842,7 @@
       </c>
       <c r="E14" s="20"/>
     </row>
-    <row r="15" spans="1:5" s="31" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" s="31" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" s="20" t="s">
         <v>598</v>
       </c>
@@ -20887,7 +20857,7 @@
       </c>
       <c r="E15" s="20"/>
     </row>
-    <row r="16" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>599</v>
       </c>
@@ -20902,7 +20872,7 @@
       </c>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>600</v>
       </c>
@@ -20917,7 +20887,7 @@
       </c>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A18" s="20" t="s">
         <v>602</v>
       </c>
@@ -20932,7 +20902,7 @@
       </c>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>603</v>
       </c>
@@ -20947,7 +20917,7 @@
       </c>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>608</v>
       </c>
@@ -20962,7 +20932,7 @@
       </c>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>609</v>
       </c>
@@ -20977,7 +20947,7 @@
       </c>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>611</v>
       </c>
@@ -20994,7 +20964,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>612</v>
       </c>
@@ -21009,7 +20979,7 @@
       </c>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>621</v>
       </c>
@@ -21024,7 +20994,7 @@
       </c>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:5" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>652</v>
       </c>
@@ -21041,7 +21011,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A26" s="23" t="s">
         <v>629</v>
       </c>
@@ -21056,7 +21026,7 @@
       </c>
       <c r="E26" s="23"/>
     </row>
-    <row r="27" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A27" s="23" t="s">
         <v>630</v>
       </c>
